--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R16" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2630,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2646,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2657,10 +2677,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845363</v>
+        <v>128845356</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541623</v>
+        <v>541606</v>
       </c>
       <c r="R17" t="n">
-        <v>7174167</v>
+        <v>7174439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2737,7 +2757,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,39 +2795,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R18" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,12 +2864,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2892,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2951,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,12 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,21 +2992,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845360</v>
+        <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541640</v>
+        <v>541428</v>
       </c>
       <c r="R20" t="n">
-        <v>7174274</v>
+        <v>7174314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,7 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,6 +3104,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3118,7 +3138,7 @@
         <v>128845365</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3225,7 +3245,7 @@
         <v>128845346</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3334,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845280</v>
+        <v>128845360</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3345,39 +3365,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541574</v>
+        <v>541640</v>
       </c>
       <c r="R23" t="n">
-        <v>7174569</v>
+        <v>7174274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3409,7 +3424,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3419,12 +3434,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3451,32 +3461,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845328</v>
+        <v>128845296</v>
       </c>
       <c r="B24" t="n">
-        <v>91490</v>
+        <v>80254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541428</v>
+        <v>541359</v>
       </c>
       <c r="R24" t="n">
-        <v>7174314</v>
+        <v>7174394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3521,7 +3531,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3531,12 +3541,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3550,17 +3560,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3578,10 +3588,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845296</v>
+        <v>128845322</v>
       </c>
       <c r="B25" t="n">
-        <v>80250</v>
+        <v>80261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3589,21 +3599,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3613,10 +3623,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541359</v>
+        <v>541579</v>
       </c>
       <c r="R25" t="n">
-        <v>7174394</v>
+        <v>7174417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3648,7 +3658,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3658,7 +3668,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3705,45 +3715,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845322</v>
+        <v>128845280</v>
       </c>
       <c r="B26" t="n">
-        <v>80257</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541579</v>
+        <v>541574</v>
       </c>
       <c r="R26" t="n">
-        <v>7174417</v>
+        <v>7174569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845340</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541062</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,6 +3928,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3944,10 +3959,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845340</v>
+        <v>128845359</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3955,21 +3970,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3979,10 +3994,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541062</v>
+        <v>541617</v>
       </c>
       <c r="R28" t="n">
-        <v>7174293</v>
+        <v>7174319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,7 +4029,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,12 +4039,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4040,21 +4050,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4071,10 +4066,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845359</v>
+        <v>128845353</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541617</v>
+        <v>541612</v>
       </c>
       <c r="R29" t="n">
-        <v>7174319</v>
+        <v>7174586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4141,7 +4136,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4151,7 +4146,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,45 +4178,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845323</v>
+        <v>128845298</v>
       </c>
       <c r="B30" t="n">
-        <v>98953</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541182</v>
+        <v>541013</v>
       </c>
       <c r="R30" t="n">
-        <v>7174332</v>
+        <v>7174346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4248,7 +4253,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4258,7 +4263,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4285,50 +4295,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>98959</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R31" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4360,7 +4365,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4370,12 +4375,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4402,10 +4402,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B32" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4433,7 +4433,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R32" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845332</v>
+        <v>128845297</v>
       </c>
       <c r="B33" t="n">
-        <v>91512</v>
+        <v>57713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,34 +4530,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541284</v>
+        <v>541232</v>
       </c>
       <c r="R33" t="n">
-        <v>7174287</v>
+        <v>7174426</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4597,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,12 +4607,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4615,21 +4623,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4646,10 +4639,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845341</v>
+        <v>128845293</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,34 +4650,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541131</v>
+        <v>541157</v>
       </c>
       <c r="R34" t="n">
-        <v>7174440</v>
+        <v>7174382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4716,7 +4714,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4726,7 +4724,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4753,48 +4756,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845275</v>
+        <v>128845332</v>
       </c>
       <c r="B35" t="n">
-        <v>92191</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541057</v>
+        <v>541284</v>
       </c>
       <c r="R35" t="n">
-        <v>7174336</v>
+        <v>7174287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4850,7 +4850,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4884,10 +4883,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,42 +4894,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R36" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4962,7 +4953,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4972,12 +4963,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5004,50 +4990,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845293</v>
+        <v>128845275</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541157</v>
+        <v>541057</v>
       </c>
       <c r="R37" t="n">
-        <v>7174382</v>
+        <v>7174336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5063,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5073,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5103,8 +5087,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845362</v>
+        <v>128845339</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,34 +5132,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541644</v>
+        <v>541139</v>
       </c>
       <c r="R38" t="n">
-        <v>7174158</v>
+        <v>7174393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5194,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,7 +5204,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5210,8 +5218,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5228,10 +5252,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845367</v>
+        <v>128845327</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5239,21 +5263,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5263,10 +5287,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541394</v>
+        <v>541654</v>
       </c>
       <c r="R39" t="n">
-        <v>7174344</v>
+        <v>7174247</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5298,7 +5322,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5308,12 +5332,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5324,6 +5348,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5340,10 +5379,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845339</v>
+        <v>128845362</v>
       </c>
       <c r="B40" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5351,37 +5390,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541139</v>
+        <v>541644</v>
       </c>
       <c r="R40" t="n">
-        <v>7174393</v>
+        <v>7174158</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5413,7 +5449,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5423,12 +5459,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5437,24 +5468,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5471,10 +5486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845361</v>
+        <v>128845367</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,10 +5521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R41" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5541,7 +5556,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5551,7 +5566,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5578,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845327</v>
+        <v>128845361</v>
       </c>
       <c r="B42" t="n">
-        <v>91490</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5589,21 +5609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5613,10 +5633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541654</v>
+        <v>541658</v>
       </c>
       <c r="R42" t="n">
-        <v>7174247</v>
+        <v>7174215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5668,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5678,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,21 +5689,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845357</v>
+        <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541607</v>
+        <v>541626</v>
       </c>
       <c r="R45" t="n">
-        <v>7174400</v>
+        <v>7174307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,7 +6026,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6037,6 +6042,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6056,7 +6076,7 @@
         <v>128845368</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6163,7 +6183,7 @@
         <v>128845342</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6267,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845290</v>
+        <v>128845357</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6298,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541211</v>
+        <v>541607</v>
       </c>
       <c r="R48" t="n">
-        <v>7174387</v>
+        <v>7174400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6342,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6352,12 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,10 +6394,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845326</v>
+        <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,34 +6405,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541626</v>
+        <v>541211</v>
       </c>
       <c r="R49" t="n">
-        <v>7174307</v>
+        <v>7174387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6454,7 +6469,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6464,12 +6479,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6480,21 +6495,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845383</v>
+        <v>128845289</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,34 +6522,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541079</v>
+        <v>541254</v>
       </c>
       <c r="R50" t="n">
-        <v>7174333</v>
+        <v>7174391</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6586,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6596,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6623,10 +6628,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845385</v>
+        <v>128845291</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,34 +6639,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541163</v>
+        <v>541147</v>
       </c>
       <c r="R51" t="n">
-        <v>7174329</v>
+        <v>7174441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6703,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,12 +6713,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6738,7 +6748,7 @@
         <v>128845335</v>
       </c>
       <c r="B52" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6862,10 +6872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845381</v>
+        <v>128845336</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6873,21 +6883,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6897,10 +6907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541025</v>
+        <v>541251</v>
       </c>
       <c r="R53" t="n">
-        <v>7174364</v>
+        <v>7174388</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6942,12 +6952,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6958,6 +6968,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6974,10 +6999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845336</v>
+        <v>128845385</v>
       </c>
       <c r="B54" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6985,21 +7010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7009,10 +7034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541251</v>
+        <v>541163</v>
       </c>
       <c r="R54" t="n">
-        <v>7174388</v>
+        <v>7174329</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7044,7 +7069,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7054,12 +7079,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7070,21 +7095,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7101,10 +7111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845304</v>
+        <v>128845381</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7136,10 +7146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541120</v>
+        <v>541025</v>
       </c>
       <c r="R55" t="n">
-        <v>7174297</v>
+        <v>7174364</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7171,7 +7181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7181,7 +7191,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7208,10 +7223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845369</v>
+        <v>128845383</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7243,10 +7258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541285</v>
+        <v>541079</v>
       </c>
       <c r="R56" t="n">
-        <v>7174269</v>
+        <v>7174333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7278,7 +7293,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7288,7 +7303,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7315,10 +7335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845289</v>
+        <v>128845304</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7326,39 +7346,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541254</v>
+        <v>541120</v>
       </c>
       <c r="R57" t="n">
-        <v>7174391</v>
+        <v>7174297</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7405,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,12 +7415,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7432,10 +7442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845291</v>
+        <v>128845369</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7443,39 +7453,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541147</v>
+        <v>541285</v>
       </c>
       <c r="R58" t="n">
-        <v>7174441</v>
+        <v>7174269</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7512,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7552,7 +7552,7 @@
         <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>128845373</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845348</v>
+        <v>128845354</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541504</v>
+        <v>541618</v>
       </c>
       <c r="R61" t="n">
-        <v>7174451</v>
+        <v>7174522</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7890,10 +7890,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845354</v>
+        <v>128845348</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541618</v>
+        <v>541504</v>
       </c>
       <c r="R62" t="n">
-        <v>7174522</v>
+        <v>7174451</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845378</v>
+        <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541032</v>
+        <v>541610</v>
       </c>
       <c r="R64" t="n">
-        <v>7174308</v>
+        <v>7174586</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,7 +8194,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8205,6 +8210,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8221,10 +8241,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845375</v>
+        <v>128845378</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8256,10 +8276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541136</v>
+        <v>541032</v>
       </c>
       <c r="R65" t="n">
-        <v>7174402</v>
+        <v>7174308</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8291,7 +8311,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8301,7 +8321,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8331,7 +8351,7 @@
         <v>128845355</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8440,10 +8460,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845284</v>
+        <v>128845375</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8451,39 +8471,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R67" t="n">
-        <v>7174351</v>
+        <v>7174402</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8515,7 +8530,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8525,12 +8540,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,10 +8567,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845324</v>
+        <v>128845282</v>
       </c>
       <c r="B68" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,34 +8578,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174586</v>
+        <v>7174473</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8642,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8652,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8668,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8684,7 +8684,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845282</v>
+        <v>128845284</v>
       </c>
       <c r="B69" t="n">
         <v>57716</v>
@@ -8727,7 +8727,7 @@
         <v>541637</v>
       </c>
       <c r="R69" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8801,10 +8801,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845384</v>
+        <v>128845364</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541112</v>
+        <v>541490</v>
       </c>
       <c r="R70" t="n">
-        <v>7174350</v>
+        <v>7174268</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8911,7 +8911,7 @@
         <v>128845351</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9020,10 +9020,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845364</v>
+        <v>128845384</v>
       </c>
       <c r="B72" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541490</v>
+        <v>541112</v>
       </c>
       <c r="R72" t="n">
-        <v>7174268</v>
+        <v>7174350</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9130,7 +9130,7 @@
         <v>128845358</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845300</v>
+        <v>128845379</v>
       </c>
       <c r="B74" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541095</v>
+        <v>540962</v>
       </c>
       <c r="R74" t="n">
-        <v>7174393</v>
+        <v>7174330</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9314,7 +9314,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9341,10 +9346,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845379</v>
+        <v>128845300</v>
       </c>
       <c r="B75" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9376,10 +9381,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540962</v>
+        <v>541095</v>
       </c>
       <c r="R75" t="n">
-        <v>7174330</v>
+        <v>7174393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9411,7 +9416,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9421,12 +9426,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845377</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128845372</v>
       </c>
       <c r="B77" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128845271</v>
       </c>
       <c r="B78" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845294</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>57876</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,34 +9805,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541544</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9886,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9906,10 +9918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845329</v>
       </c>
       <c r="B80" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9917,21 +9929,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9941,10 +9953,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541141</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9976,7 +9988,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9986,7 +9998,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9997,6 +10014,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10013,10 +10045,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>91490</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,21 +10056,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10048,10 +10080,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541027</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10083,7 +10115,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10093,12 +10125,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10109,21 +10141,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10140,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B82" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10151,46 +10168,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R82" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10227,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10237,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10267,7 +10267,7 @@
         <v>128845352</v>
       </c>
       <c r="B83" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>128845347</v>
       </c>
       <c r="B84" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>128845302</v>
       </c>
       <c r="B85" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>128845273</v>
       </c>
       <c r="B86" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>128845344</v>
       </c>
       <c r="B87" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10824,50 +10824,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B88" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10899,7 +10894,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10909,12 +10904,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10925,6 +10920,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10941,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845276</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
         <v>57716</v>
@@ -10972,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10981,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541274</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174268</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11016,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11026,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11058,45 +11068,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845272</v>
+        <v>128845281</v>
       </c>
       <c r="B90" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541629</v>
+        <v>541599</v>
       </c>
       <c r="R90" t="n">
-        <v>7174402</v>
+        <v>7174544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11128,7 +11143,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11138,12 +11153,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11154,21 +11169,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11185,7 +11185,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B91" t="n">
         <v>57716</v>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R91" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -11305,7 +11305,7 @@
         <v>128845338</v>
       </c>
       <c r="B92" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11429,10 +11429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845274</v>
+        <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11458,19 +11458,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541116</v>
+        <v>541134</v>
       </c>
       <c r="R93" t="n">
-        <v>7174272</v>
+        <v>7174353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11502,7 +11499,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11512,12 +11509,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11526,7 +11523,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11556,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845270</v>
+        <v>128845274</v>
       </c>
       <c r="B94" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,16 +11585,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541134</v>
+        <v>541116</v>
       </c>
       <c r="R94" t="n">
-        <v>7174353</v>
+        <v>7174272</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11630,7 +11629,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11640,12 +11639,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11654,6 +11653,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845285</v>
+        <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,39 +11815,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541640</v>
+        <v>541271</v>
       </c>
       <c r="R96" t="n">
-        <v>7174353</v>
+        <v>7174269</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11879,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11889,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11905,6 +11900,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12038,10 +12048,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845370</v>
+        <v>128845285</v>
       </c>
       <c r="B98" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12049,34 +12059,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541222</v>
+        <v>541640</v>
       </c>
       <c r="R98" t="n">
-        <v>7174409</v>
+        <v>7174353</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12108,7 +12123,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12118,12 +12133,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12150,10 +12165,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845331</v>
+        <v>128845370</v>
       </c>
       <c r="B99" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12161,21 +12176,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12185,10 +12200,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541271</v>
+        <v>541222</v>
       </c>
       <c r="R99" t="n">
-        <v>7174269</v>
+        <v>7174409</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12220,7 +12235,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12230,12 +12245,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12246,21 +12261,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12280,7 +12280,7 @@
         <v>128845382</v>
       </c>
       <c r="B100" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>128845343</v>
       </c>
       <c r="B101" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>128845269</v>
       </c>
       <c r="B102" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>128845376</v>
       </c>
       <c r="B103" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>128845334</v>
       </c>
       <c r="B105" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845330</v>
       </c>
       <c r="B106" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845366</v>
+        <v>128845345</v>
       </c>
       <c r="B107" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541398</v>
+        <v>541348</v>
       </c>
       <c r="R107" t="n">
-        <v>7174337</v>
+        <v>7174394</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,7 +13156,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13183,10 +13188,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845350</v>
+        <v>128845366</v>
       </c>
       <c r="B108" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13218,10 +13223,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541554</v>
+        <v>541398</v>
       </c>
       <c r="R108" t="n">
-        <v>7174535</v>
+        <v>7174337</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13253,7 +13258,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13263,12 +13268,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,10 +13295,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845349</v>
+        <v>128845350</v>
       </c>
       <c r="B109" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541462</v>
+        <v>541554</v>
       </c>
       <c r="R109" t="n">
-        <v>7174528</v>
+        <v>7174535</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,7 +13375,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13402,10 +13407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845345</v>
+        <v>128845349</v>
       </c>
       <c r="B110" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13437,10 +13442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541348</v>
+        <v>541462</v>
       </c>
       <c r="R110" t="n">
-        <v>7174394</v>
+        <v>7174528</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13472,7 +13477,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,12 +13487,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845325</v>
+        <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>91495</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541618</v>
+        <v>541606</v>
       </c>
       <c r="R16" t="n">
-        <v>7174399</v>
+        <v>7174439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,12 +2630,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,21 +2641,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2677,7 +2657,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845356</v>
+        <v>128845363</v>
       </c>
       <c r="B17" t="n">
         <v>79120</v>
@@ -2712,10 +2692,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541606</v>
+        <v>541623</v>
       </c>
       <c r="R17" t="n">
-        <v>7174439</v>
+        <v>7174167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2727,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,7 +2737,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2784,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845363</v>
+        <v>128845286</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,34 +2775,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541623</v>
+        <v>541617</v>
       </c>
       <c r="R18" t="n">
-        <v>7174167</v>
+        <v>7174320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2854,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,7 +2849,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2891,10 +2881,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845325</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>91500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2892,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541618</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2961,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,6 +2977,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3011,7 +3011,7 @@
         <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845365</v>
+        <v>128845360</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541453</v>
+        <v>541640</v>
       </c>
       <c r="R21" t="n">
-        <v>7174305</v>
+        <v>7174274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3242,7 +3242,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845346</v>
+        <v>128845365</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541373</v>
+        <v>541453</v>
       </c>
       <c r="R22" t="n">
-        <v>7174407</v>
+        <v>7174305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3322,12 +3322,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3354,7 +3349,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845360</v>
+        <v>128845346</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -3389,10 +3384,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541640</v>
+        <v>541373</v>
       </c>
       <c r="R23" t="n">
-        <v>7174274</v>
+        <v>7174407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,7 +3419,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3434,7 +3429,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845340</v>
+        <v>128845323</v>
       </c>
       <c r="B27" t="n">
-        <v>91517</v>
+        <v>98966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541062</v>
+        <v>541182</v>
       </c>
       <c r="R27" t="n">
-        <v>7174293</v>
+        <v>7174332</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,21 +3923,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3959,7 +3939,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845359</v>
+        <v>128845353</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3994,10 +3974,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541617</v>
+        <v>541612</v>
       </c>
       <c r="R28" t="n">
-        <v>7174319</v>
+        <v>7174586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4029,7 +4009,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4039,7 +4019,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4066,7 +4051,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845353</v>
+        <v>128845359</v>
       </c>
       <c r="B29" t="n">
         <v>79120</v>
@@ -4101,10 +4086,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541612</v>
+        <v>541617</v>
       </c>
       <c r="R29" t="n">
-        <v>7174586</v>
+        <v>7174319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4136,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4146,12 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845298</v>
+        <v>128845340</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,39 +4169,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541013</v>
+        <v>541062</v>
       </c>
       <c r="R30" t="n">
-        <v>7174346</v>
+        <v>7174293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,7 +4228,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4263,12 +4238,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4279,6 +4254,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4295,45 +4285,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845323</v>
+        <v>128845298</v>
       </c>
       <c r="B31" t="n">
-        <v>98959</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219880</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541182</v>
+        <v>541013</v>
       </c>
       <c r="R31" t="n">
-        <v>7174332</v>
+        <v>7174346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4365,7 +4360,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4375,7 +4370,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B33" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,42 +4530,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R33" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4597,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4607,12 +4599,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4639,10 +4626,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845293</v>
+        <v>128845332</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,39 +4637,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541157</v>
+        <v>541284</v>
       </c>
       <c r="R34" t="n">
-        <v>7174382</v>
+        <v>7174287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4714,7 +4696,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4724,12 +4706,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4740,6 +4722,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4756,45 +4753,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845332</v>
+        <v>128845275</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>92201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541284</v>
+        <v>541057</v>
       </c>
       <c r="R35" t="n">
-        <v>7174287</v>
+        <v>7174336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4850,6 +4850,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4883,10 +4884,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845341</v>
+        <v>128845297</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4894,34 +4895,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541131</v>
+        <v>541232</v>
       </c>
       <c r="R36" t="n">
-        <v>7174440</v>
+        <v>7174426</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4953,7 +4962,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4963,7 +4972,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4990,48 +5004,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845275</v>
+        <v>128845293</v>
       </c>
       <c r="B37" t="n">
-        <v>92196</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541057</v>
+        <v>541157</v>
       </c>
       <c r="R37" t="n">
-        <v>7174336</v>
+        <v>7174382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5063,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5073,12 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5087,24 +5103,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845339</v>
+        <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>91500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,37 +5132,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541139</v>
+        <v>541654</v>
       </c>
       <c r="R38" t="n">
-        <v>7174393</v>
+        <v>7174247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5194,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5204,12 +5201,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5218,7 +5215,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845327</v>
+        <v>128845339</v>
       </c>
       <c r="B39" t="n">
-        <v>91495</v>
+        <v>91522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,34 +5259,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541654</v>
+        <v>541139</v>
       </c>
       <c r="R39" t="n">
-        <v>7174247</v>
+        <v>7174393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5322,7 +5321,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5332,12 +5331,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5346,6 +5345,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B45" t="n">
-        <v>91495</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R45" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,12 +6026,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,21 +6037,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6287,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845357</v>
+        <v>128845290</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6298,34 +6278,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541607</v>
+        <v>541211</v>
       </c>
       <c r="R48" t="n">
-        <v>7174400</v>
+        <v>7174387</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6342,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6352,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6394,10 +6384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845290</v>
+        <v>128845326</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>91500</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6405,39 +6395,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541211</v>
+        <v>541626</v>
       </c>
       <c r="R49" t="n">
-        <v>7174387</v>
+        <v>7174307</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6469,7 +6454,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6479,12 +6464,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6495,6 +6480,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845289</v>
+        <v>128845335</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,39 +6522,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541254</v>
+        <v>541610</v>
       </c>
       <c r="R50" t="n">
-        <v>7174391</v>
+        <v>7174521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6586,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6596,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6612,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6628,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845291</v>
+        <v>128845383</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6639,39 +6649,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541147</v>
+        <v>541079</v>
       </c>
       <c r="R51" t="n">
-        <v>7174441</v>
+        <v>7174333</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6703,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6713,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,10 +6750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845335</v>
+        <v>128845385</v>
       </c>
       <c r="B52" t="n">
-        <v>91517</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6756,21 +6761,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6780,10 +6785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541610</v>
+        <v>541163</v>
       </c>
       <c r="R52" t="n">
-        <v>7174521</v>
+        <v>7174329</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6815,7 +6820,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6825,12 +6830,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6841,21 +6846,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6872,10 +6862,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845336</v>
+        <v>128845304</v>
       </c>
       <c r="B53" t="n">
-        <v>91517</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,21 +6873,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6907,10 +6897,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541251</v>
+        <v>541120</v>
       </c>
       <c r="R53" t="n">
-        <v>7174388</v>
+        <v>7174297</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6942,7 +6932,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6952,12 +6942,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6968,21 +6953,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6999,7 +6969,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845385</v>
+        <v>128845369</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -7034,10 +7004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541163</v>
+        <v>541285</v>
       </c>
       <c r="R54" t="n">
-        <v>7174329</v>
+        <v>7174269</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7069,7 +7039,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7079,12 +7049,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7223,10 +7188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845383</v>
+        <v>128845289</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7234,34 +7199,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541079</v>
+        <v>541254</v>
       </c>
       <c r="R56" t="n">
-        <v>7174333</v>
+        <v>7174391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7293,7 +7263,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7303,12 +7273,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7335,10 +7305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845304</v>
+        <v>128845291</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7346,34 +7316,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541120</v>
+        <v>541147</v>
       </c>
       <c r="R57" t="n">
-        <v>7174297</v>
+        <v>7174441</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7405,7 +7380,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7415,7 +7390,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7442,10 +7422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845369</v>
+        <v>128845336</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7453,21 +7433,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7477,10 +7457,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541285</v>
+        <v>541251</v>
       </c>
       <c r="R58" t="n">
-        <v>7174269</v>
+        <v>7174388</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7512,7 +7492,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7522,7 +7502,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7533,6 +7518,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7552,7 +7552,7 @@
         <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B60" t="n">
         <v>79120</v>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7783,7 +7783,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845354</v>
+        <v>128845373</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541618</v>
+        <v>541143</v>
       </c>
       <c r="R61" t="n">
-        <v>7174522</v>
+        <v>7174450</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7890,7 +7890,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845348</v>
+        <v>128845354</v>
       </c>
       <c r="B62" t="n">
         <v>79120</v>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541504</v>
+        <v>541618</v>
       </c>
       <c r="R62" t="n">
-        <v>7174451</v>
+        <v>7174522</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8117,7 +8117,7 @@
         <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845355</v>
+        <v>128845375</v>
       </c>
       <c r="B66" t="n">
         <v>79120</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R66" t="n">
-        <v>7174473</v>
+        <v>7174402</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,12 +8428,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8460,7 +8455,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845375</v>
+        <v>128845355</v>
       </c>
       <c r="B67" t="n">
         <v>79120</v>
@@ -8495,10 +8490,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R67" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8530,7 +8525,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8540,7 +8535,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845364</v>
+        <v>128845384</v>
       </c>
       <c r="B70" t="n">
         <v>79120</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541490</v>
+        <v>541112</v>
       </c>
       <c r="R70" t="n">
-        <v>7174268</v>
+        <v>7174350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8908,7 +8908,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128845351</v>
+        <v>128845364</v>
       </c>
       <c r="B71" t="n">
         <v>79120</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541563</v>
+        <v>541490</v>
       </c>
       <c r="R71" t="n">
-        <v>7174549</v>
+        <v>7174268</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8988,12 +8988,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9020,7 +9015,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845384</v>
+        <v>128845351</v>
       </c>
       <c r="B72" t="n">
         <v>79120</v>
@@ -9055,10 +9050,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541112</v>
+        <v>541563</v>
       </c>
       <c r="R72" t="n">
-        <v>7174350</v>
+        <v>7174549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9090,7 +9085,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9100,7 +9095,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9234,7 +9234,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845379</v>
+        <v>128845300</v>
       </c>
       <c r="B74" t="n">
         <v>79120</v>
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540962</v>
+        <v>541095</v>
       </c>
       <c r="R74" t="n">
-        <v>7174330</v>
+        <v>7174393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9314,12 +9314,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9346,7 +9341,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845300</v>
+        <v>128845379</v>
       </c>
       <c r="B75" t="n">
         <v>79120</v>
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541095</v>
+        <v>540962</v>
       </c>
       <c r="R75" t="n">
-        <v>7174393</v>
+        <v>7174330</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9416,7 +9411,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9426,7 +9421,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128845377</v>
+        <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541055</v>
+        <v>541616</v>
       </c>
       <c r="R76" t="n">
-        <v>7174298</v>
+        <v>7174449</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9533,7 +9533,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På stående levande gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9544,6 +9549,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9667,32 +9687,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845271</v>
+        <v>128845377</v>
       </c>
       <c r="B78" t="n">
-        <v>92196</v>
+        <v>79120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9702,10 +9722,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541616</v>
+        <v>541055</v>
       </c>
       <c r="R78" t="n">
-        <v>7174449</v>
+        <v>7174298</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9737,7 +9757,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9747,12 +9767,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På stående levande gran</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9763,21 +9778,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B79" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,46 +9805,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R79" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9876,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9886,12 +9874,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9918,10 +9901,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B80" t="n">
-        <v>91495</v>
+        <v>57876</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9929,34 +9912,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R80" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9988,7 +9983,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9998,12 +9993,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10014,21 +10009,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10045,10 +10025,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10056,21 +10036,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10080,10 +10060,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R81" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10115,7 +10095,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10125,12 +10105,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10141,6 +10121,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10157,7 +10152,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845371</v>
+        <v>128845380</v>
       </c>
       <c r="B82" t="n">
         <v>79120</v>
@@ -10192,10 +10187,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541216</v>
+        <v>541027</v>
       </c>
       <c r="R82" t="n">
-        <v>7174399</v>
+        <v>7174356</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10227,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10237,7 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10264,32 +10264,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128845352</v>
+        <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541591</v>
+        <v>541329</v>
       </c>
       <c r="R83" t="n">
-        <v>7174563</v>
+        <v>7174232</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10344,7 +10344,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10355,6 +10360,21 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10590,32 +10610,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845273</v>
+        <v>128845352</v>
       </c>
       <c r="B86" t="n">
-        <v>92196</v>
+        <v>79120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10625,10 +10645,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541329</v>
+        <v>541591</v>
       </c>
       <c r="R86" t="n">
-        <v>7174232</v>
+        <v>7174563</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10660,7 +10680,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10670,12 +10690,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10686,21 +10701,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845344</v>
+        <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541312</v>
+        <v>541629</v>
       </c>
       <c r="R87" t="n">
-        <v>7174300</v>
+        <v>7174402</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,7 +10797,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10808,6 +10813,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10824,45 +10844,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845272</v>
+        <v>128845278</v>
       </c>
       <c r="B88" t="n">
-        <v>92196</v>
+        <v>57716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541629</v>
+        <v>541418</v>
       </c>
       <c r="R88" t="n">
-        <v>7174402</v>
+        <v>7174396</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10894,7 +10919,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10904,12 +10929,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10920,21 +10945,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10951,7 +10961,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845281</v>
       </c>
       <c r="B89" t="n">
         <v>57716</v>
@@ -10982,7 +10992,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10991,10 +11001,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541599</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174544</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11036,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11046,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11068,7 +11078,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B90" t="n">
         <v>57716</v>
@@ -11108,10 +11118,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R90" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11143,7 +11153,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11153,7 +11163,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -11185,10 +11195,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845276</v>
+        <v>128845344</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11196,39 +11206,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541274</v>
+        <v>541312</v>
       </c>
       <c r="R91" t="n">
-        <v>7174268</v>
+        <v>7174300</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11265,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,12 +11275,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11302,45 +11302,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845338</v>
+        <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>91517</v>
+        <v>92201</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541232</v>
+        <v>541116</v>
       </c>
       <c r="R92" t="n">
-        <v>7174426</v>
+        <v>7174272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11372,7 +11375,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11382,12 +11385,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11396,6 +11399,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11432,7 +11436,7 @@
         <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11556,48 +11560,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845274</v>
+        <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>92196</v>
+        <v>91522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541116</v>
+        <v>541232</v>
       </c>
       <c r="R94" t="n">
-        <v>7174272</v>
+        <v>7174426</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11629,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11639,12 +11640,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11653,7 +11654,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11807,7 +11807,7 @@
         <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11931,10 +11931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845288</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11942,39 +11942,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541261</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174398</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12006,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12016,12 +12011,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12048,10 +12043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845285</v>
+        <v>128845382</v>
       </c>
       <c r="B98" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12059,39 +12054,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541640</v>
+        <v>541041</v>
       </c>
       <c r="R98" t="n">
-        <v>7174353</v>
+        <v>7174348</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12123,7 +12113,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12133,12 +12123,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12165,10 +12150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845370</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12176,34 +12161,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541222</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174409</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12235,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12245,12 +12235,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12277,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845382</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12288,34 +12278,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541041</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174348</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12347,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12357,7 +12352,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91517</v>
+        <v>91500</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R105" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91495</v>
+        <v>91522</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R106" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13076,7 +13076,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845345</v>
+        <v>128845366</v>
       </c>
       <c r="B107" t="n">
         <v>79120</v>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541348</v>
+        <v>541398</v>
       </c>
       <c r="R107" t="n">
-        <v>7174394</v>
+        <v>7174337</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,12 +13156,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13188,7 +13183,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845366</v>
+        <v>128845350</v>
       </c>
       <c r="B108" t="n">
         <v>79120</v>
@@ -13223,10 +13218,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541398</v>
+        <v>541554</v>
       </c>
       <c r="R108" t="n">
-        <v>7174337</v>
+        <v>7174535</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13258,7 +13253,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13268,7 +13263,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845350</v>
+        <v>128845349</v>
       </c>
       <c r="B109" t="n">
         <v>79120</v>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541554</v>
+        <v>541462</v>
       </c>
       <c r="R109" t="n">
-        <v>7174535</v>
+        <v>7174528</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,12 +13375,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13407,7 +13402,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845349</v>
+        <v>128845345</v>
       </c>
       <c r="B110" t="n">
         <v>79120</v>
@@ -13442,10 +13437,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541462</v>
+        <v>541348</v>
       </c>
       <c r="R110" t="n">
-        <v>7174528</v>
+        <v>7174394</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13477,7 +13472,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13487,7 +13482,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845286</v>
+        <v>128845325</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>91500</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,39 +2775,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541617</v>
+        <v>541618</v>
       </c>
       <c r="R18" t="n">
-        <v>7174320</v>
+        <v>7174399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2834,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,12 +2844,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2865,6 +2860,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2881,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>91500</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2892,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2951,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,12 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,21 +2992,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845328</v>
+        <v>128845360</v>
       </c>
       <c r="B20" t="n">
-        <v>91500</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541428</v>
+        <v>541640</v>
       </c>
       <c r="R20" t="n">
-        <v>7174314</v>
+        <v>7174274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3088,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3104,21 +3099,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3135,7 +3115,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845360</v>
+        <v>128845365</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -3170,10 +3150,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541640</v>
+        <v>541453</v>
       </c>
       <c r="R21" t="n">
-        <v>7174274</v>
+        <v>7174305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3185,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,7 +3195,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3242,7 +3222,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845365</v>
+        <v>128845346</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -3277,10 +3257,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541453</v>
+        <v>541373</v>
       </c>
       <c r="R22" t="n">
-        <v>7174305</v>
+        <v>7174407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3312,7 +3292,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3322,7 +3302,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3349,32 +3334,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845346</v>
+        <v>128845296</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3384,10 +3369,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541373</v>
+        <v>541359</v>
       </c>
       <c r="R23" t="n">
-        <v>7174407</v>
+        <v>7174394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3419,7 +3404,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3429,12 +3414,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,6 +3430,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845296</v>
+        <v>128845322</v>
       </c>
       <c r="B24" t="n">
-        <v>80254</v>
+        <v>80261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541359</v>
+        <v>541579</v>
       </c>
       <c r="R24" t="n">
-        <v>7174394</v>
+        <v>7174417</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3588,45 +3588,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845322</v>
+        <v>128845280</v>
       </c>
       <c r="B25" t="n">
-        <v>80261</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541579</v>
+        <v>541574</v>
       </c>
       <c r="R25" t="n">
-        <v>7174417</v>
+        <v>7174569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3658,7 +3663,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3668,12 +3673,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,21 +3689,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,10 +3705,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845280</v>
+        <v>128845328</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>91500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,39 +3716,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541574</v>
+        <v>541428</v>
       </c>
       <c r="R26" t="n">
-        <v>7174569</v>
+        <v>7174314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3775,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3785,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3816,6 +3801,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845323</v>
+        <v>128845340</v>
       </c>
       <c r="B27" t="n">
-        <v>98966</v>
+        <v>91522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541182</v>
+        <v>541062</v>
       </c>
       <c r="R27" t="n">
-        <v>7174332</v>
+        <v>7174293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3923,6 +3928,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4158,10 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,34 +4189,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R30" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4228,7 +4253,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4238,12 +4263,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,21 +4279,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4285,50 +4295,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845298</v>
+        <v>128845323</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>98966</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541013</v>
+        <v>541182</v>
       </c>
       <c r="R31" t="n">
-        <v>7174346</v>
+        <v>7174332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4360,7 +4365,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4370,12 +4375,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845341</v>
+        <v>128845332</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541131</v>
+        <v>541284</v>
       </c>
       <c r="R33" t="n">
-        <v>7174440</v>
+        <v>7174287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,7 +4599,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4610,6 +4615,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4626,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B34" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,21 +4657,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4661,10 +4681,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R34" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4696,7 +4716,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4706,12 +4726,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4722,21 +4737,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4753,48 +4753,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845275</v>
+        <v>128845293</v>
       </c>
       <c r="B35" t="n">
-        <v>92201</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541057</v>
+        <v>541157</v>
       </c>
       <c r="R35" t="n">
-        <v>7174336</v>
+        <v>7174382</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4826,7 +4828,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4836,12 +4838,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4850,24 +4852,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4884,42 +4870,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845297</v>
+        <v>128845275</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>92201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4927,10 +4908,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541232</v>
+        <v>541057</v>
       </c>
       <c r="R36" t="n">
-        <v>7174426</v>
+        <v>7174336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4962,7 +4943,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4972,12 +4953,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4986,8 +4967,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5004,10 +5001,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845293</v>
+        <v>128845297</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5015,16 +5012,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5033,21 +5030,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541157</v>
+        <v>541232</v>
       </c>
       <c r="R37" t="n">
-        <v>7174382</v>
+        <v>7174426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845339</v>
+        <v>128845283</v>
       </c>
       <c r="B39" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,37 +5259,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541139</v>
+        <v>541605</v>
       </c>
       <c r="R39" t="n">
-        <v>7174393</v>
+        <v>7174433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5321,7 +5323,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5331,12 +5333,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5345,24 +5347,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,10 +5365,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845362</v>
+        <v>128845295</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5390,34 +5376,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R40" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5449,7 +5447,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5459,7 +5457,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5486,10 +5489,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845367</v>
+        <v>128845339</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5497,34 +5500,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541394</v>
+        <v>541139</v>
       </c>
       <c r="R41" t="n">
-        <v>7174344</v>
+        <v>7174393</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5556,7 +5562,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5566,12 +5572,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5580,8 +5586,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5598,7 +5620,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845361</v>
+        <v>128845362</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -5633,10 +5655,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541658</v>
+        <v>541644</v>
       </c>
       <c r="R42" t="n">
-        <v>7174215</v>
+        <v>7174158</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5668,7 +5690,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5678,7 +5700,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5705,10 +5727,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845283</v>
+        <v>128845367</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,39 +5738,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541605</v>
+        <v>541394</v>
       </c>
       <c r="R43" t="n">
-        <v>7174433</v>
+        <v>7174344</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5780,7 +5797,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,12 +5807,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5822,10 +5839,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845295</v>
+        <v>128845361</v>
       </c>
       <c r="B44" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5833,46 +5850,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R44" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5909,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5919,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845290</v>
+        <v>128845326</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>91500</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6278,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541211</v>
+        <v>541626</v>
       </c>
       <c r="R48" t="n">
-        <v>7174387</v>
+        <v>7174307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6342,7 +6337,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6352,12 +6347,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6368,6 +6363,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6384,10 +6394,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845326</v>
+        <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>91500</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,34 +6405,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541626</v>
+        <v>541211</v>
       </c>
       <c r="R49" t="n">
-        <v>7174307</v>
+        <v>7174387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6454,7 +6469,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6464,12 +6479,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6480,21 +6495,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845335</v>
+        <v>128845383</v>
       </c>
       <c r="B50" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541610</v>
+        <v>541079</v>
       </c>
       <c r="R50" t="n">
-        <v>7174521</v>
+        <v>7174333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,21 +6607,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6638,7 +6623,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845383</v>
+        <v>128845385</v>
       </c>
       <c r="B51" t="n">
         <v>79120</v>
@@ -6673,10 +6658,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541079</v>
+        <v>541163</v>
       </c>
       <c r="R51" t="n">
-        <v>7174333</v>
+        <v>7174329</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6693,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,7 +6703,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6750,7 +6735,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845385</v>
+        <v>128845304</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -6785,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541163</v>
+        <v>541120</v>
       </c>
       <c r="R52" t="n">
-        <v>7174329</v>
+        <v>7174297</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6820,7 +6805,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6830,12 +6815,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6862,7 +6842,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845304</v>
+        <v>128845369</v>
       </c>
       <c r="B53" t="n">
         <v>79120</v>
@@ -6897,10 +6877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541120</v>
+        <v>541285</v>
       </c>
       <c r="R53" t="n">
-        <v>7174297</v>
+        <v>7174269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6912,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6942,7 +6922,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6969,7 +6949,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845369</v>
+        <v>128845381</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -7004,10 +6984,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541285</v>
+        <v>541025</v>
       </c>
       <c r="R54" t="n">
-        <v>7174269</v>
+        <v>7174364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7039,7 +7019,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7049,7 +7029,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7076,10 +7061,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845381</v>
+        <v>128845335</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7087,21 +7072,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7111,10 +7096,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541025</v>
+        <v>541610</v>
       </c>
       <c r="R55" t="n">
-        <v>7174364</v>
+        <v>7174521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7146,7 +7131,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7156,12 +7141,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7172,6 +7157,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7188,10 +7188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845289</v>
+        <v>128845336</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7199,39 +7199,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541254</v>
+        <v>541251</v>
       </c>
       <c r="R56" t="n">
-        <v>7174391</v>
+        <v>7174388</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7263,7 +7258,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7273,12 +7268,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7289,6 +7284,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7305,7 +7315,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845291</v>
+        <v>128845289</v>
       </c>
       <c r="B57" t="n">
         <v>57716</v>
@@ -7345,10 +7355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541147</v>
+        <v>541254</v>
       </c>
       <c r="R57" t="n">
-        <v>7174441</v>
+        <v>7174391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7380,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7390,7 +7400,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7422,10 +7432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845336</v>
+        <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7433,34 +7443,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541251</v>
+        <v>541147</v>
       </c>
       <c r="R58" t="n">
-        <v>7174388</v>
+        <v>7174441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7492,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7502,12 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7518,21 +7533,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7676,7 +7676,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845348</v>
+        <v>128845373</v>
       </c>
       <c r="B60" t="n">
         <v>79120</v>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541504</v>
+        <v>541143</v>
       </c>
       <c r="R60" t="n">
-        <v>7174451</v>
+        <v>7174450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7783,7 +7783,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R61" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845324</v>
+        <v>128845378</v>
       </c>
       <c r="B64" t="n">
-        <v>91500</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541610</v>
+        <v>541032</v>
       </c>
       <c r="R64" t="n">
-        <v>7174586</v>
+        <v>7174308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,12 +8194,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8210,21 +8205,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8241,7 +8221,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845378</v>
+        <v>128845375</v>
       </c>
       <c r="B65" t="n">
         <v>79120</v>
@@ -8276,10 +8256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541032</v>
+        <v>541136</v>
       </c>
       <c r="R65" t="n">
-        <v>7174308</v>
+        <v>7174402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8311,7 +8291,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8321,7 +8301,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8348,7 +8328,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845375</v>
+        <v>128845355</v>
       </c>
       <c r="B66" t="n">
         <v>79120</v>
@@ -8383,10 +8363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R66" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8398,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,7 +8408,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8455,10 +8440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845355</v>
+        <v>128845324</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8466,21 +8451,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8490,10 +8475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R67" t="n">
-        <v>7174473</v>
+        <v>7174586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8525,7 +8510,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8535,12 +8520,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8551,6 +8536,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8567,7 +8567,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845282</v>
+        <v>128845284</v>
       </c>
       <c r="B68" t="n">
         <v>57716</v>
@@ -8610,7 +8610,7 @@
         <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8684,7 +8684,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845284</v>
+        <v>128845282</v>
       </c>
       <c r="B69" t="n">
         <v>57716</v>
@@ -8727,7 +8727,7 @@
         <v>541637</v>
       </c>
       <c r="R69" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128845271</v>
+        <v>128845372</v>
       </c>
       <c r="B76" t="n">
-        <v>92201</v>
+        <v>79120</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541616</v>
+        <v>541206</v>
       </c>
       <c r="R76" t="n">
-        <v>7174449</v>
+        <v>7174374</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9533,12 +9533,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På stående levande gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9549,21 +9544,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9580,7 +9560,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845372</v>
+        <v>128845377</v>
       </c>
       <c r="B77" t="n">
         <v>79120</v>
@@ -9615,10 +9595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541206</v>
+        <v>541055</v>
       </c>
       <c r="R77" t="n">
-        <v>7174374</v>
+        <v>7174298</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9650,7 +9630,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9660,7 +9640,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9687,32 +9667,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845377</v>
+        <v>128845271</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9722,10 +9702,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541055</v>
+        <v>541616</v>
       </c>
       <c r="R78" t="n">
-        <v>7174298</v>
+        <v>7174449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9757,7 +9737,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9767,7 +9747,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På stående levande gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9778,6 +9763,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9794,7 +9794,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845371</v>
+        <v>128845380</v>
       </c>
       <c r="B79" t="n">
         <v>79120</v>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541216</v>
+        <v>541027</v>
       </c>
       <c r="R79" t="n">
-        <v>7174399</v>
+        <v>7174356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,7 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9901,10 +9906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B80" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9912,46 +9917,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R80" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9983,7 +9976,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9993,12 +9986,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10025,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B81" t="n">
-        <v>91500</v>
+        <v>57876</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10036,34 +10024,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10121,21 +10121,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10152,10 +10137,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B82" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10163,21 +10148,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10187,10 +10172,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R82" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10207,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10217,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10248,6 +10233,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10391,7 +10391,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128845347</v>
+        <v>128845352</v>
       </c>
       <c r="B84" t="n">
         <v>79120</v>
@@ -10426,10 +10426,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541411</v>
+        <v>541591</v>
       </c>
       <c r="R84" t="n">
-        <v>7174397</v>
+        <v>7174563</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10471,12 +10471,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10503,7 +10498,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845302</v>
+        <v>128845347</v>
       </c>
       <c r="B85" t="n">
         <v>79120</v>
@@ -10538,10 +10533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541089</v>
+        <v>541411</v>
       </c>
       <c r="R85" t="n">
-        <v>7174431</v>
+        <v>7174397</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10573,7 +10568,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10583,7 +10578,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10610,7 +10610,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845352</v>
+        <v>128845302</v>
       </c>
       <c r="B86" t="n">
         <v>79120</v>
@@ -10645,10 +10645,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541591</v>
+        <v>541089</v>
       </c>
       <c r="R86" t="n">
-        <v>7174563</v>
+        <v>7174431</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10844,10 +10844,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845344</v>
       </c>
       <c r="B88" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10855,39 +10855,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541312</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10919,7 +10914,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10929,12 +10924,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10961,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845281</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
         <v>57716</v>
@@ -10992,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11001,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541599</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174544</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11036,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11046,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11195,10 +11185,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845344</v>
+        <v>128845281</v>
       </c>
       <c r="B91" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11206,34 +11196,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541312</v>
+        <v>541599</v>
       </c>
       <c r="R91" t="n">
-        <v>7174300</v>
+        <v>7174544</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11265,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11275,7 +11270,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845338</v>
+        <v>128845287</v>
       </c>
       <c r="B94" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11571,34 +11571,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541232</v>
+        <v>541428</v>
       </c>
       <c r="R94" t="n">
-        <v>7174426</v>
+        <v>7174314</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11630,7 +11635,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11640,12 +11645,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11656,21 +11661,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11687,10 +11677,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845287</v>
+        <v>128845338</v>
       </c>
       <c r="B95" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11698,39 +11688,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541428</v>
+        <v>541232</v>
       </c>
       <c r="R95" t="n">
-        <v>7174314</v>
+        <v>7174426</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11762,7 +11747,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11772,12 +11757,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11788,6 +11773,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845331</v>
+        <v>128845370</v>
       </c>
       <c r="B96" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541271</v>
+        <v>541222</v>
       </c>
       <c r="R96" t="n">
-        <v>7174269</v>
+        <v>7174409</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,21 +11900,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11931,7 +11916,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
         <v>79120</v>
@@ -11966,10 +11951,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +11986,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,12 +11996,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12043,10 +12023,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845382</v>
+        <v>128845331</v>
       </c>
       <c r="B98" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12054,21 +12034,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12078,10 +12058,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541041</v>
+        <v>541271</v>
       </c>
       <c r="R98" t="n">
-        <v>7174348</v>
+        <v>7174269</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12113,7 +12093,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12123,7 +12103,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12134,6 +12119,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12150,7 +12150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
         <v>57716</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,7 +12267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B100" t="n">
         <v>57716</v>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R100" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845343</v>
+        <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,34 +12395,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541074</v>
+        <v>541322</v>
       </c>
       <c r="R101" t="n">
-        <v>7174298</v>
+        <v>7174361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,7 +12501,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845269</v>
+        <v>128845343</v>
       </c>
       <c r="B102" t="n">
         <v>79120</v>
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541134</v>
+        <v>541074</v>
       </c>
       <c r="R102" t="n">
-        <v>7174353</v>
+        <v>7174298</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12571,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12581,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,7 +12608,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845376</v>
+        <v>128845269</v>
       </c>
       <c r="B103" t="n">
         <v>79120</v>
@@ -12633,10 +12643,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541109</v>
+        <v>541134</v>
       </c>
       <c r="R103" t="n">
-        <v>7174267</v>
+        <v>7174353</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12678,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12688,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12705,10 +12715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845277</v>
+        <v>128845376</v>
       </c>
       <c r="B104" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12716,39 +12726,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541322</v>
+        <v>541109</v>
       </c>
       <c r="R104" t="n">
-        <v>7174361</v>
+        <v>7174267</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12790,12 +12795,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13512,6 +13512,2063 @@
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128845318</v>
+      </c>
+      <c r="B111" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>541072</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7174294</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128845314</v>
+      </c>
+      <c r="B112" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>541139</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7174373</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128845306</v>
+      </c>
+      <c r="B113" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>541120</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7174297</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128845308</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>541477</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7174417</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128845317</v>
+      </c>
+      <c r="B115" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>541122</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7174274</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128845301</v>
+      </c>
+      <c r="B116" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>541095</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7174393</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128845316</v>
+      </c>
+      <c r="B117" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>541116</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7174329</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128845310</v>
+      </c>
+      <c r="B118" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>541311</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7174260</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128845303</v>
+      </c>
+      <c r="B119" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>541089</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7174431</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128845315</v>
+      </c>
+      <c r="B120" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>541125</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7174337</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128845307</v>
+      </c>
+      <c r="B121" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>541291</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7174294</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128845311</v>
+      </c>
+      <c r="B122" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>541243</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7174412</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128845319</v>
+      </c>
+      <c r="B123" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>541045</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7174303</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128845313</v>
+      </c>
+      <c r="B124" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>541147</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7174347</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128845320</v>
+      </c>
+      <c r="B125" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>541019</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7174311</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>3 ledknutar lite luden bladbas</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128845309</v>
+      </c>
+      <c r="B126" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>541406</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7174317</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128845299</v>
+      </c>
+      <c r="B127" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>541152</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7174446</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128845312</v>
+      </c>
+      <c r="B128" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>541164</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7174343</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128845321</v>
+      </c>
+      <c r="B129" t="n">
+        <v>99891</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Granberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>541268</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7174406</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845360</v>
+        <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541640</v>
+        <v>541428</v>
       </c>
       <c r="R20" t="n">
-        <v>7174274</v>
+        <v>7174314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,7 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,6 +3104,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3115,7 +3135,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845365</v>
+        <v>128845360</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -3150,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541453</v>
+        <v>541640</v>
       </c>
       <c r="R21" t="n">
-        <v>7174305</v>
+        <v>7174274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3185,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3195,7 +3215,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3222,7 +3242,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845346</v>
+        <v>128845365</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -3257,10 +3277,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541373</v>
+        <v>541453</v>
       </c>
       <c r="R22" t="n">
-        <v>7174407</v>
+        <v>7174305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3292,7 +3312,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3302,12 +3322,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3334,32 +3349,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845296</v>
+        <v>128845346</v>
       </c>
       <c r="B23" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3369,10 +3384,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541359</v>
+        <v>541373</v>
       </c>
       <c r="R23" t="n">
-        <v>7174394</v>
+        <v>7174407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3404,7 +3419,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3414,12 +3429,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,21 +3445,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845322</v>
+        <v>128845296</v>
       </c>
       <c r="B24" t="n">
-        <v>80261</v>
+        <v>80254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541579</v>
+        <v>541359</v>
       </c>
       <c r="R24" t="n">
-        <v>7174417</v>
+        <v>7174394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3588,50 +3588,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845280</v>
+        <v>128845322</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>80261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541574</v>
+        <v>541579</v>
       </c>
       <c r="R25" t="n">
-        <v>7174569</v>
+        <v>7174417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3663,7 +3658,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3673,12 +3668,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3689,6 +3684,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3705,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845328</v>
+        <v>128845280</v>
       </c>
       <c r="B26" t="n">
-        <v>91500</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3716,34 +3726,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541428</v>
+        <v>541574</v>
       </c>
       <c r="R26" t="n">
-        <v>7174314</v>
+        <v>7174569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -4295,45 +4295,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845323</v>
+        <v>128845279</v>
       </c>
       <c r="B31" t="n">
-        <v>98966</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541182</v>
+        <v>541504</v>
       </c>
       <c r="R31" t="n">
-        <v>7174332</v>
+        <v>7174451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4365,7 +4370,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4375,7 +4380,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4402,50 +4412,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>98966</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R32" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4477,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,12 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4519,45 +4519,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845332</v>
+        <v>128845275</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>92201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541284</v>
+        <v>541057</v>
       </c>
       <c r="R33" t="n">
-        <v>7174287</v>
+        <v>7174336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,12 +4602,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4613,6 +4616,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4646,10 +4650,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845341</v>
+        <v>128845332</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,21 +4661,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4681,10 +4685,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541131</v>
+        <v>541284</v>
       </c>
       <c r="R34" t="n">
-        <v>7174440</v>
+        <v>7174287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4716,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4726,7 +4730,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4737,6 +4746,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4870,48 +4894,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845275</v>
+        <v>128845341</v>
       </c>
       <c r="B36" t="n">
-        <v>92201</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541057</v>
+        <v>541131</v>
       </c>
       <c r="R36" t="n">
-        <v>7174336</v>
+        <v>7174440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4943,7 +4964,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4953,12 +4974,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4967,24 +4983,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845327</v>
+        <v>128845339</v>
       </c>
       <c r="B38" t="n">
-        <v>91500</v>
+        <v>91522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,34 +5132,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541654</v>
+        <v>541139</v>
       </c>
       <c r="R38" t="n">
-        <v>7174247</v>
+        <v>7174393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5194,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5204,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5215,6 +5218,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5248,10 +5252,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845283</v>
+        <v>128845362</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,39 +5263,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541605</v>
+        <v>541644</v>
       </c>
       <c r="R39" t="n">
-        <v>7174433</v>
+        <v>7174158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5323,7 +5322,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5333,12 +5332,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5365,10 +5359,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845295</v>
+        <v>128845367</v>
       </c>
       <c r="B40" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,36 +5370,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -5447,7 +5429,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5457,12 +5439,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5489,10 +5471,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845339</v>
+        <v>128845361</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5500,37 +5482,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541139</v>
+        <v>541658</v>
       </c>
       <c r="R41" t="n">
-        <v>7174393</v>
+        <v>7174215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5562,7 +5541,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5572,12 +5551,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5586,24 +5560,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5620,10 +5578,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845362</v>
+        <v>128845295</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5631,34 +5589,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5690,7 +5660,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5700,7 +5670,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5727,10 +5702,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845367</v>
+        <v>128845327</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5738,21 +5713,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5762,10 +5737,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541394</v>
+        <v>541654</v>
       </c>
       <c r="R43" t="n">
-        <v>7174344</v>
+        <v>7174247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5797,7 +5772,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5807,12 +5782,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5823,6 +5798,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5839,10 +5829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845361</v>
+        <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5850,34 +5840,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541658</v>
+        <v>541605</v>
       </c>
       <c r="R44" t="n">
-        <v>7174215</v>
+        <v>7174433</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5919,7 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845383</v>
+        <v>128845335</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541079</v>
+        <v>541610</v>
       </c>
       <c r="R50" t="n">
-        <v>7174333</v>
+        <v>7174521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6623,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845385</v>
+        <v>128845336</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,21 +6649,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6658,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541163</v>
+        <v>541251</v>
       </c>
       <c r="R51" t="n">
-        <v>7174329</v>
+        <v>7174388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6719,6 +6734,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6735,7 +6765,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845304</v>
+        <v>128845383</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -6770,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541120</v>
+        <v>541079</v>
       </c>
       <c r="R52" t="n">
-        <v>7174297</v>
+        <v>7174333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6815,7 +6845,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6842,7 +6877,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845369</v>
+        <v>128845385</v>
       </c>
       <c r="B53" t="n">
         <v>79120</v>
@@ -6877,10 +6912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541285</v>
+        <v>541163</v>
       </c>
       <c r="R53" t="n">
-        <v>7174269</v>
+        <v>7174329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6912,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6922,7 +6957,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6949,7 +6989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845381</v>
+        <v>128845304</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -6984,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541025</v>
+        <v>541120</v>
       </c>
       <c r="R54" t="n">
-        <v>7174364</v>
+        <v>7174297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7019,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7029,12 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7061,10 +7096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845335</v>
+        <v>128845369</v>
       </c>
       <c r="B55" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7072,21 +7107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7096,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541610</v>
+        <v>541285</v>
       </c>
       <c r="R55" t="n">
-        <v>7174521</v>
+        <v>7174269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7131,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7141,12 +7176,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7157,21 +7187,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7188,10 +7203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845336</v>
+        <v>128845381</v>
       </c>
       <c r="B56" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7199,21 +7214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7223,10 +7238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541251</v>
+        <v>541025</v>
       </c>
       <c r="R56" t="n">
-        <v>7174388</v>
+        <v>7174364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7258,7 +7273,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7268,12 +7283,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7284,21 +7299,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7676,10 +7676,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845292</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,34 +7687,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541140</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7746,7 +7751,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7756,7 +7761,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7890,7 +7900,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845354</v>
+        <v>128845373</v>
       </c>
       <c r="B62" t="n">
         <v>79120</v>
@@ -7925,10 +7935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541618</v>
+        <v>541143</v>
       </c>
       <c r="R62" t="n">
-        <v>7174522</v>
+        <v>7174450</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7960,7 +7970,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7970,7 +7980,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7997,10 +8007,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845292</v>
+        <v>128845354</v>
       </c>
       <c r="B63" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8008,39 +8018,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541140</v>
+        <v>541618</v>
       </c>
       <c r="R63" t="n">
-        <v>7174441</v>
+        <v>7174522</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8082,12 +8087,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845378</v>
+        <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541032</v>
+        <v>541610</v>
       </c>
       <c r="R64" t="n">
-        <v>7174308</v>
+        <v>7174586</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,7 +8194,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8205,6 +8210,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8221,7 +8241,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845375</v>
+        <v>128845378</v>
       </c>
       <c r="B65" t="n">
         <v>79120</v>
@@ -8256,10 +8276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541136</v>
+        <v>541032</v>
       </c>
       <c r="R65" t="n">
-        <v>7174402</v>
+        <v>7174308</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8291,7 +8311,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8301,7 +8321,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8328,7 +8348,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845355</v>
+        <v>128845375</v>
       </c>
       <c r="B66" t="n">
         <v>79120</v>
@@ -8363,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R66" t="n">
-        <v>7174473</v>
+        <v>7174402</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8398,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8408,12 +8428,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8440,10 +8455,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845324</v>
+        <v>128845355</v>
       </c>
       <c r="B67" t="n">
-        <v>91500</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8451,21 +8466,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8475,10 +8490,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R67" t="n">
-        <v>7174586</v>
+        <v>7174473</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8510,7 +8525,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8520,12 +8535,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8536,21 +8551,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128845372</v>
+        <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541206</v>
+        <v>541616</v>
       </c>
       <c r="R76" t="n">
-        <v>7174374</v>
+        <v>7174449</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9533,7 +9533,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På stående levande gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9544,6 +9549,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9560,7 +9580,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845377</v>
+        <v>128845372</v>
       </c>
       <c r="B77" t="n">
         <v>79120</v>
@@ -9595,10 +9615,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541055</v>
+        <v>541206</v>
       </c>
       <c r="R77" t="n">
-        <v>7174298</v>
+        <v>7174374</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9630,7 +9650,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9640,7 +9660,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9667,32 +9687,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845271</v>
+        <v>128845377</v>
       </c>
       <c r="B78" t="n">
-        <v>92201</v>
+        <v>79120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9702,10 +9722,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541616</v>
+        <v>541055</v>
       </c>
       <c r="R78" t="n">
-        <v>7174449</v>
+        <v>7174298</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9737,7 +9757,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9747,12 +9767,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På stående levande gran</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9763,21 +9778,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,21 +9805,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,6 +9890,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9906,7 +9921,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845380</v>
       </c>
       <c r="B80" t="n">
         <v>79120</v>
@@ -9941,10 +9956,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541027</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9976,7 +9991,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9986,7 +10001,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10013,10 +10033,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B81" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,46 +10044,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R81" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10095,7 +10103,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10105,12 +10113,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10137,10 +10140,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B82" t="n">
-        <v>91500</v>
+        <v>57876</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10148,34 +10151,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R82" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10207,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10217,12 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10233,21 +10248,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845272</v>
+        <v>128845344</v>
       </c>
       <c r="B87" t="n">
-        <v>92201</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541629</v>
+        <v>541312</v>
       </c>
       <c r="R87" t="n">
-        <v>7174402</v>
+        <v>7174300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,12 +10797,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10813,21 +10808,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10844,10 +10824,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845344</v>
+        <v>128845278</v>
       </c>
       <c r="B88" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10855,34 +10835,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541312</v>
+        <v>541418</v>
       </c>
       <c r="R88" t="n">
-        <v>7174300</v>
+        <v>7174396</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10914,7 +10899,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10924,7 +10909,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10951,50 +10941,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B89" t="n">
-        <v>57716</v>
+        <v>92201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11011,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11021,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11052,6 +11037,21 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845287</v>
+        <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11571,39 +11571,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541428</v>
+        <v>541232</v>
       </c>
       <c r="R94" t="n">
-        <v>7174314</v>
+        <v>7174426</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11635,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11645,12 +11640,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11661,6 +11656,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11677,10 +11687,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845338</v>
+        <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11688,34 +11698,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541232</v>
+        <v>541428</v>
       </c>
       <c r="R95" t="n">
-        <v>7174426</v>
+        <v>7174314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,7 +11762,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11757,12 +11772,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11773,21 +11788,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845370</v>
+        <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541222</v>
+        <v>541271</v>
       </c>
       <c r="R96" t="n">
-        <v>7174409</v>
+        <v>7174269</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,6 +11900,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11916,7 +11931,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
         <v>79120</v>
@@ -11951,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11986,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11996,7 +12011,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12023,10 +12043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845331</v>
+        <v>128845382</v>
       </c>
       <c r="B98" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12034,21 +12054,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12058,10 +12078,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541271</v>
+        <v>541041</v>
       </c>
       <c r="R98" t="n">
-        <v>7174269</v>
+        <v>7174348</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12093,7 +12113,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12103,12 +12123,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12119,21 +12134,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845277</v>
+        <v>128845343</v>
       </c>
       <c r="B101" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,39 +12395,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541322</v>
+        <v>541074</v>
       </c>
       <c r="R101" t="n">
-        <v>7174361</v>
+        <v>7174298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12459,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12469,12 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12501,7 +12491,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B102" t="n">
         <v>79120</v>
@@ -12536,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R102" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12571,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12581,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12608,7 +12598,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845269</v>
+        <v>128845376</v>
       </c>
       <c r="B103" t="n">
         <v>79120</v>
@@ -12643,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541134</v>
+        <v>541109</v>
       </c>
       <c r="R103" t="n">
-        <v>7174353</v>
+        <v>7174267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12678,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12688,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12715,10 +12705,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845376</v>
+        <v>128845277</v>
       </c>
       <c r="B104" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,34 +12716,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541109</v>
+        <v>541322</v>
       </c>
       <c r="R104" t="n">
-        <v>7174267</v>
+        <v>7174361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12785,7 +12780,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12795,7 +12790,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13730,7 +13730,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128845306</v>
+        <v>128845308</v>
       </c>
       <c r="B113" t="n">
         <v>99891</v>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>541120</v>
+        <v>541477</v>
       </c>
       <c r="R113" t="n">
-        <v>7174297</v>
+        <v>7174417</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13838,7 +13838,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128845308</v>
+        <v>128845306</v>
       </c>
       <c r="B114" t="n">
         <v>99891</v>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>541477</v>
+        <v>541120</v>
       </c>
       <c r="R114" t="n">
-        <v>7174417</v>
+        <v>7174297</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14702,7 +14702,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128845311</v>
+        <v>128845319</v>
       </c>
       <c r="B122" t="n">
         <v>99891</v>
@@ -14737,10 +14737,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>541243</v>
+        <v>541045</v>
       </c>
       <c r="R122" t="n">
-        <v>7174412</v>
+        <v>7174303</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14810,7 +14810,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128845319</v>
+        <v>128845311</v>
       </c>
       <c r="B123" t="n">
         <v>99891</v>
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>541045</v>
+        <v>541243</v>
       </c>
       <c r="R123" t="n">
-        <v>7174303</v>
+        <v>7174412</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15247,7 +15247,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128845299</v>
+        <v>128845321</v>
       </c>
       <c r="B127" t="n">
         <v>99891</v>
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>541152</v>
+        <v>541268</v>
       </c>
       <c r="R127" t="n">
-        <v>7174446</v>
+        <v>7174406</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15355,7 +15355,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128845312</v>
+        <v>128845299</v>
       </c>
       <c r="B128" t="n">
         <v>99891</v>
@@ -15390,10 +15390,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>541164</v>
+        <v>541152</v>
       </c>
       <c r="R128" t="n">
-        <v>7174343</v>
+        <v>7174446</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15463,7 +15463,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128845321</v>
+        <v>128845312</v>
       </c>
       <c r="B129" t="n">
         <v>99891</v>
@@ -15498,10 +15498,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>541268</v>
+        <v>541164</v>
       </c>
       <c r="R129" t="n">
-        <v>7174406</v>
+        <v>7174343</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2553,7 +2553,7 @@
         <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>128845363</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B18" t="n">
-        <v>91500</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,34 +2775,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R18" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2844,12 +2849,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2860,21 +2865,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2891,10 +2881,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845325</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2892,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541618</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2961,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,6 +2977,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3011,7 +3011,7 @@
         <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845360</v>
+        <v>128845346</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541640</v>
+        <v>541373</v>
       </c>
       <c r="R21" t="n">
-        <v>7174274</v>
+        <v>7174407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,7 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3242,10 +3247,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845365</v>
+        <v>128845360</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3277,10 +3282,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541453</v>
+        <v>541640</v>
       </c>
       <c r="R22" t="n">
-        <v>7174305</v>
+        <v>7174274</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3312,7 +3317,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3322,7 +3327,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3349,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845346</v>
+        <v>128845365</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3384,10 +3389,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541373</v>
+        <v>541453</v>
       </c>
       <c r="R23" t="n">
-        <v>7174407</v>
+        <v>7174305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3419,7 +3424,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3429,12 +3434,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3461,45 +3461,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845296</v>
+        <v>128845280</v>
       </c>
       <c r="B24" t="n">
-        <v>80254</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541359</v>
+        <v>541574</v>
       </c>
       <c r="R24" t="n">
-        <v>7174394</v>
+        <v>7174569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3531,7 +3536,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3541,12 +3546,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3557,21 +3562,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3588,10 +3578,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845322</v>
+        <v>128845296</v>
       </c>
       <c r="B25" t="n">
-        <v>80261</v>
+        <v>80258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,21 +3589,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3623,10 +3613,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541579</v>
+        <v>541359</v>
       </c>
       <c r="R25" t="n">
-        <v>7174417</v>
+        <v>7174394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3658,7 +3648,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3668,7 +3658,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3715,50 +3705,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845280</v>
+        <v>128845322</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>80265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541574</v>
+        <v>541579</v>
       </c>
       <c r="R26" t="n">
-        <v>7174569</v>
+        <v>7174417</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3775,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3785,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3816,6 +3801,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845340</v>
+        <v>128845353</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541062</v>
+        <v>541612</v>
       </c>
       <c r="R27" t="n">
-        <v>7174293</v>
+        <v>7174586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,21 +3928,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3959,10 +3944,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845353</v>
+        <v>128845298</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3970,34 +3955,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541612</v>
+        <v>541013</v>
       </c>
       <c r="R28" t="n">
-        <v>7174586</v>
+        <v>7174346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4029,7 +4019,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4039,12 +4029,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4071,10 +4061,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845359</v>
+        <v>128845279</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4082,34 +4072,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541617</v>
+        <v>541504</v>
       </c>
       <c r="R29" t="n">
-        <v>7174319</v>
+        <v>7174451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4141,7 +4136,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4151,7 +4146,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,50 +4178,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845298</v>
+        <v>128845323</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>98970</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541013</v>
+        <v>541182</v>
       </c>
       <c r="R30" t="n">
-        <v>7174346</v>
+        <v>7174332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,7 +4248,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4263,12 +4258,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4295,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845279</v>
+        <v>128845340</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4306,39 +4296,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541504</v>
+        <v>541062</v>
       </c>
       <c r="R31" t="n">
-        <v>7174451</v>
+        <v>7174293</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4370,7 +4355,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4380,12 +4365,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4396,6 +4381,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4412,32 +4412,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845323</v>
+        <v>128845359</v>
       </c>
       <c r="B32" t="n">
-        <v>98966</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541182</v>
+        <v>541617</v>
       </c>
       <c r="R32" t="n">
-        <v>7174332</v>
+        <v>7174319</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4519,48 +4519,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845275</v>
+        <v>128845332</v>
       </c>
       <c r="B33" t="n">
-        <v>92201</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541057</v>
+        <v>541284</v>
       </c>
       <c r="R33" t="n">
-        <v>7174336</v>
+        <v>7174287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,12 +4599,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4616,7 +4613,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4650,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845332</v>
+        <v>128845297</v>
       </c>
       <c r="B34" t="n">
-        <v>91522</v>
+        <v>57717</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4661,34 +4657,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541284</v>
+        <v>541232</v>
       </c>
       <c r="R34" t="n">
-        <v>7174287</v>
+        <v>7174426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4720,7 +4724,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4730,12 +4734,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4746,21 +4750,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4780,7 +4769,7 @@
         <v>128845293</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4894,45 +4883,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845341</v>
+        <v>128845275</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>92205</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541131</v>
+        <v>541057</v>
       </c>
       <c r="R36" t="n">
-        <v>7174440</v>
+        <v>7174336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4964,7 +4956,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4974,7 +4966,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4983,8 +4980,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5001,10 +5014,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B37" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5012,42 +5025,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R37" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5084,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5094,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845339</v>
+        <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,37 +5132,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541139</v>
+        <v>541654</v>
       </c>
       <c r="R38" t="n">
-        <v>7174393</v>
+        <v>7174247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5194,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5204,12 +5201,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5218,7 +5215,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845362</v>
+        <v>128845295</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>57880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,34 +5259,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R39" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5322,7 +5330,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5332,7 +5340,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5359,10 +5372,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845367</v>
+        <v>128845339</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5370,34 +5383,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541394</v>
+        <v>541139</v>
       </c>
       <c r="R40" t="n">
-        <v>7174344</v>
+        <v>7174393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5429,7 +5445,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5439,12 +5455,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5453,8 +5469,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5471,10 +5503,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845361</v>
+        <v>128845367</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,10 +5538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R41" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5541,7 +5573,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5551,7 +5583,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5578,10 +5615,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845295</v>
+        <v>128845362</v>
       </c>
       <c r="B42" t="n">
-        <v>57876</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5589,46 +5626,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541394</v>
+        <v>541644</v>
       </c>
       <c r="R42" t="n">
-        <v>7174344</v>
+        <v>7174158</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5660,7 +5685,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5670,12 +5695,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5702,10 +5722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845327</v>
+        <v>128845361</v>
       </c>
       <c r="B43" t="n">
-        <v>91500</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5713,21 +5733,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5737,10 +5757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541654</v>
+        <v>541658</v>
       </c>
       <c r="R43" t="n">
-        <v>7174247</v>
+        <v>7174215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5772,7 +5792,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5782,12 +5802,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5798,21 +5813,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5832,7 +5832,7 @@
         <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845357</v>
+        <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541607</v>
+        <v>541626</v>
       </c>
       <c r="R45" t="n">
-        <v>7174400</v>
+        <v>7174307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,7 +6026,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6037,6 +6042,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6056,7 +6076,7 @@
         <v>128845368</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6160,10 +6180,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845342</v>
+        <v>128845357</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541011</v>
+        <v>541607</v>
       </c>
       <c r="R47" t="n">
-        <v>7174346</v>
+        <v>7174400</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6230,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6240,7 +6260,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6267,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845326</v>
+        <v>128845342</v>
       </c>
       <c r="B48" t="n">
-        <v>91500</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,21 +6298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6302,10 +6322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541626</v>
+        <v>541011</v>
       </c>
       <c r="R48" t="n">
-        <v>7174307</v>
+        <v>7174346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6337,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6347,12 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6363,21 +6378,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6397,7 +6397,7 @@
         <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845335</v>
+        <v>128845336</v>
       </c>
       <c r="B50" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541610</v>
+        <v>541251</v>
       </c>
       <c r="R50" t="n">
-        <v>7174521</v>
+        <v>7174388</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6638,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845336</v>
+        <v>128845335</v>
       </c>
       <c r="B51" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541251</v>
+        <v>541610</v>
       </c>
       <c r="R51" t="n">
-        <v>7174388</v>
+        <v>7174521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6765,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845383</v>
+        <v>128845369</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541079</v>
+        <v>541285</v>
       </c>
       <c r="R52" t="n">
-        <v>7174333</v>
+        <v>7174269</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,12 +6845,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6877,10 +6872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845385</v>
+        <v>128845381</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541163</v>
+        <v>541025</v>
       </c>
       <c r="R53" t="n">
-        <v>7174329</v>
+        <v>7174364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6957,7 +6952,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6989,10 +6984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845304</v>
+        <v>128845385</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,10 +7019,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541120</v>
+        <v>541163</v>
       </c>
       <c r="R54" t="n">
-        <v>7174297</v>
+        <v>7174329</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7054,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7064,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7096,10 +7096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845369</v>
+        <v>128845383</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541285</v>
+        <v>541079</v>
       </c>
       <c r="R55" t="n">
-        <v>7174269</v>
+        <v>7174333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7176,7 +7176,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7203,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845381</v>
+        <v>128845304</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7238,10 +7243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541025</v>
+        <v>541120</v>
       </c>
       <c r="R56" t="n">
-        <v>7174364</v>
+        <v>7174297</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7273,7 +7278,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7283,12 +7288,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7318,7 +7318,7 @@
         <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845333</v>
+        <v>128845373</v>
       </c>
       <c r="B59" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541462</v>
+        <v>541143</v>
       </c>
       <c r="R59" t="n">
-        <v>7174528</v>
+        <v>7174450</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,12 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7645,21 +7640,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7676,10 +7656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845292</v>
+        <v>128845348</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,39 +7667,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541140</v>
+        <v>541504</v>
       </c>
       <c r="R60" t="n">
-        <v>7174441</v>
+        <v>7174451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7751,7 +7726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7761,12 +7736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7793,10 +7763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845348</v>
+        <v>128845354</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7828,10 +7798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541504</v>
+        <v>541618</v>
       </c>
       <c r="R61" t="n">
-        <v>7174451</v>
+        <v>7174522</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7863,7 +7833,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7873,7 +7843,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7900,10 +7870,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845373</v>
+        <v>128845292</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7911,34 +7881,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541143</v>
+        <v>541140</v>
       </c>
       <c r="R62" t="n">
-        <v>7174450</v>
+        <v>7174441</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7970,7 +7945,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7980,7 +7955,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8007,10 +7987,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845354</v>
+        <v>128845333</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8018,21 +7998,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8042,10 +8022,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541618</v>
+        <v>541462</v>
       </c>
       <c r="R63" t="n">
-        <v>7174522</v>
+        <v>7174528</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8077,7 +8057,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8087,7 +8067,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8098,6 +8083,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8117,7 +8117,7 @@
         <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>128845378</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>128845375</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>128845355</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>128845284</v>
       </c>
       <c r="B68" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128845282</v>
       </c>
       <c r="B69" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>128845384</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>128845364</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128845351</v>
       </c>
       <c r="B72" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9127,10 +9127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845358</v>
+        <v>128845379</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541633</v>
+        <v>540962</v>
       </c>
       <c r="R73" t="n">
-        <v>7174358</v>
+        <v>7174330</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,7 +9207,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9234,10 +9239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845300</v>
+        <v>128845358</v>
       </c>
       <c r="B74" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541095</v>
+        <v>541633</v>
       </c>
       <c r="R74" t="n">
-        <v>7174393</v>
+        <v>7174358</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9304,7 +9309,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9314,7 +9319,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9341,10 +9346,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845379</v>
+        <v>128845300</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9376,10 +9381,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540962</v>
+        <v>541095</v>
       </c>
       <c r="R75" t="n">
-        <v>7174330</v>
+        <v>7174393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9411,7 +9416,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9421,12 +9426,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>128845372</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>128845377</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B79" t="n">
-        <v>91500</v>
+        <v>57880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,34 +9805,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R79" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9886,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,21 +9902,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9921,10 +9918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B80" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9932,21 +9929,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9956,10 +9953,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R80" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9991,7 +9988,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10001,12 +9998,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10017,6 +10014,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10033,10 +10045,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845371</v>
+        <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,10 +10080,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541216</v>
+        <v>541027</v>
       </c>
       <c r="R81" t="n">
-        <v>7174399</v>
+        <v>7174356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10103,7 +10115,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10113,7 +10125,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10140,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B82" t="n">
-        <v>57876</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10151,46 +10168,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R82" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10227,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10237,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>128845352</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10498,10 +10498,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845347</v>
+        <v>128845302</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541411</v>
+        <v>541089</v>
       </c>
       <c r="R85" t="n">
-        <v>7174397</v>
+        <v>7174431</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10578,12 +10578,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10610,10 +10605,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845302</v>
+        <v>128845347</v>
       </c>
       <c r="B86" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10645,10 +10640,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541089</v>
+        <v>541411</v>
       </c>
       <c r="R86" t="n">
-        <v>7174431</v>
+        <v>7174397</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10680,7 +10675,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10690,7 +10685,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845344</v>
+        <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>92205</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541312</v>
+        <v>541629</v>
       </c>
       <c r="R87" t="n">
-        <v>7174300</v>
+        <v>7174402</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,7 +10797,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10808,6 +10813,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10824,10 +10844,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845344</v>
       </c>
       <c r="B88" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10835,39 +10855,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541312</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10899,7 +10914,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10909,12 +10924,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10941,45 +10951,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845272</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
-        <v>92201</v>
+        <v>57720</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541629</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174402</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11011,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11021,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11037,21 +11052,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11071,7 +11071,7 @@
         <v>128845276</v>
       </c>
       <c r="B90" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>128845281</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11931,10 +11931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,12 +12011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12043,10 +12038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B98" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R98" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12113,7 +12108,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12123,7 +12118,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12153,7 +12153,7 @@
         <v>128845285</v>
       </c>
       <c r="B99" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>128845288</v>
       </c>
       <c r="B100" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845343</v>
+        <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,34 +12395,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541074</v>
+        <v>541322</v>
       </c>
       <c r="R101" t="n">
-        <v>7174298</v>
+        <v>7174361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,10 +12501,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845269</v>
+        <v>128845343</v>
       </c>
       <c r="B102" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541134</v>
+        <v>541074</v>
       </c>
       <c r="R102" t="n">
-        <v>7174353</v>
+        <v>7174298</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12571,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12581,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12601,7 +12611,7 @@
         <v>128845376</v>
       </c>
       <c r="B103" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12705,10 +12715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845277</v>
+        <v>128845269</v>
       </c>
       <c r="B104" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12716,39 +12726,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541322</v>
+        <v>541134</v>
       </c>
       <c r="R104" t="n">
-        <v>7174361</v>
+        <v>7174353</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12790,12 +12795,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12825,7 +12825,7 @@
         <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845366</v>
+        <v>128845345</v>
       </c>
       <c r="B107" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541398</v>
+        <v>541348</v>
       </c>
       <c r="R107" t="n">
-        <v>7174337</v>
+        <v>7174394</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,7 +13156,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13183,10 +13188,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845350</v>
+        <v>128845349</v>
       </c>
       <c r="B108" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13218,10 +13223,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541554</v>
+        <v>541462</v>
       </c>
       <c r="R108" t="n">
-        <v>7174535</v>
+        <v>7174528</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13253,7 +13258,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13263,12 +13268,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,10 +13295,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845349</v>
+        <v>128845350</v>
       </c>
       <c r="B109" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541462</v>
+        <v>541554</v>
       </c>
       <c r="R109" t="n">
-        <v>7174528</v>
+        <v>7174535</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,7 +13375,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13402,10 +13407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845345</v>
+        <v>128845366</v>
       </c>
       <c r="B110" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13437,10 +13442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541348</v>
+        <v>541398</v>
       </c>
       <c r="R110" t="n">
-        <v>7174394</v>
+        <v>7174337</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13472,7 +13477,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,12 +13487,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99891</v>
+        <v>99895</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R16" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2630,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2646,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2657,7 +2677,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845363</v>
+        <v>128845356</v>
       </c>
       <c r="B17" t="n">
         <v>79124</v>
@@ -2692,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541623</v>
+        <v>541606</v>
       </c>
       <c r="R17" t="n">
-        <v>7174167</v>
+        <v>7174439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2737,7 +2757,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,39 +2795,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R18" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,12 +2864,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2892,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2951,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,12 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,21 +2992,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3135,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845346</v>
+        <v>128845296</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541373</v>
+        <v>541359</v>
       </c>
       <c r="R21" t="n">
-        <v>7174407</v>
+        <v>7174394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,6 +3231,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3247,32 +3262,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845360</v>
+        <v>128845322</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>80265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3282,10 +3297,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541640</v>
+        <v>541579</v>
       </c>
       <c r="R22" t="n">
-        <v>7174274</v>
+        <v>7174417</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3317,7 +3332,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3327,7 +3342,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3338,6 +3358,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3354,10 +3389,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845365</v>
+        <v>128845280</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3365,34 +3400,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541453</v>
+        <v>541574</v>
       </c>
       <c r="R23" t="n">
-        <v>7174305</v>
+        <v>7174569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,7 +3464,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3434,7 +3474,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3461,10 +3506,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845280</v>
+        <v>128845360</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3472,39 +3517,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541574</v>
+        <v>541640</v>
       </c>
       <c r="R24" t="n">
-        <v>7174569</v>
+        <v>7174274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3536,7 +3576,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3546,12 +3586,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3578,32 +3613,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845296</v>
+        <v>128845365</v>
       </c>
       <c r="B25" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3613,10 +3648,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541359</v>
+        <v>541453</v>
       </c>
       <c r="R25" t="n">
-        <v>7174394</v>
+        <v>7174305</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3648,7 +3683,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3658,12 +3693,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3674,21 +3704,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3705,32 +3720,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845322</v>
+        <v>128845346</v>
       </c>
       <c r="B26" t="n">
-        <v>80265</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3740,10 +3755,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541579</v>
+        <v>541373</v>
       </c>
       <c r="R26" t="n">
-        <v>7174417</v>
+        <v>7174407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845323</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>98970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541182</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174332</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3944,10 +3939,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845298</v>
+        <v>128845353</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3955,39 +3950,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541013</v>
+        <v>541612</v>
       </c>
       <c r="R28" t="n">
-        <v>7174346</v>
+        <v>7174586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4019,7 +4009,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4029,12 +4019,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4061,10 +4051,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845279</v>
+        <v>128845359</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4072,39 +4062,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541504</v>
+        <v>541617</v>
       </c>
       <c r="R29" t="n">
-        <v>7174451</v>
+        <v>7174319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4136,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4146,12 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,32 +4158,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845323</v>
+        <v>128845340</v>
       </c>
       <c r="B30" t="n">
-        <v>98970</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4213,10 +4193,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541182</v>
+        <v>541062</v>
       </c>
       <c r="R30" t="n">
-        <v>7174332</v>
+        <v>7174293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4248,7 +4228,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4258,7 +4238,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4269,6 +4254,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>57717</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4296,34 +4296,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R31" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4365,12 +4370,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4381,21 +4386,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4412,10 +4402,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845359</v>
+        <v>128845279</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4423,34 +4413,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541617</v>
+        <v>541504</v>
       </c>
       <c r="R32" t="n">
-        <v>7174319</v>
+        <v>7174451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4492,7 +4487,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B34" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,42 +4657,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R34" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4724,7 +4716,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4734,12 +4726,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4766,50 +4753,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845293</v>
+        <v>128845275</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>92205</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541157</v>
+        <v>541057</v>
       </c>
       <c r="R35" t="n">
-        <v>7174382</v>
+        <v>7174336</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4841,7 +4826,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4851,12 +4836,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4865,8 +4850,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4883,37 +4884,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845275</v>
+        <v>128845297</v>
       </c>
       <c r="B36" t="n">
-        <v>92205</v>
+        <v>57717</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4921,10 +4927,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541057</v>
+        <v>541232</v>
       </c>
       <c r="R36" t="n">
-        <v>7174336</v>
+        <v>7174426</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4956,7 +4962,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4966,12 +4972,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4980,24 +4986,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5014,10 +5004,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845341</v>
+        <v>128845293</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5025,34 +5015,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541131</v>
+        <v>541157</v>
       </c>
       <c r="R37" t="n">
-        <v>7174440</v>
+        <v>7174382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5084,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5094,7 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845295</v>
+        <v>128845339</v>
       </c>
       <c r="B39" t="n">
-        <v>57880</v>
+        <v>91526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,35 +5259,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5295,10 +5286,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541394</v>
+        <v>541139</v>
       </c>
       <c r="R39" t="n">
-        <v>7174344</v>
+        <v>7174393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5330,7 +5321,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5340,12 +5331,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5354,8 +5345,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5372,10 +5379,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845339</v>
+        <v>128845361</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5383,37 +5390,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541139</v>
+        <v>541658</v>
       </c>
       <c r="R40" t="n">
-        <v>7174393</v>
+        <v>7174215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5445,7 +5449,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5455,12 +5459,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5469,24 +5468,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5503,10 +5486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845367</v>
+        <v>128845283</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5514,34 +5497,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541394</v>
+        <v>541605</v>
       </c>
       <c r="R41" t="n">
-        <v>7174344</v>
+        <v>7174433</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5573,7 +5561,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5583,12 +5571,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5615,10 +5603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845362</v>
+        <v>128845295</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>57880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5626,34 +5614,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5695,7 +5695,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5722,7 +5727,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845361</v>
+        <v>128845362</v>
       </c>
       <c r="B43" t="n">
         <v>79124</v>
@@ -5757,10 +5762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541658</v>
+        <v>541644</v>
       </c>
       <c r="R43" t="n">
-        <v>7174215</v>
+        <v>7174158</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5792,7 +5797,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5802,7 +5807,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5829,10 +5834,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845283</v>
+        <v>128845367</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5840,39 +5845,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541605</v>
+        <v>541394</v>
       </c>
       <c r="R44" t="n">
-        <v>7174433</v>
+        <v>7174344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B45" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R45" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,12 +6026,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,21 +6037,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6180,7 +6160,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845357</v>
+        <v>128845342</v>
       </c>
       <c r="B47" t="n">
         <v>79124</v>
@@ -6215,10 +6195,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541607</v>
+        <v>541011</v>
       </c>
       <c r="R47" t="n">
-        <v>7174400</v>
+        <v>7174346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6230,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,7 +6240,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6287,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845342</v>
+        <v>128845326</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6298,21 +6278,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6322,10 +6302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541011</v>
+        <v>541626</v>
       </c>
       <c r="R48" t="n">
-        <v>7174346</v>
+        <v>7174307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6337,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6347,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6378,6 +6363,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845336</v>
+        <v>128845383</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541251</v>
+        <v>541079</v>
       </c>
       <c r="R50" t="n">
-        <v>7174388</v>
+        <v>7174333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,21 +6607,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6638,10 +6623,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845335</v>
+        <v>128845385</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6649,21 +6634,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6673,10 +6658,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541610</v>
+        <v>541163</v>
       </c>
       <c r="R51" t="n">
-        <v>7174521</v>
+        <v>7174329</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6693,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,12 +6703,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6734,21 +6719,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6765,7 +6735,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845369</v>
+        <v>128845304</v>
       </c>
       <c r="B52" t="n">
         <v>79124</v>
@@ -6800,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541285</v>
+        <v>541120</v>
       </c>
       <c r="R52" t="n">
-        <v>7174269</v>
+        <v>7174297</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6835,7 +6805,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,7 +6815,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6872,7 +6842,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845381</v>
+        <v>128845369</v>
       </c>
       <c r="B53" t="n">
         <v>79124</v>
@@ -6907,10 +6877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541025</v>
+        <v>541285</v>
       </c>
       <c r="R53" t="n">
-        <v>7174364</v>
+        <v>7174269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6942,7 +6912,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6952,12 +6922,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6984,7 +6949,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845385</v>
+        <v>128845381</v>
       </c>
       <c r="B54" t="n">
         <v>79124</v>
@@ -7019,10 +6984,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541163</v>
+        <v>541025</v>
       </c>
       <c r="R54" t="n">
-        <v>7174329</v>
+        <v>7174364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7054,7 +7019,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7064,7 +7029,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7096,10 +7061,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845383</v>
+        <v>128845335</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7107,21 +7072,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7131,10 +7096,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541079</v>
+        <v>541610</v>
       </c>
       <c r="R55" t="n">
-        <v>7174333</v>
+        <v>7174521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7166,7 +7131,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7176,12 +7141,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7192,6 +7157,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7208,10 +7188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845304</v>
+        <v>128845336</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,21 +7199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7243,10 +7223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541120</v>
+        <v>541251</v>
       </c>
       <c r="R56" t="n">
-        <v>7174297</v>
+        <v>7174388</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7278,7 +7258,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7288,7 +7268,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7299,6 +7284,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7549,7 +7549,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B59" t="n">
         <v>79124</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R59" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7656,7 +7656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845348</v>
+        <v>128845373</v>
       </c>
       <c r="B60" t="n">
         <v>79124</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541504</v>
+        <v>541143</v>
       </c>
       <c r="R60" t="n">
-        <v>7174451</v>
+        <v>7174450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845324</v>
+        <v>128845378</v>
       </c>
       <c r="B64" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541610</v>
+        <v>541032</v>
       </c>
       <c r="R64" t="n">
-        <v>7174586</v>
+        <v>7174308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,12 +8194,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8210,21 +8205,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8241,7 +8221,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845378</v>
+        <v>128845375</v>
       </c>
       <c r="B65" t="n">
         <v>79124</v>
@@ -8276,10 +8256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541032</v>
+        <v>541136</v>
       </c>
       <c r="R65" t="n">
-        <v>7174308</v>
+        <v>7174402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8311,7 +8291,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8321,7 +8301,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8348,7 +8328,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845375</v>
+        <v>128845355</v>
       </c>
       <c r="B66" t="n">
         <v>79124</v>
@@ -8383,10 +8363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R66" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8398,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,7 +8408,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8455,10 +8440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845355</v>
+        <v>128845284</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8466,24 +8451,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8493,7 +8483,7 @@
         <v>541637</v>
       </c>
       <c r="R67" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8525,7 +8515,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8535,12 +8525,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8567,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845284</v>
+        <v>128845324</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>91504</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8578,39 +8568,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R68" t="n">
-        <v>7174351</v>
+        <v>7174586</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8642,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8668,6 +8653,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9127,7 +9127,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845379</v>
+        <v>128845358</v>
       </c>
       <c r="B73" t="n">
         <v>79124</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540962</v>
+        <v>541633</v>
       </c>
       <c r="R73" t="n">
-        <v>7174330</v>
+        <v>7174358</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,12 +9207,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9239,7 +9234,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845358</v>
+        <v>128845300</v>
       </c>
       <c r="B74" t="n">
         <v>79124</v>
@@ -9274,10 +9269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541633</v>
+        <v>541095</v>
       </c>
       <c r="R74" t="n">
-        <v>7174358</v>
+        <v>7174393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9309,7 +9304,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9319,7 +9314,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9346,7 +9341,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845300</v>
+        <v>128845379</v>
       </c>
       <c r="B75" t="n">
         <v>79124</v>
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541095</v>
+        <v>540962</v>
       </c>
       <c r="R75" t="n">
-        <v>7174393</v>
+        <v>7174330</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9416,7 +9411,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9426,7 +9421,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128845271</v>
+        <v>128845372</v>
       </c>
       <c r="B76" t="n">
-        <v>92205</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541616</v>
+        <v>541206</v>
       </c>
       <c r="R76" t="n">
-        <v>7174449</v>
+        <v>7174374</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9533,12 +9533,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På stående levande gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9549,21 +9544,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9580,7 +9560,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845372</v>
+        <v>128845377</v>
       </c>
       <c r="B77" t="n">
         <v>79124</v>
@@ -9615,10 +9595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541206</v>
+        <v>541055</v>
       </c>
       <c r="R77" t="n">
-        <v>7174374</v>
+        <v>7174298</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9650,7 +9630,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9660,7 +9640,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9687,32 +9667,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845377</v>
+        <v>128845271</v>
       </c>
       <c r="B78" t="n">
-        <v>79124</v>
+        <v>92205</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9722,10 +9702,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541055</v>
+        <v>541616</v>
       </c>
       <c r="R78" t="n">
-        <v>7174298</v>
+        <v>7174449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9757,7 +9737,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9767,7 +9747,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På stående levande gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9778,6 +9763,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845294</v>
+        <v>128845380</v>
       </c>
       <c r="B79" t="n">
-        <v>57880</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,46 +9805,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541544</v>
+        <v>541027</v>
       </c>
       <c r="R79" t="n">
-        <v>7174513</v>
+        <v>7174356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9876,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9886,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9918,10 +9906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B80" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9929,21 +9917,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9953,10 +9941,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R80" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9988,7 +9976,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9998,12 +9986,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10014,21 +9997,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10045,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10056,21 +10024,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10080,10 +10048,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R81" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10115,7 +10083,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10125,12 +10093,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10141,6 +10109,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10157,10 +10140,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845371</v>
+        <v>128845294</v>
       </c>
       <c r="B82" t="n">
-        <v>79124</v>
+        <v>57880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,34 +10151,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541216</v>
+        <v>541544</v>
       </c>
       <c r="R82" t="n">
-        <v>7174399</v>
+        <v>7174513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10227,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10237,7 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10498,7 +10498,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845302</v>
+        <v>128845347</v>
       </c>
       <c r="B85" t="n">
         <v>79124</v>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541089</v>
+        <v>541411</v>
       </c>
       <c r="R85" t="n">
-        <v>7174431</v>
+        <v>7174397</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10578,7 +10578,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10605,7 +10610,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845347</v>
+        <v>128845302</v>
       </c>
       <c r="B86" t="n">
         <v>79124</v>
@@ -10640,10 +10645,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541411</v>
+        <v>541089</v>
       </c>
       <c r="R86" t="n">
-        <v>7174397</v>
+        <v>7174431</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10675,7 +10680,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10685,12 +10690,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845272</v>
+        <v>128845344</v>
       </c>
       <c r="B87" t="n">
-        <v>92205</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541629</v>
+        <v>541312</v>
       </c>
       <c r="R87" t="n">
-        <v>7174402</v>
+        <v>7174300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,12 +10797,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10813,21 +10808,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10844,10 +10824,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845344</v>
+        <v>128845278</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10855,34 +10835,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541312</v>
+        <v>541418</v>
       </c>
       <c r="R88" t="n">
-        <v>7174300</v>
+        <v>7174396</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10914,7 +10899,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10924,7 +10909,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10951,7 +10941,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845276</v>
       </c>
       <c r="B89" t="n">
         <v>57720</v>
@@ -10982,7 +10972,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10991,10 +10981,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541274</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174268</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11016,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11026,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11068,7 +11058,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845276</v>
+        <v>128845281</v>
       </c>
       <c r="B90" t="n">
         <v>57720</v>
@@ -11108,10 +11098,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541274</v>
+        <v>541599</v>
       </c>
       <c r="R90" t="n">
-        <v>7174268</v>
+        <v>7174544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11143,7 +11133,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11153,7 +11143,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -11185,50 +11175,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845281</v>
+        <v>128845272</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>92205</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541599</v>
+        <v>541629</v>
       </c>
       <c r="R91" t="n">
-        <v>7174544</v>
+        <v>7174402</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11245,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,12 +11255,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11286,6 +11271,21 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845331</v>
+        <v>128845285</v>
       </c>
       <c r="B96" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,34 +11815,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541271</v>
+        <v>541640</v>
       </c>
       <c r="R96" t="n">
-        <v>7174269</v>
+        <v>7174353</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11879,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11889,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,21 +11905,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11931,10 +11921,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845288</v>
       </c>
       <c r="B97" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11942,34 +11932,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541261</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174398</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +11996,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,7 +12006,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12038,10 +12038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845370</v>
+        <v>128845331</v>
       </c>
       <c r="B98" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12049,21 +12049,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12073,10 +12073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541222</v>
+        <v>541271</v>
       </c>
       <c r="R98" t="n">
-        <v>7174409</v>
+        <v>7174269</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12134,6 +12134,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12150,10 +12165,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845370</v>
       </c>
       <c r="B99" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12161,39 +12176,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541222</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174409</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12235,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,12 +12245,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12267,10 +12277,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845288</v>
+        <v>128845382</v>
       </c>
       <c r="B100" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12278,39 +12288,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541261</v>
+        <v>541041</v>
       </c>
       <c r="R100" t="n">
-        <v>7174398</v>
+        <v>7174348</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12347,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,12 +12357,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845277</v>
+        <v>128845343</v>
       </c>
       <c r="B101" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,39 +12395,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541322</v>
+        <v>541074</v>
       </c>
       <c r="R101" t="n">
-        <v>7174361</v>
+        <v>7174298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12459,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12469,12 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12501,7 +12491,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B102" t="n">
         <v>79124</v>
@@ -12536,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R102" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12571,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12581,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12715,10 +12705,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845269</v>
+        <v>128845277</v>
       </c>
       <c r="B104" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,34 +12716,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541134</v>
+        <v>541322</v>
       </c>
       <c r="R104" t="n">
-        <v>7174353</v>
+        <v>7174361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12785,7 +12780,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12795,7 +12790,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B105" t="n">
-        <v>91504</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R105" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B106" t="n">
-        <v>91526</v>
+        <v>91504</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R106" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13076,7 +13076,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845345</v>
+        <v>128845366</v>
       </c>
       <c r="B107" t="n">
         <v>79124</v>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541348</v>
+        <v>541398</v>
       </c>
       <c r="R107" t="n">
-        <v>7174394</v>
+        <v>7174337</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,12 +13156,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13188,7 +13183,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845349</v>
+        <v>128845350</v>
       </c>
       <c r="B108" t="n">
         <v>79124</v>
@@ -13223,10 +13218,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541462</v>
+        <v>541554</v>
       </c>
       <c r="R108" t="n">
-        <v>7174528</v>
+        <v>7174535</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13258,7 +13253,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13268,7 +13263,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845350</v>
+        <v>128845349</v>
       </c>
       <c r="B109" t="n">
         <v>79124</v>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541554</v>
+        <v>541462</v>
       </c>
       <c r="R109" t="n">
-        <v>7174535</v>
+        <v>7174528</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,12 +13375,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13407,7 +13402,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845366</v>
+        <v>128845345</v>
       </c>
       <c r="B110" t="n">
         <v>79124</v>
@@ -13442,10 +13437,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541398</v>
+        <v>541348</v>
       </c>
       <c r="R110" t="n">
-        <v>7174337</v>
+        <v>7174394</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13477,7 +13472,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13487,7 +13482,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845325</v>
+        <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541618</v>
+        <v>541606</v>
       </c>
       <c r="R16" t="n">
-        <v>7174399</v>
+        <v>7174439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,12 +2630,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,21 +2641,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2677,7 +2657,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845356</v>
+        <v>128845363</v>
       </c>
       <c r="B17" t="n">
         <v>79124</v>
@@ -2712,10 +2692,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541606</v>
+        <v>541623</v>
       </c>
       <c r="R17" t="n">
-        <v>7174439</v>
+        <v>7174167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2727,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,7 +2737,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2784,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845363</v>
+        <v>128845325</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2775,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2819,10 +2799,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541623</v>
+        <v>541618</v>
       </c>
       <c r="R18" t="n">
-        <v>7174167</v>
+        <v>7174399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2854,7 +2834,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,7 +2844,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,6 +2860,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845328</v>
+        <v>128845360</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541428</v>
+        <v>541640</v>
       </c>
       <c r="R20" t="n">
-        <v>7174314</v>
+        <v>7174274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3088,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3104,21 +3099,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3135,45 +3115,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845296</v>
+        <v>128845280</v>
       </c>
       <c r="B21" t="n">
-        <v>80258</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541359</v>
+        <v>541574</v>
       </c>
       <c r="R21" t="n">
-        <v>7174394</v>
+        <v>7174569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3190,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,12 +3200,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,21 +3216,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3262,32 +3232,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845322</v>
+        <v>128845328</v>
       </c>
       <c r="B22" t="n">
-        <v>80265</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3297,10 +3267,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541579</v>
+        <v>541428</v>
       </c>
       <c r="R22" t="n">
-        <v>7174417</v>
+        <v>7174314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,7 +3302,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3342,12 +3312,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3361,17 +3331,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3389,10 +3359,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845280</v>
+        <v>128845365</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3400,39 +3370,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541574</v>
+        <v>541453</v>
       </c>
       <c r="R23" t="n">
-        <v>7174569</v>
+        <v>7174305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3464,7 +3429,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3474,12 +3439,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3506,32 +3466,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845360</v>
+        <v>128845296</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3541,10 +3501,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541640</v>
+        <v>541359</v>
       </c>
       <c r="R24" t="n">
-        <v>7174274</v>
+        <v>7174394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3576,7 +3536,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3586,7 +3546,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3597,6 +3562,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3613,32 +3593,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845365</v>
+        <v>128845322</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>80265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3648,10 +3628,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541453</v>
+        <v>541579</v>
       </c>
       <c r="R25" t="n">
-        <v>7174305</v>
+        <v>7174417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3683,7 +3663,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3693,7 +3673,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3704,6 +3689,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845323</v>
+        <v>128845353</v>
       </c>
       <c r="B27" t="n">
-        <v>98970</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541182</v>
+        <v>541612</v>
       </c>
       <c r="R27" t="n">
-        <v>7174332</v>
+        <v>7174586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3939,10 +3944,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845353</v>
+        <v>128845340</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3950,21 +3955,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541612</v>
+        <v>541062</v>
       </c>
       <c r="R28" t="n">
-        <v>7174586</v>
+        <v>7174293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4009,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4019,12 +4024,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4035,6 +4040,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4158,10 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,34 +4189,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R30" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4228,7 +4253,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4238,12 +4263,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,21 +4279,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4285,10 +4295,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B31" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4296,16 +4306,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4316,7 +4326,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4325,10 +4335,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R31" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4360,7 +4370,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4370,12 +4380,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4402,50 +4412,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>98970</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R32" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4477,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,12 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845339</v>
+        <v>128845367</v>
       </c>
       <c r="B39" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,37 +5259,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541139</v>
+        <v>541394</v>
       </c>
       <c r="R39" t="n">
-        <v>7174393</v>
+        <v>7174344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5321,7 +5318,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5331,12 +5328,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5345,24 +5342,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,10 +5360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845361</v>
+        <v>128845339</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5390,34 +5371,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541658</v>
+        <v>541139</v>
       </c>
       <c r="R40" t="n">
-        <v>7174215</v>
+        <v>7174393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5449,7 +5433,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5459,7 +5443,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5468,8 +5457,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5486,10 +5491,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845283</v>
+        <v>128845362</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5497,39 +5502,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541605</v>
+        <v>541644</v>
       </c>
       <c r="R41" t="n">
-        <v>7174433</v>
+        <v>7174158</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5571,12 +5571,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5603,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845295</v>
+        <v>128845361</v>
       </c>
       <c r="B42" t="n">
-        <v>57880</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5614,46 +5609,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R42" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5685,7 +5668,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5695,12 +5678,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5727,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845362</v>
+        <v>128845283</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5738,34 +5716,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541644</v>
+        <v>541605</v>
       </c>
       <c r="R43" t="n">
-        <v>7174158</v>
+        <v>7174433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5797,7 +5780,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5807,7 +5790,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5834,10 +5822,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845367</v>
+        <v>128845295</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>57880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5845,24 +5833,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845357</v>
+        <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541607</v>
+        <v>541626</v>
       </c>
       <c r="R45" t="n">
-        <v>7174400</v>
+        <v>7174307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,7 +6026,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6037,6 +6042,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6053,7 +6073,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845368</v>
+        <v>128845357</v>
       </c>
       <c r="B46" t="n">
         <v>79124</v>
@@ -6088,10 +6108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541363</v>
+        <v>541607</v>
       </c>
       <c r="R46" t="n">
-        <v>7174330</v>
+        <v>7174400</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6123,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6133,7 +6153,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6160,7 +6180,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845342</v>
+        <v>128845368</v>
       </c>
       <c r="B47" t="n">
         <v>79124</v>
@@ -6195,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541011</v>
+        <v>541363</v>
       </c>
       <c r="R47" t="n">
-        <v>7174346</v>
+        <v>7174330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6230,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6240,7 +6260,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6267,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845326</v>
+        <v>128845342</v>
       </c>
       <c r="B48" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,21 +6298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6302,10 +6322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541626</v>
+        <v>541011</v>
       </c>
       <c r="R48" t="n">
-        <v>7174307</v>
+        <v>7174346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6337,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6347,12 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6363,21 +6378,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6735,7 +6735,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845304</v>
+        <v>128845381</v>
       </c>
       <c r="B52" t="n">
         <v>79124</v>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541120</v>
+        <v>541025</v>
       </c>
       <c r="R52" t="n">
-        <v>7174297</v>
+        <v>7174364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6815,7 +6815,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6842,10 +6847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845369</v>
+        <v>128845335</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6853,21 +6858,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6877,10 +6882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541285</v>
+        <v>541610</v>
       </c>
       <c r="R53" t="n">
-        <v>7174269</v>
+        <v>7174521</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6912,7 +6917,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6922,7 +6927,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6933,6 +6943,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6949,10 +6974,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845381</v>
+        <v>128845336</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,21 +6985,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6984,10 +7009,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541025</v>
+        <v>541251</v>
       </c>
       <c r="R54" t="n">
-        <v>7174364</v>
+        <v>7174388</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7019,7 +7044,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7029,12 +7054,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7045,6 +7070,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7061,10 +7101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845335</v>
+        <v>128845304</v>
       </c>
       <c r="B55" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7072,21 +7112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7096,10 +7136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541610</v>
+        <v>541120</v>
       </c>
       <c r="R55" t="n">
-        <v>7174521</v>
+        <v>7174297</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7131,7 +7171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7141,12 +7181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7157,21 +7192,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7188,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845336</v>
+        <v>128845369</v>
       </c>
       <c r="B56" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7199,21 +7219,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7223,10 +7243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541251</v>
+        <v>541285</v>
       </c>
       <c r="R56" t="n">
-        <v>7174388</v>
+        <v>7174269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7258,7 +7278,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7268,12 +7288,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7284,21 +7299,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7315,7 +7315,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845289</v>
+        <v>128845291</v>
       </c>
       <c r="B57" t="n">
         <v>57720</v>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541254</v>
+        <v>541147</v>
       </c>
       <c r="R57" t="n">
-        <v>7174391</v>
+        <v>7174441</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845291</v>
+        <v>128845289</v>
       </c>
       <c r="B58" t="n">
         <v>57720</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541147</v>
+        <v>541254</v>
       </c>
       <c r="R58" t="n">
-        <v>7174441</v>
+        <v>7174391</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7656,10 +7656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845292</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7667,34 +7667,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541140</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7731,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7741,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7763,10 +7773,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845354</v>
+        <v>128845333</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7774,21 +7784,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7798,10 +7808,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541618</v>
+        <v>541462</v>
       </c>
       <c r="R61" t="n">
-        <v>7174522</v>
+        <v>7174528</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7833,7 +7843,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7843,7 +7853,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7854,6 +7869,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7870,10 +7900,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845292</v>
+        <v>128845373</v>
       </c>
       <c r="B62" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7881,39 +7911,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541140</v>
+        <v>541143</v>
       </c>
       <c r="R62" t="n">
-        <v>7174441</v>
+        <v>7174450</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7945,7 +7970,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7955,12 +7980,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7987,10 +8007,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845333</v>
+        <v>128845354</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7998,21 +8018,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8022,10 +8042,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541462</v>
+        <v>541618</v>
       </c>
       <c r="R63" t="n">
-        <v>7174528</v>
+        <v>7174522</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8057,7 +8077,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8067,12 +8087,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8083,21 +8098,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845378</v>
+        <v>128845284</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,34 +8125,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541032</v>
+        <v>541637</v>
       </c>
       <c r="R64" t="n">
-        <v>7174308</v>
+        <v>7174351</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8189,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,7 +8199,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8221,10 +8231,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845375</v>
+        <v>128845282</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8232,34 +8242,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R65" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8291,7 +8306,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8301,7 +8316,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8328,10 +8348,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845355</v>
+        <v>128845324</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8339,21 +8359,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8363,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R66" t="n">
-        <v>7174473</v>
+        <v>7174586</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8398,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8408,12 +8428,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8424,6 +8444,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8440,10 +8475,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845284</v>
+        <v>128845375</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8451,39 +8486,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R67" t="n">
-        <v>7174351</v>
+        <v>7174402</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8515,7 +8545,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8525,12 +8555,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,10 +8582,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845324</v>
+        <v>128845378</v>
       </c>
       <c r="B68" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,21 +8593,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8592,10 +8617,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541610</v>
+        <v>541032</v>
       </c>
       <c r="R68" t="n">
-        <v>7174586</v>
+        <v>7174308</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8652,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8662,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8673,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8684,10 +8689,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845282</v>
+        <v>128845355</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8695,29 +8700,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845384</v>
+        <v>128845351</v>
       </c>
       <c r="B70" t="n">
         <v>79124</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541112</v>
+        <v>541563</v>
       </c>
       <c r="R70" t="n">
-        <v>7174350</v>
+        <v>7174549</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,7 +8881,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8908,7 +8913,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128845364</v>
+        <v>128845384</v>
       </c>
       <c r="B71" t="n">
         <v>79124</v>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541490</v>
+        <v>541112</v>
       </c>
       <c r="R71" t="n">
-        <v>7174268</v>
+        <v>7174350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8978,7 +8983,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8988,7 +8993,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9015,7 +9020,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845351</v>
+        <v>128845364</v>
       </c>
       <c r="B72" t="n">
         <v>79124</v>
@@ -9050,10 +9055,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541563</v>
+        <v>541490</v>
       </c>
       <c r="R72" t="n">
-        <v>7174549</v>
+        <v>7174268</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9085,7 +9090,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9095,12 +9100,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9127,7 +9127,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845358</v>
+        <v>128845379</v>
       </c>
       <c r="B73" t="n">
         <v>79124</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541633</v>
+        <v>540962</v>
       </c>
       <c r="R73" t="n">
-        <v>7174358</v>
+        <v>7174330</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,7 +9207,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9234,7 +9239,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845300</v>
+        <v>128845358</v>
       </c>
       <c r="B74" t="n">
         <v>79124</v>
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541095</v>
+        <v>541633</v>
       </c>
       <c r="R74" t="n">
-        <v>7174393</v>
+        <v>7174358</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9304,7 +9309,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9314,7 +9319,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9341,7 +9346,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845379</v>
+        <v>128845300</v>
       </c>
       <c r="B75" t="n">
         <v>79124</v>
@@ -9376,10 +9381,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540962</v>
+        <v>541095</v>
       </c>
       <c r="R75" t="n">
-        <v>7174330</v>
+        <v>7174393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9411,7 +9416,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9421,12 +9426,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,21 +9805,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,6 +9890,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10013,10 +10028,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,21 +10039,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10048,10 +10063,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541027</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10083,7 +10098,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10093,12 +10108,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10109,21 +10124,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10824,50 +10824,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B88" t="n">
-        <v>57720</v>
+        <v>92205</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10899,7 +10894,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10909,12 +10904,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10925,6 +10920,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10941,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845276</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
         <v>57720</v>
@@ -10972,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10981,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541274</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174268</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11016,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11026,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11058,7 +11068,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B90" t="n">
         <v>57720</v>
@@ -11098,10 +11108,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R90" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11133,7 +11143,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11143,7 +11153,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -11175,45 +11185,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845272</v>
+        <v>128845281</v>
       </c>
       <c r="B91" t="n">
-        <v>92205</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541629</v>
+        <v>541599</v>
       </c>
       <c r="R91" t="n">
-        <v>7174402</v>
+        <v>7174544</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11245,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11255,12 +11270,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11271,21 +11286,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845285</v>
+        <v>128845370</v>
       </c>
       <c r="B96" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,39 +11815,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541640</v>
+        <v>541222</v>
       </c>
       <c r="R96" t="n">
-        <v>7174353</v>
+        <v>7174409</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11879,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11889,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11921,10 +11916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845288</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11932,39 +11927,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541261</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174398</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11996,7 +11986,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12006,12 +11996,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12165,10 +12150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845370</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12176,34 +12161,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541222</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174409</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12235,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12245,12 +12235,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12277,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845382</v>
+        <v>128845288</v>
       </c>
       <c r="B100" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12288,34 +12278,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541041</v>
+        <v>541261</v>
       </c>
       <c r="R100" t="n">
-        <v>7174348</v>
+        <v>7174398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12347,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12357,7 +12352,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12384,7 +12384,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B101" t="n">
         <v>79124</v>
@@ -12419,10 +12419,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R101" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,7 +12491,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845269</v>
+        <v>128845376</v>
       </c>
       <c r="B102" t="n">
         <v>79124</v>
@@ -12526,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541134</v>
+        <v>541109</v>
       </c>
       <c r="R102" t="n">
-        <v>7174353</v>
+        <v>7174267</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,7 +12598,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845376</v>
+        <v>128845343</v>
       </c>
       <c r="B103" t="n">
         <v>79124</v>
@@ -12633,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541109</v>
+        <v>541074</v>
       </c>
       <c r="R103" t="n">
-        <v>7174267</v>
+        <v>7174298</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R16" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2630,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2646,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2657,10 +2677,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845363</v>
+        <v>128845286</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,34 +2688,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541623</v>
+        <v>541617</v>
       </c>
       <c r="R17" t="n">
-        <v>7174167</v>
+        <v>7174320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2752,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2737,7 +2762,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845325</v>
+        <v>128845356</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,21 +2805,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2799,10 +2829,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541618</v>
+        <v>541606</v>
       </c>
       <c r="R18" t="n">
-        <v>7174399</v>
+        <v>7174439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2864,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2844,12 +2874,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2860,21 +2885,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2891,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2912,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845360</v>
+        <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541640</v>
+        <v>541428</v>
       </c>
       <c r="R20" t="n">
-        <v>7174274</v>
+        <v>7174314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,7 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,6 +3104,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3118,7 +3138,7 @@
         <v>128845280</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3232,32 +3252,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845328</v>
+        <v>128845296</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>80163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3267,10 +3287,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541428</v>
+        <v>541359</v>
       </c>
       <c r="R22" t="n">
-        <v>7174314</v>
+        <v>7174394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3302,7 +3322,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3312,12 +3332,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3331,17 +3351,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3359,32 +3379,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845365</v>
+        <v>128845322</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>80170</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3414,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541453</v>
+        <v>541579</v>
       </c>
       <c r="R23" t="n">
-        <v>7174305</v>
+        <v>7174417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,7 +3449,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3439,7 +3459,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3450,6 +3475,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3466,32 +3506,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845296</v>
+        <v>128845360</v>
       </c>
       <c r="B24" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3501,10 +3541,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541359</v>
+        <v>541640</v>
       </c>
       <c r="R24" t="n">
-        <v>7174394</v>
+        <v>7174274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3536,7 +3576,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3546,12 +3586,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3562,21 +3597,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3593,32 +3613,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845322</v>
+        <v>128845365</v>
       </c>
       <c r="B25" t="n">
-        <v>80265</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3628,10 +3648,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541579</v>
+        <v>541453</v>
       </c>
       <c r="R25" t="n">
-        <v>7174417</v>
+        <v>7174305</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3663,7 +3683,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3673,12 +3693,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3689,21 +3704,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3723,7 +3723,7 @@
         <v>128845346</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845279</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,34 +3843,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541504</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3917,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3944,10 +3949,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845340</v>
+        <v>128845353</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3955,21 +3960,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3979,10 +3984,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541062</v>
+        <v>541612</v>
       </c>
       <c r="R28" t="n">
-        <v>7174293</v>
+        <v>7174586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,12 +4029,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4040,21 +4045,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4074,7 +4064,7 @@
         <v>128845359</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4181,7 +4171,7 @@
         <v>128845298</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845279</v>
+        <v>128845340</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4306,39 +4296,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541504</v>
+        <v>541062</v>
       </c>
       <c r="R31" t="n">
-        <v>7174451</v>
+        <v>7174293</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4370,7 +4355,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4380,12 +4365,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4396,6 +4381,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,7 +4415,7 @@
         <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128845332</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845341</v>
+        <v>128845297</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,34 +4657,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541131</v>
+        <v>541232</v>
       </c>
       <c r="R34" t="n">
-        <v>7174440</v>
+        <v>7174426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4716,7 +4724,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4726,7 +4734,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4756,7 +4769,7 @@
         <v>128845275</v>
       </c>
       <c r="B35" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4884,10 +4897,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B36" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,42 +4908,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R36" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4962,7 +4967,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4972,12 +4977,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5007,7 +5007,7 @@
         <v>128845293</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845327</v>
+        <v>128845339</v>
       </c>
       <c r="B38" t="n">
-        <v>91504</v>
+        <v>91531</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,34 +5132,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541654</v>
+        <v>541139</v>
       </c>
       <c r="R38" t="n">
-        <v>7174247</v>
+        <v>7174393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5194,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5204,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5215,6 +5218,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5248,10 +5252,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845367</v>
+        <v>128845362</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5283,10 +5287,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541394</v>
+        <v>541644</v>
       </c>
       <c r="R39" t="n">
-        <v>7174344</v>
+        <v>7174158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5318,7 +5322,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5328,12 +5332,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5360,10 +5359,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845339</v>
+        <v>128845367</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5371,37 +5370,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541139</v>
+        <v>541394</v>
       </c>
       <c r="R40" t="n">
-        <v>7174393</v>
+        <v>7174344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5433,7 +5429,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5443,12 +5439,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5457,24 +5453,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5491,10 +5471,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845362</v>
+        <v>128845361</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5526,10 +5506,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541644</v>
+        <v>541658</v>
       </c>
       <c r="R41" t="n">
-        <v>7174158</v>
+        <v>7174215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5561,7 +5541,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5571,7 +5551,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5598,10 +5578,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845361</v>
+        <v>128845295</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5609,34 +5589,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5668,7 +5660,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5678,7 +5670,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5705,10 +5702,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845283</v>
+        <v>128845327</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>91509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,39 +5713,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541605</v>
+        <v>541654</v>
       </c>
       <c r="R43" t="n">
-        <v>7174433</v>
+        <v>7174247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5780,7 +5772,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,12 +5782,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5806,6 +5798,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5822,10 +5829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845295</v>
+        <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>57880</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5833,46 +5840,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541394</v>
+        <v>541605</v>
       </c>
       <c r="R44" t="n">
-        <v>7174344</v>
+        <v>7174433</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B45" t="n">
-        <v>91504</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R45" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,12 +6026,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,21 +6037,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6073,10 +6053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845357</v>
+        <v>128845368</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6108,10 +6088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541607</v>
+        <v>541363</v>
       </c>
       <c r="R46" t="n">
-        <v>7174400</v>
+        <v>7174330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6143,7 +6123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6153,7 +6133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6180,10 +6160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845368</v>
+        <v>128845342</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6215,10 +6195,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541363</v>
+        <v>541011</v>
       </c>
       <c r="R47" t="n">
-        <v>7174330</v>
+        <v>7174346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6230,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,7 +6240,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6287,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845342</v>
+        <v>128845326</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6298,21 +6278,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6322,10 +6302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541011</v>
+        <v>541626</v>
       </c>
       <c r="R48" t="n">
-        <v>7174346</v>
+        <v>7174307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6337,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6347,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6378,6 +6363,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6397,7 +6397,7 @@
         <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845383</v>
+        <v>128845335</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541079</v>
+        <v>541610</v>
       </c>
       <c r="R50" t="n">
-        <v>7174333</v>
+        <v>7174521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6623,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845385</v>
+        <v>128845336</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,21 +6649,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6658,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541163</v>
+        <v>541251</v>
       </c>
       <c r="R51" t="n">
-        <v>7174329</v>
+        <v>7174388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6719,6 +6734,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6735,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845381</v>
+        <v>128845383</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6770,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541025</v>
+        <v>541079</v>
       </c>
       <c r="R52" t="n">
-        <v>7174364</v>
+        <v>7174333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6815,7 +6845,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6847,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845335</v>
+        <v>128845385</v>
       </c>
       <c r="B53" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6858,21 +6888,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6882,10 +6912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541610</v>
+        <v>541163</v>
       </c>
       <c r="R53" t="n">
-        <v>7174521</v>
+        <v>7174329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6917,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6927,12 +6957,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6943,21 +6973,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6974,10 +6989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845336</v>
+        <v>128845304</v>
       </c>
       <c r="B54" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6985,21 +7000,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7009,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541251</v>
+        <v>541120</v>
       </c>
       <c r="R54" t="n">
-        <v>7174388</v>
+        <v>7174297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7044,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7054,12 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7070,21 +7080,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7101,10 +7096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845304</v>
+        <v>128845369</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7136,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541120</v>
+        <v>541285</v>
       </c>
       <c r="R55" t="n">
-        <v>7174297</v>
+        <v>7174269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7171,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7181,7 +7176,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7208,10 +7203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845369</v>
+        <v>128845381</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7243,10 +7238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541285</v>
+        <v>541025</v>
       </c>
       <c r="R56" t="n">
-        <v>7174269</v>
+        <v>7174364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7278,7 +7273,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7288,7 +7283,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7315,10 +7315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845291</v>
+        <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541147</v>
+        <v>541254</v>
       </c>
       <c r="R57" t="n">
-        <v>7174441</v>
+        <v>7174391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845289</v>
+        <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541254</v>
+        <v>541147</v>
       </c>
       <c r="R58" t="n">
-        <v>7174391</v>
+        <v>7174441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845348</v>
+        <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541504</v>
+        <v>541462</v>
       </c>
       <c r="R59" t="n">
-        <v>7174451</v>
+        <v>7174528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7640,6 +7645,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7656,10 +7676,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845292</v>
+        <v>128845348</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7667,39 +7687,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541140</v>
+        <v>541504</v>
       </c>
       <c r="R60" t="n">
-        <v>7174441</v>
+        <v>7174451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7731,7 +7746,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7741,12 +7756,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7773,10 +7783,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845333</v>
+        <v>128845373</v>
       </c>
       <c r="B61" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7784,21 +7794,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7808,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541462</v>
+        <v>541143</v>
       </c>
       <c r="R61" t="n">
-        <v>7174528</v>
+        <v>7174450</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7853,12 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7869,21 +7874,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7900,10 +7890,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845373</v>
+        <v>128845354</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7935,10 +7925,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541143</v>
+        <v>541618</v>
       </c>
       <c r="R62" t="n">
-        <v>7174450</v>
+        <v>7174522</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7970,7 +7960,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7980,7 +7970,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8007,10 +7997,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845354</v>
+        <v>128845292</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8018,34 +8008,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541618</v>
+        <v>541140</v>
       </c>
       <c r="R63" t="n">
-        <v>7174522</v>
+        <v>7174441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8077,7 +8072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8087,7 +8082,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845284</v>
+        <v>128845282</v>
       </c>
       <c r="B64" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>541637</v>
       </c>
       <c r="R64" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8231,10 +8231,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845282</v>
+        <v>128845284</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>541637</v>
       </c>
       <c r="R65" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -8348,10 +8348,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845324</v>
+        <v>128845378</v>
       </c>
       <c r="B66" t="n">
-        <v>91504</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8359,21 +8359,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541610</v>
+        <v>541032</v>
       </c>
       <c r="R66" t="n">
-        <v>7174586</v>
+        <v>7174308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,12 +8428,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8444,21 +8439,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8478,7 +8458,7 @@
         <v>128845375</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8582,10 +8562,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845378</v>
+        <v>128845355</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8617,10 +8597,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541032</v>
+        <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174308</v>
+        <v>7174473</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8652,7 +8632,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8662,7 +8642,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8689,10 +8674,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845355</v>
+        <v>128845324</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8700,21 +8685,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8724,10 +8709,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R69" t="n">
-        <v>7174473</v>
+        <v>7174586</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8744,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,12 +8754,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8785,6 +8770,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8801,10 +8801,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845351</v>
+        <v>128845384</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541563</v>
+        <v>541112</v>
       </c>
       <c r="R70" t="n">
-        <v>7174549</v>
+        <v>7174350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,12 +8881,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8913,10 +8908,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128845384</v>
+        <v>128845364</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541112</v>
+        <v>541490</v>
       </c>
       <c r="R71" t="n">
-        <v>7174350</v>
+        <v>7174268</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8983,7 +8978,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8993,7 +8988,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9020,10 +9015,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845364</v>
+        <v>128845351</v>
       </c>
       <c r="B72" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9055,10 +9050,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541490</v>
+        <v>541563</v>
       </c>
       <c r="R72" t="n">
-        <v>7174268</v>
+        <v>7174549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9090,7 +9085,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9100,7 +9095,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9127,10 +9127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845379</v>
+        <v>128845358</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540962</v>
+        <v>541633</v>
       </c>
       <c r="R73" t="n">
-        <v>7174330</v>
+        <v>7174358</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,12 +9207,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9239,10 +9234,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845358</v>
+        <v>128845300</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9274,10 +9269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541633</v>
+        <v>541095</v>
       </c>
       <c r="R74" t="n">
-        <v>7174358</v>
+        <v>7174393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9309,7 +9304,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9319,7 +9314,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9346,10 +9341,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845300</v>
+        <v>128845379</v>
       </c>
       <c r="B75" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541095</v>
+        <v>540962</v>
       </c>
       <c r="R75" t="n">
-        <v>7174393</v>
+        <v>7174330</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9416,7 +9411,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9426,7 +9421,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845372</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>128845377</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>128845271</v>
       </c>
       <c r="B78" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B79" t="n">
-        <v>91504</v>
+        <v>57883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,34 +9805,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R79" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9886,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,21 +9902,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9921,10 +9918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845329</v>
       </c>
       <c r="B80" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9932,21 +9929,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9956,10 +9953,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541141</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9991,7 +9988,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10001,7 +9998,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10012,6 +10014,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10031,7 +10048,7 @@
         <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10140,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845294</v>
+        <v>128845371</v>
       </c>
       <c r="B82" t="n">
-        <v>57880</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10151,46 +10168,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541544</v>
+        <v>541216</v>
       </c>
       <c r="R82" t="n">
-        <v>7174513</v>
+        <v>7174399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10227,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10237,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Synobs</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>128845352</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>128845347</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>128845302</v>
       </c>
       <c r="B86" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845344</v>
+        <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>92210</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541312</v>
+        <v>541629</v>
       </c>
       <c r="R87" t="n">
-        <v>7174300</v>
+        <v>7174402</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,7 +10797,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10808,6 +10813,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10824,32 +10844,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845272</v>
+        <v>128845344</v>
       </c>
       <c r="B88" t="n">
-        <v>92205</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10859,10 +10879,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541629</v>
+        <v>541312</v>
       </c>
       <c r="R88" t="n">
-        <v>7174402</v>
+        <v>7174300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10894,7 +10914,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10904,12 +10924,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10920,21 +10935,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10954,7 +10954,7 @@
         <v>128845278</v>
       </c>
       <c r="B89" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11068,10 +11068,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845276</v>
+        <v>128845281</v>
       </c>
       <c r="B90" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541274</v>
+        <v>541599</v>
       </c>
       <c r="R90" t="n">
-        <v>7174268</v>
+        <v>7174544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -11185,10 +11185,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R91" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -11305,7 +11305,7 @@
         <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845370</v>
+        <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541222</v>
+        <v>541271</v>
       </c>
       <c r="R96" t="n">
-        <v>7174409</v>
+        <v>7174269</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,6 +11900,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11916,10 +11931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11951,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11986,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11996,7 +12011,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12023,10 +12043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845331</v>
+        <v>128845382</v>
       </c>
       <c r="B98" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12034,21 +12054,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12058,10 +12078,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541271</v>
+        <v>541041</v>
       </c>
       <c r="R98" t="n">
-        <v>7174269</v>
+        <v>7174348</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12093,7 +12113,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12103,12 +12123,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12119,21 +12134,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12150,10 +12150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845269</v>
+        <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,34 +12395,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541134</v>
+        <v>541322</v>
       </c>
       <c r="R101" t="n">
-        <v>7174353</v>
+        <v>7174361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,10 +12501,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845376</v>
+        <v>128845343</v>
       </c>
       <c r="B102" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541109</v>
+        <v>541074</v>
       </c>
       <c r="R102" t="n">
-        <v>7174267</v>
+        <v>7174298</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12571,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12581,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,10 +12608,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12633,10 +12643,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R103" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12678,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12688,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12705,10 +12715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845277</v>
+        <v>128845376</v>
       </c>
       <c r="B104" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12716,39 +12726,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541322</v>
+        <v>541109</v>
       </c>
       <c r="R104" t="n">
-        <v>7174361</v>
+        <v>7174267</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12790,12 +12795,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>91509</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R105" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91504</v>
+        <v>91531</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R106" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13079,7 +13079,7 @@
         <v>128845366</v>
       </c>
       <c r="B107" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>128845350</v>
       </c>
       <c r="B108" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>128845349</v>
       </c>
       <c r="B109" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>128845345</v>
       </c>
       <c r="B110" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99895</v>
+        <v>99902</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845325</v>
+        <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541618</v>
+        <v>541606</v>
       </c>
       <c r="R16" t="n">
-        <v>7174399</v>
+        <v>7174439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,12 +2630,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,21 +2641,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2677,10 +2657,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,39 +2668,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R17" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,7 +2727,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2762,12 +2737,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2794,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>91516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2805,21 +2775,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2829,10 +2799,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R18" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2864,7 +2834,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2874,7 +2844,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,6 +2860,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2901,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845363</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541623</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174167</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,32 +3008,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845328</v>
+        <v>128845296</v>
       </c>
       <c r="B20" t="n">
-        <v>91516</v>
+        <v>80168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541428</v>
+        <v>541359</v>
       </c>
       <c r="R20" t="n">
-        <v>7174314</v>
+        <v>7174394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3135,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845360</v>
+        <v>128845322</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541640</v>
+        <v>541579</v>
       </c>
       <c r="R21" t="n">
-        <v>7174274</v>
+        <v>7174417</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,7 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3226,6 +3231,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3242,7 +3262,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845365</v>
+        <v>128845360</v>
       </c>
       <c r="B22" t="n">
         <v>79034</v>
@@ -3277,10 +3297,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541453</v>
+        <v>541640</v>
       </c>
       <c r="R22" t="n">
-        <v>7174305</v>
+        <v>7174274</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3312,7 +3332,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3322,7 +3342,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3349,7 +3369,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845346</v>
+        <v>128845365</v>
       </c>
       <c r="B23" t="n">
         <v>79034</v>
@@ -3384,10 +3404,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541373</v>
+        <v>541453</v>
       </c>
       <c r="R23" t="n">
-        <v>7174407</v>
+        <v>7174305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3419,7 +3439,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3429,12 +3449,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3461,32 +3476,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845296</v>
+        <v>128845346</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3511,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541359</v>
+        <v>541373</v>
       </c>
       <c r="R24" t="n">
-        <v>7174394</v>
+        <v>7174407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3531,7 +3546,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3541,12 +3556,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3557,21 +3572,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3588,45 +3588,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845322</v>
+        <v>128845280</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541579</v>
+        <v>541574</v>
       </c>
       <c r="R25" t="n">
-        <v>7174417</v>
+        <v>7174569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3658,7 +3663,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3668,12 +3673,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,21 +3689,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,10 +3705,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845280</v>
+        <v>128845328</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>91516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,39 +3716,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541574</v>
+        <v>541428</v>
       </c>
       <c r="R26" t="n">
-        <v>7174569</v>
+        <v>7174314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3775,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3785,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3816,6 +3801,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845323</v>
+        <v>128845353</v>
       </c>
       <c r="B27" t="n">
-        <v>98985</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541182</v>
+        <v>541612</v>
       </c>
       <c r="R27" t="n">
-        <v>7174332</v>
+        <v>7174586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3939,7 +3944,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845353</v>
+        <v>128845359</v>
       </c>
       <c r="B28" t="n">
         <v>79034</v>
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541612</v>
+        <v>541617</v>
       </c>
       <c r="R28" t="n">
-        <v>7174586</v>
+        <v>7174319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4009,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4019,12 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,10 +4051,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845359</v>
+        <v>128845340</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541617</v>
+        <v>541062</v>
       </c>
       <c r="R29" t="n">
-        <v>7174319</v>
+        <v>7174293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4131,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4142,6 +4147,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4392,32 +4412,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845340</v>
+        <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>98985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4427,10 +4447,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541062</v>
+        <v>541182</v>
       </c>
       <c r="R32" t="n">
-        <v>7174293</v>
+        <v>7174332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4472,12 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4488,21 +4503,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4650,10 +4650,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4661,42 +4661,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R34" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4728,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4738,12 +4730,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,10 +4757,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845332</v>
+        <v>128845293</v>
       </c>
       <c r="B35" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4781,34 +4768,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541284</v>
+        <v>541157</v>
       </c>
       <c r="R35" t="n">
-        <v>7174287</v>
+        <v>7174382</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4840,7 +4832,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4850,12 +4842,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,21 +4858,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4897,10 +4874,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845341</v>
+        <v>128845332</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4908,21 +4885,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4932,10 +4909,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541131</v>
+        <v>541284</v>
       </c>
       <c r="R36" t="n">
-        <v>7174440</v>
+        <v>7174287</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4967,7 +4944,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4977,7 +4954,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4988,6 +4970,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5004,10 +5001,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845293</v>
+        <v>128845297</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5015,16 +5012,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5033,21 +5030,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541157</v>
+        <v>541232</v>
       </c>
       <c r="R37" t="n">
-        <v>7174382</v>
+        <v>7174426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845383</v>
+        <v>128845289</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,34 +6522,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541079</v>
+        <v>541254</v>
       </c>
       <c r="R50" t="n">
-        <v>7174333</v>
+        <v>7174391</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6586,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6596,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6623,10 +6628,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845385</v>
+        <v>128845291</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,34 +6639,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541163</v>
+        <v>541147</v>
       </c>
       <c r="R51" t="n">
-        <v>7174329</v>
+        <v>7174441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6703,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,12 +6713,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6735,10 +6745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845304</v>
+        <v>128845335</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6746,21 +6756,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6770,10 +6780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541120</v>
+        <v>541610</v>
       </c>
       <c r="R52" t="n">
-        <v>7174297</v>
+        <v>7174521</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6815,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6815,7 +6825,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6826,6 +6841,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6842,10 +6872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845369</v>
+        <v>128845336</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6853,21 +6883,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6877,10 +6907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541285</v>
+        <v>541251</v>
       </c>
       <c r="R53" t="n">
-        <v>7174269</v>
+        <v>7174388</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6912,7 +6942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6922,7 +6952,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6933,6 +6968,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6949,7 +6999,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845381</v>
+        <v>128845383</v>
       </c>
       <c r="B54" t="n">
         <v>79034</v>
@@ -6984,10 +7034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541025</v>
+        <v>541079</v>
       </c>
       <c r="R54" t="n">
-        <v>7174364</v>
+        <v>7174333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7019,7 +7069,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7029,7 +7079,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7061,10 +7111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845335</v>
+        <v>128845385</v>
       </c>
       <c r="B55" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7072,21 +7122,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7096,10 +7146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541610</v>
+        <v>541163</v>
       </c>
       <c r="R55" t="n">
-        <v>7174521</v>
+        <v>7174329</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7131,7 +7181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7141,12 +7191,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7157,21 +7207,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7188,10 +7223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845336</v>
+        <v>128845304</v>
       </c>
       <c r="B56" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7199,21 +7234,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7223,10 +7258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541251</v>
+        <v>541120</v>
       </c>
       <c r="R56" t="n">
-        <v>7174388</v>
+        <v>7174297</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7258,7 +7293,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7268,12 +7303,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7284,21 +7314,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7315,10 +7330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845289</v>
+        <v>128845369</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7326,39 +7341,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541254</v>
+        <v>541285</v>
       </c>
       <c r="R57" t="n">
-        <v>7174391</v>
+        <v>7174269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7400,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,12 +7410,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7432,10 +7437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845291</v>
+        <v>128845381</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7443,39 +7448,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541147</v>
+        <v>541025</v>
       </c>
       <c r="R58" t="n">
-        <v>7174441</v>
+        <v>7174364</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,7 +7549,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B59" t="n">
         <v>79034</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R59" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7656,7 +7656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845354</v>
+        <v>128845373</v>
       </c>
       <c r="B60" t="n">
         <v>79034</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541618</v>
+        <v>541143</v>
       </c>
       <c r="R60" t="n">
-        <v>7174522</v>
+        <v>7174450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7763,10 +7763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845333</v>
+        <v>128845354</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7774,21 +7774,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541462</v>
+        <v>541618</v>
       </c>
       <c r="R61" t="n">
-        <v>7174528</v>
+        <v>7174522</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7843,12 +7843,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7859,21 +7854,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7890,10 +7870,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845348</v>
+        <v>128845333</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7901,21 +7881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7925,10 +7905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541504</v>
+        <v>541462</v>
       </c>
       <c r="R62" t="n">
-        <v>7174451</v>
+        <v>7174528</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7960,7 +7940,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7970,7 +7950,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7981,6 +7966,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845294</v>
+        <v>128845380</v>
       </c>
       <c r="B79" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,46 +9805,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541544</v>
+        <v>541027</v>
       </c>
       <c r="R79" t="n">
-        <v>7174513</v>
+        <v>7174356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9876,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9886,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9918,10 +9906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B80" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9929,21 +9917,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9953,10 +9941,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R80" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9988,7 +9976,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9998,12 +9986,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10014,21 +9997,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10045,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>91516</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10056,21 +10024,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10080,10 +10048,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R81" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10115,7 +10083,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10125,12 +10093,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10141,6 +10109,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10157,10 +10140,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845371</v>
+        <v>128845294</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,34 +10151,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541216</v>
+        <v>541544</v>
       </c>
       <c r="R82" t="n">
-        <v>7174399</v>
+        <v>7174513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10227,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10237,7 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10717,32 +10717,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845272</v>
+        <v>128845344</v>
       </c>
       <c r="B87" t="n">
-        <v>92218</v>
+        <v>79034</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541629</v>
+        <v>541312</v>
       </c>
       <c r="R87" t="n">
-        <v>7174402</v>
+        <v>7174300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,12 +10797,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10813,21 +10808,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10844,50 +10824,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>92218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10919,7 +10894,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10929,12 +10904,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10945,6 +10920,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10961,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845276</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
         <v>57723</v>
@@ -10992,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11001,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541274</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174268</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11036,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11046,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11078,7 +11068,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B90" t="n">
         <v>57723</v>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R90" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11153,7 +11143,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11163,7 +11153,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -11195,10 +11185,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845344</v>
+        <v>128845281</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11206,34 +11196,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541312</v>
+        <v>541599</v>
       </c>
       <c r="R91" t="n">
-        <v>7174300</v>
+        <v>7174544</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11265,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11275,7 +11270,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11302,48 +11302,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845274</v>
+        <v>128845338</v>
       </c>
       <c r="B92" t="n">
-        <v>92218</v>
+        <v>91538</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541116</v>
+        <v>541232</v>
       </c>
       <c r="R92" t="n">
-        <v>7174272</v>
+        <v>7174426</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11375,7 +11372,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11385,12 +11382,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11399,7 +11396,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11433,45 +11429,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845270</v>
+        <v>128845287</v>
       </c>
       <c r="B93" t="n">
-        <v>92218</v>
+        <v>57723</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541134</v>
+        <v>541428</v>
       </c>
       <c r="R93" t="n">
-        <v>7174353</v>
+        <v>7174314</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11503,7 +11504,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11513,12 +11514,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11529,21 +11530,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11560,45 +11546,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845338</v>
+        <v>128845274</v>
       </c>
       <c r="B94" t="n">
-        <v>91538</v>
+        <v>92218</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541232</v>
+        <v>541116</v>
       </c>
       <c r="R94" t="n">
-        <v>7174426</v>
+        <v>7174272</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11630,7 +11619,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11640,12 +11629,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11654,6 +11643,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11687,50 +11677,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845287</v>
+        <v>128845270</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>92218</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541428</v>
+        <v>541134</v>
       </c>
       <c r="R95" t="n">
-        <v>7174314</v>
+        <v>7174353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11762,7 +11747,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11772,12 +11757,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11788,6 +11773,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91538</v>
+        <v>91516</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R105" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91516</v>
+        <v>91538</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R106" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD106" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845356</v>
+        <v>128845286</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,34 +2561,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541606</v>
+        <v>541617</v>
       </c>
       <c r="R16" t="n">
-        <v>7174439</v>
+        <v>7174320</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2625,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2635,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2657,10 +2667,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845363</v>
+        <v>128845325</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>91519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,21 +2678,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2692,10 +2702,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541623</v>
+        <v>541618</v>
       </c>
       <c r="R17" t="n">
-        <v>7174167</v>
+        <v>7174399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2737,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2737,7 +2747,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2748,6 +2763,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2764,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845325</v>
+        <v>128845356</v>
       </c>
       <c r="B18" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,21 +2805,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2799,10 +2829,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541618</v>
+        <v>541606</v>
       </c>
       <c r="R18" t="n">
-        <v>7174399</v>
+        <v>7174439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2864,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2844,12 +2874,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2860,21 +2885,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2891,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2912,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,45 +3008,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845296</v>
+        <v>128845280</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541359</v>
+        <v>541574</v>
       </c>
       <c r="R20" t="n">
-        <v>7174394</v>
+        <v>7174569</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3083,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3093,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3104,21 +3109,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3135,32 +3125,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845322</v>
+        <v>128845328</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>91519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3160,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541579</v>
+        <v>541428</v>
       </c>
       <c r="R21" t="n">
-        <v>7174417</v>
+        <v>7174314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3195,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,12 +3205,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3234,17 +3224,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3476,32 +3466,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845346</v>
+        <v>128845296</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3511,10 +3501,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541373</v>
+        <v>541359</v>
       </c>
       <c r="R24" t="n">
-        <v>7174407</v>
+        <v>7174394</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3546,7 +3536,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3556,12 +3546,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,6 +3562,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3588,50 +3593,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845280</v>
+        <v>128845322</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541574</v>
+        <v>541579</v>
       </c>
       <c r="R25" t="n">
-        <v>7174569</v>
+        <v>7174417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3689,6 +3689,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3705,10 +3720,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845328</v>
+        <v>128845346</v>
       </c>
       <c r="B26" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3716,21 +3731,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3740,10 +3755,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541428</v>
+        <v>541373</v>
       </c>
       <c r="R26" t="n">
-        <v>7174314</v>
+        <v>7174407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845340</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541062</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,6 +3928,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3944,32 +3959,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845359</v>
+        <v>128845323</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>98990</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3979,10 +3994,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541617</v>
+        <v>541182</v>
       </c>
       <c r="R28" t="n">
-        <v>7174319</v>
+        <v>7174332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,7 +4029,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4039,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,10 +4066,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845340</v>
+        <v>128845353</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4062,21 +4077,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4086,10 +4101,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541062</v>
+        <v>541612</v>
       </c>
       <c r="R29" t="n">
-        <v>7174293</v>
+        <v>7174586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4136,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,12 +4146,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4147,21 +4162,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845279</v>
+        <v>128845359</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,39 +4189,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541504</v>
+        <v>541617</v>
       </c>
       <c r="R30" t="n">
-        <v>7174451</v>
+        <v>7174319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,7 +4248,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4263,12 +4258,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4412,45 +4402,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845323</v>
+        <v>128845279</v>
       </c>
       <c r="B32" t="n">
-        <v>98985</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541182</v>
+        <v>541504</v>
       </c>
       <c r="R32" t="n">
-        <v>7174332</v>
+        <v>7174451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4492,7 +4487,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4519,48 +4519,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845275</v>
+        <v>128845332</v>
       </c>
       <c r="B33" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541057</v>
+        <v>541284</v>
       </c>
       <c r="R33" t="n">
-        <v>7174336</v>
+        <v>7174287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,12 +4599,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4616,7 +4613,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4650,45 +4646,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845341</v>
+        <v>128845275</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>92223</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541131</v>
+        <v>541057</v>
       </c>
       <c r="R34" t="n">
-        <v>7174440</v>
+        <v>7174336</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4720,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4730,7 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4739,8 +4743,24 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4757,10 +4777,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845293</v>
+        <v>128845341</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4768,39 +4788,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541157</v>
+        <v>541131</v>
       </c>
       <c r="R35" t="n">
-        <v>7174382</v>
+        <v>7174440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4832,7 +4847,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4842,12 +4857,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4874,10 +4884,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845332</v>
+        <v>128845297</v>
       </c>
       <c r="B36" t="n">
-        <v>91538</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4885,34 +4895,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541284</v>
+        <v>541232</v>
       </c>
       <c r="R36" t="n">
-        <v>7174287</v>
+        <v>7174426</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4944,7 +4962,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4954,12 +4972,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4970,21 +4988,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5001,10 +5004,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845297</v>
+        <v>128845293</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5012,16 +5015,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5030,24 +5033,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541232</v>
+        <v>541157</v>
       </c>
       <c r="R37" t="n">
-        <v>7174426</v>
+        <v>7174382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5124,7 +5124,7 @@
         <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845339</v>
+        <v>128845283</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,37 +5259,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541139</v>
+        <v>541605</v>
       </c>
       <c r="R39" t="n">
-        <v>7174393</v>
+        <v>7174433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5321,7 +5323,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5331,12 +5333,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5345,24 +5347,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,10 +5365,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845362</v>
+        <v>128845339</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5390,34 +5376,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541644</v>
+        <v>541139</v>
       </c>
       <c r="R40" t="n">
-        <v>7174158</v>
+        <v>7174393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5449,7 +5438,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5459,7 +5448,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5468,8 +5462,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5486,7 +5496,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845367</v>
+        <v>128845362</v>
       </c>
       <c r="B41" t="n">
         <v>79034</v>
@@ -5521,10 +5531,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541394</v>
+        <v>541644</v>
       </c>
       <c r="R41" t="n">
-        <v>7174344</v>
+        <v>7174158</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5556,7 +5566,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5566,12 +5576,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5598,7 +5603,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845361</v>
+        <v>128845367</v>
       </c>
       <c r="B42" t="n">
         <v>79034</v>
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5668,7 +5673,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5678,7 +5683,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5705,10 +5715,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845283</v>
+        <v>128845361</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,39 +5726,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541605</v>
+        <v>541658</v>
       </c>
       <c r="R43" t="n">
-        <v>7174433</v>
+        <v>7174215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5780,7 +5785,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,12 +5795,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B45" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,21 +5957,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R45" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,12 +6026,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,21 +6037,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6073,10 +6053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845290</v>
+        <v>128845368</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6084,39 +6064,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541211</v>
+        <v>541363</v>
       </c>
       <c r="R46" t="n">
-        <v>7174387</v>
+        <v>7174330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6148,7 +6123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6158,12 +6133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6190,7 +6160,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845357</v>
+        <v>128845342</v>
       </c>
       <c r="B47" t="n">
         <v>79034</v>
@@ -6225,10 +6195,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541607</v>
+        <v>541011</v>
       </c>
       <c r="R47" t="n">
-        <v>7174400</v>
+        <v>7174346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6260,7 +6230,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6270,7 +6240,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6297,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845368</v>
+        <v>128845326</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>91519</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6308,21 +6278,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6332,10 +6302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541363</v>
+        <v>541626</v>
       </c>
       <c r="R48" t="n">
-        <v>7174330</v>
+        <v>7174307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6367,7 +6337,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6377,7 +6347,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6388,6 +6363,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6404,10 +6394,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845342</v>
+        <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6415,34 +6405,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541011</v>
+        <v>541211</v>
       </c>
       <c r="R49" t="n">
-        <v>7174346</v>
+        <v>7174387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6474,7 +6469,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6484,7 +6479,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845289</v>
+        <v>128845336</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,39 +6522,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541254</v>
+        <v>541251</v>
       </c>
       <c r="R50" t="n">
-        <v>7174391</v>
+        <v>7174388</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6586,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6596,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6612,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6628,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845291</v>
+        <v>128845335</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6639,39 +6649,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541147</v>
+        <v>541610</v>
       </c>
       <c r="R51" t="n">
-        <v>7174441</v>
+        <v>7174521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6703,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6713,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6729,6 +6734,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6745,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845335</v>
+        <v>128845383</v>
       </c>
       <c r="B52" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6756,21 +6776,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6780,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541610</v>
+        <v>541079</v>
       </c>
       <c r="R52" t="n">
-        <v>7174521</v>
+        <v>7174333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6815,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6825,12 +6845,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6841,21 +6861,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6872,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845336</v>
+        <v>128845385</v>
       </c>
       <c r="B53" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,21 +6888,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541251</v>
+        <v>541163</v>
       </c>
       <c r="R53" t="n">
-        <v>7174388</v>
+        <v>7174329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6952,12 +6957,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6968,21 +6973,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6999,7 +6989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845383</v>
+        <v>128845304</v>
       </c>
       <c r="B54" t="n">
         <v>79034</v>
@@ -7034,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541079</v>
+        <v>541120</v>
       </c>
       <c r="R54" t="n">
-        <v>7174333</v>
+        <v>7174297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7069,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7079,12 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7111,7 +7096,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845385</v>
+        <v>128845369</v>
       </c>
       <c r="B55" t="n">
         <v>79034</v>
@@ -7146,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541163</v>
+        <v>541285</v>
       </c>
       <c r="R55" t="n">
-        <v>7174329</v>
+        <v>7174269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7191,12 +7176,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7223,7 +7203,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845304</v>
+        <v>128845381</v>
       </c>
       <c r="B56" t="n">
         <v>79034</v>
@@ -7258,10 +7238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541120</v>
+        <v>541025</v>
       </c>
       <c r="R56" t="n">
-        <v>7174297</v>
+        <v>7174364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7293,7 +7273,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7303,7 +7283,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7330,10 +7315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845369</v>
+        <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7341,34 +7326,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541285</v>
+        <v>541254</v>
       </c>
       <c r="R57" t="n">
-        <v>7174269</v>
+        <v>7174391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7400,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7410,7 +7400,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7437,10 +7432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845381</v>
+        <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7448,34 +7443,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541025</v>
+        <v>541147</v>
       </c>
       <c r="R58" t="n">
-        <v>7174364</v>
+        <v>7174441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845348</v>
+        <v>128845292</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,34 +7560,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541504</v>
+        <v>541140</v>
       </c>
       <c r="R59" t="n">
-        <v>7174451</v>
+        <v>7174441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7624,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7634,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7656,10 +7666,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845333</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7667,21 +7677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7691,10 +7701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541462</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174528</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7736,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7746,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7747,6 +7762,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7763,7 +7793,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845354</v>
+        <v>128845348</v>
       </c>
       <c r="B61" t="n">
         <v>79034</v>
@@ -7798,10 +7828,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541618</v>
+        <v>541504</v>
       </c>
       <c r="R61" t="n">
-        <v>7174522</v>
+        <v>7174451</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7833,7 +7863,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7843,7 +7873,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7870,10 +7900,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845333</v>
+        <v>128845373</v>
       </c>
       <c r="B62" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7881,21 +7911,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7905,10 +7935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541462</v>
+        <v>541143</v>
       </c>
       <c r="R62" t="n">
-        <v>7174528</v>
+        <v>7174450</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7940,7 +7970,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7950,12 +7980,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7966,21 +7991,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7997,10 +8007,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845292</v>
+        <v>128845354</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8008,39 +8018,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541140</v>
+        <v>541618</v>
       </c>
       <c r="R63" t="n">
-        <v>7174441</v>
+        <v>7174522</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8082,12 +8087,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845324</v>
+        <v>128845284</v>
       </c>
       <c r="B64" t="n">
-        <v>91516</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,34 +8125,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R64" t="n">
-        <v>7174586</v>
+        <v>7174351</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8189,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,12 +8199,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8210,21 +8215,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8241,10 +8231,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845378</v>
+        <v>128845324</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>91519</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,21 +8242,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8276,10 +8266,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541032</v>
+        <v>541610</v>
       </c>
       <c r="R65" t="n">
-        <v>7174308</v>
+        <v>7174586</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8311,7 +8301,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8321,7 +8311,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8332,6 +8327,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8348,7 +8358,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845375</v>
+        <v>128845378</v>
       </c>
       <c r="B66" t="n">
         <v>79034</v>
@@ -8383,10 +8393,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541136</v>
+        <v>541032</v>
       </c>
       <c r="R66" t="n">
-        <v>7174402</v>
+        <v>7174308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8428,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,7 +8438,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8455,7 +8465,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845355</v>
+        <v>128845375</v>
       </c>
       <c r="B67" t="n">
         <v>79034</v>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R67" t="n">
-        <v>7174473</v>
+        <v>7174402</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8525,7 +8535,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8535,12 +8545,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8567,10 +8572,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845284</v>
+        <v>128845355</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8578,29 +8583,24 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8610,7 +8610,7 @@
         <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>91519</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,21 +9805,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,6 +9890,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9906,7 +9921,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845380</v>
       </c>
       <c r="B80" t="n">
         <v>79034</v>
@@ -9941,10 +9956,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541027</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9976,7 +9991,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9986,7 +10001,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10013,10 +10033,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B81" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,21 +10044,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10048,10 +10068,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10083,7 +10103,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10093,12 +10113,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10109,21 +10124,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10717,10 +10717,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845344</v>
+        <v>128845278</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10728,34 +10728,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541312</v>
+        <v>541418</v>
       </c>
       <c r="R87" t="n">
-        <v>7174300</v>
+        <v>7174396</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10792,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,7 +10802,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10824,45 +10834,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845272</v>
+        <v>128845281</v>
       </c>
       <c r="B88" t="n">
-        <v>92218</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541629</v>
+        <v>541599</v>
       </c>
       <c r="R88" t="n">
-        <v>7174402</v>
+        <v>7174544</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10894,7 +10909,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10904,12 +10919,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10920,21 +10935,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10951,50 +10951,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>92223</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11021,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11031,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11052,6 +11047,21 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11068,10 +11078,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845276</v>
+        <v>128845344</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11079,39 +11089,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541274</v>
+        <v>541312</v>
       </c>
       <c r="R90" t="n">
-        <v>7174268</v>
+        <v>7174300</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11143,7 +11148,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11153,12 +11158,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11185,7 +11185,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B91" t="n">
         <v>57723</v>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R91" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -11302,45 +11302,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845338</v>
+        <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>91538</v>
+        <v>92223</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541232</v>
+        <v>541116</v>
       </c>
       <c r="R92" t="n">
-        <v>7174426</v>
+        <v>7174272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11372,7 +11375,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11382,12 +11385,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11396,6 +11399,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11429,50 +11433,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845287</v>
+        <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>57723</v>
+        <v>92223</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541428</v>
+        <v>541134</v>
       </c>
       <c r="R93" t="n">
-        <v>7174314</v>
+        <v>7174353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11504,7 +11503,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11514,12 +11513,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11530,6 +11529,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11546,48 +11560,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845274</v>
+        <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541116</v>
+        <v>541232</v>
       </c>
       <c r="R94" t="n">
-        <v>7174272</v>
+        <v>7174426</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11619,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11629,12 +11640,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11643,7 +11654,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11677,45 +11687,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845270</v>
+        <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>92218</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541134</v>
+        <v>541428</v>
       </c>
       <c r="R95" t="n">
-        <v>7174353</v>
+        <v>7174314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,7 +11762,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11757,12 +11772,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11773,21 +11788,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11807,7 +11807,7 @@
         <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
         <v>57723</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,7 +12267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
         <v>57723</v>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12825,7 +12825,7 @@
         <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99910</v>
+        <v>99915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845286</v>
+        <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,39 +2561,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541617</v>
+        <v>541606</v>
       </c>
       <c r="R16" t="n">
-        <v>7174320</v>
+        <v>7174439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2625,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2635,12 +2630,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2667,10 +2657,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845325</v>
+        <v>128845363</v>
       </c>
       <c r="B17" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2678,21 +2668,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2702,10 +2692,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541618</v>
+        <v>541623</v>
       </c>
       <c r="R17" t="n">
-        <v>7174399</v>
+        <v>7174167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2737,7 +2727,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2747,12 +2737,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2763,21 +2748,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2794,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2805,21 +2775,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2829,10 +2799,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R18" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2864,7 +2834,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2874,7 +2844,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,6 +2860,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2901,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845363</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541623</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174167</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845280</v>
+        <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,39 +3019,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541574</v>
+        <v>541428</v>
       </c>
       <c r="R20" t="n">
-        <v>7174569</v>
+        <v>7174314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3083,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3093,12 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3109,6 +3104,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3125,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845328</v>
+        <v>128845296</v>
       </c>
       <c r="B21" t="n">
-        <v>91519</v>
+        <v>80169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3160,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541428</v>
+        <v>541359</v>
       </c>
       <c r="R21" t="n">
-        <v>7174314</v>
+        <v>7174394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3195,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3205,12 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3224,17 +3234,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3252,32 +3262,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845360</v>
+        <v>128845322</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>80176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3287,10 +3297,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541640</v>
+        <v>541579</v>
       </c>
       <c r="R22" t="n">
-        <v>7174274</v>
+        <v>7174417</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3322,7 +3332,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3332,7 +3342,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3343,6 +3358,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3359,10 +3389,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845365</v>
+        <v>128845360</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3394,10 +3424,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541453</v>
+        <v>541640</v>
       </c>
       <c r="R23" t="n">
-        <v>7174305</v>
+        <v>7174274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,7 +3459,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3439,7 +3469,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3466,32 +3496,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845296</v>
+        <v>128845365</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3501,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541359</v>
+        <v>541453</v>
       </c>
       <c r="R24" t="n">
-        <v>7174394</v>
+        <v>7174305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3536,7 +3566,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3546,12 +3576,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3562,21 +3587,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3593,32 +3603,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845322</v>
+        <v>128845346</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3628,10 +3638,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541579</v>
+        <v>541373</v>
       </c>
       <c r="R25" t="n">
-        <v>7174417</v>
+        <v>7174407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3663,7 +3673,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3673,12 +3683,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3689,21 +3699,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3720,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845346</v>
+        <v>128845280</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3731,34 +3726,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541373</v>
+        <v>541574</v>
       </c>
       <c r="R26" t="n">
-        <v>7174407</v>
+        <v>7174569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845340</v>
+        <v>128845353</v>
       </c>
       <c r="B27" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541062</v>
+        <v>541612</v>
       </c>
       <c r="R27" t="n">
-        <v>7174293</v>
+        <v>7174586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,21 +3928,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3959,32 +3944,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845323</v>
+        <v>128845359</v>
       </c>
       <c r="B28" t="n">
-        <v>98990</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3994,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541182</v>
+        <v>541617</v>
       </c>
       <c r="R28" t="n">
-        <v>7174332</v>
+        <v>7174319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4029,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4039,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4066,10 +4051,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845353</v>
+        <v>128845279</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4077,34 +4062,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541612</v>
+        <v>541504</v>
       </c>
       <c r="R29" t="n">
-        <v>7174586</v>
+        <v>7174451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4136,7 +4126,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4146,12 +4136,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,32 +4168,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845359</v>
+        <v>128845323</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>98993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4213,10 +4203,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541617</v>
+        <v>541182</v>
       </c>
       <c r="R30" t="n">
-        <v>7174319</v>
+        <v>7174332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4248,7 +4238,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4258,7 +4248,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4402,10 +4392,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845279</v>
+        <v>128845340</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4413,39 +4403,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541504</v>
+        <v>541062</v>
       </c>
       <c r="R32" t="n">
-        <v>7174451</v>
+        <v>7174293</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4477,7 +4462,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,12 +4472,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4503,6 +4488,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R33" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,12 +4599,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4615,21 +4610,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4646,37 +4626,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845275</v>
+        <v>128845297</v>
       </c>
       <c r="B34" t="n">
-        <v>92223</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4684,10 +4669,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541057</v>
+        <v>541232</v>
       </c>
       <c r="R34" t="n">
-        <v>7174336</v>
+        <v>7174426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4704,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4714,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4743,24 +4728,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4777,10 +4746,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845341</v>
+        <v>128845332</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4788,21 +4757,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4812,10 +4781,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541131</v>
+        <v>541284</v>
       </c>
       <c r="R35" t="n">
-        <v>7174440</v>
+        <v>7174287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4847,7 +4816,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4857,7 +4826,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4868,6 +4842,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4884,42 +4873,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845297</v>
+        <v>128845275</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>92226</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4927,10 +4911,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541232</v>
+        <v>541057</v>
       </c>
       <c r="R36" t="n">
-        <v>7174426</v>
+        <v>7174336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4962,7 +4946,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4972,12 +4956,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4986,8 +4970,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5124,7 +5124,7 @@
         <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845339</v>
+        <v>128845295</v>
       </c>
       <c r="B40" t="n">
-        <v>91541</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,26 +5376,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5403,10 +5412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541139</v>
+        <v>541394</v>
       </c>
       <c r="R40" t="n">
-        <v>7174393</v>
+        <v>7174344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5438,7 +5447,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5448,12 +5457,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5462,24 +5471,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5499,7 +5492,7 @@
         <v>128845362</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5603,10 +5596,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845367</v>
+        <v>128845361</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,10 +5631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R42" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5673,7 +5666,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5683,12 +5676,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5715,10 +5703,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845361</v>
+        <v>128845339</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5726,34 +5714,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541658</v>
+        <v>541139</v>
       </c>
       <c r="R43" t="n">
-        <v>7174215</v>
+        <v>7174393</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5785,7 +5776,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5795,7 +5786,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,8 +5800,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5822,10 +5834,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845295</v>
+        <v>128845367</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5833,36 +5845,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845357</v>
+        <v>128845368</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541607</v>
+        <v>541363</v>
       </c>
       <c r="R45" t="n">
-        <v>7174400</v>
+        <v>7174330</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6053,10 +6053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845368</v>
+        <v>128845342</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541363</v>
+        <v>541011</v>
       </c>
       <c r="R46" t="n">
-        <v>7174330</v>
+        <v>7174346</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6160,10 +6160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845342</v>
+        <v>128845326</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6171,21 +6171,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541011</v>
+        <v>541626</v>
       </c>
       <c r="R47" t="n">
-        <v>7174346</v>
+        <v>7174307</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6240,7 +6240,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6251,6 +6256,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6267,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B48" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,21 +6298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6302,10 +6322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R48" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6337,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6347,12 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6363,21 +6378,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845336</v>
+        <v>128845385</v>
       </c>
       <c r="B50" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541251</v>
+        <v>541163</v>
       </c>
       <c r="R50" t="n">
-        <v>7174388</v>
+        <v>7174329</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,21 +6607,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6638,10 +6623,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845335</v>
+        <v>128845369</v>
       </c>
       <c r="B51" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6649,21 +6634,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6673,10 +6658,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541610</v>
+        <v>541285</v>
       </c>
       <c r="R51" t="n">
-        <v>7174521</v>
+        <v>7174269</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6693,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,12 +6703,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6734,21 +6714,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6765,10 +6730,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845383</v>
+        <v>128845335</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6776,21 +6741,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6800,10 +6765,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541079</v>
+        <v>541610</v>
       </c>
       <c r="R52" t="n">
-        <v>7174333</v>
+        <v>7174521</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6835,7 +6800,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,12 +6810,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6861,6 +6826,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6877,10 +6857,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845385</v>
+        <v>128845336</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6888,21 +6868,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6912,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541163</v>
+        <v>541251</v>
       </c>
       <c r="R53" t="n">
-        <v>7174329</v>
+        <v>7174388</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6947,7 +6927,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6957,12 +6937,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6973,6 +6953,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6989,10 +6984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845304</v>
+        <v>128845289</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7000,34 +6995,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541120</v>
+        <v>541254</v>
       </c>
       <c r="R54" t="n">
-        <v>7174297</v>
+        <v>7174391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7069,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7096,10 +7101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845369</v>
+        <v>128845291</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7107,34 +7112,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541285</v>
+        <v>541147</v>
       </c>
       <c r="R55" t="n">
-        <v>7174269</v>
+        <v>7174441</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7166,7 +7176,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7176,7 +7186,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7203,10 +7218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845381</v>
+        <v>128845383</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7238,10 +7253,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541025</v>
+        <v>541079</v>
       </c>
       <c r="R56" t="n">
-        <v>7174364</v>
+        <v>7174333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7273,7 +7288,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7283,7 +7298,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7315,10 +7330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845289</v>
+        <v>128845304</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7326,39 +7341,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541254</v>
+        <v>541120</v>
       </c>
       <c r="R57" t="n">
-        <v>7174391</v>
+        <v>7174297</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7400,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,12 +7410,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7432,10 +7437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845291</v>
+        <v>128845381</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7443,39 +7448,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541147</v>
+        <v>541025</v>
       </c>
       <c r="R58" t="n">
-        <v>7174441</v>
+        <v>7174364</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845292</v>
+        <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,39 +7560,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541140</v>
+        <v>541462</v>
       </c>
       <c r="R59" t="n">
-        <v>7174441</v>
+        <v>7174528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7624,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7634,12 +7629,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7650,6 +7645,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7666,10 +7676,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845333</v>
+        <v>128845292</v>
       </c>
       <c r="B60" t="n">
-        <v>91541</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7677,34 +7687,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541462</v>
+        <v>541140</v>
       </c>
       <c r="R60" t="n">
-        <v>7174528</v>
+        <v>7174441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7736,7 +7751,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7746,12 +7761,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7762,21 +7777,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7796,7 +7796,7 @@
         <v>128845348</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>128845373</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>128845354</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845284</v>
+        <v>128845378</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,39 +8125,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541637</v>
+        <v>541032</v>
       </c>
       <c r="R64" t="n">
-        <v>7174351</v>
+        <v>7174308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8189,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8199,12 +8194,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8231,10 +8221,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845324</v>
+        <v>128845375</v>
       </c>
       <c r="B65" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8242,21 +8232,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8266,10 +8256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541610</v>
+        <v>541136</v>
       </c>
       <c r="R65" t="n">
-        <v>7174586</v>
+        <v>7174402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8301,7 +8291,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8311,12 +8301,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8327,21 +8312,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8358,10 +8328,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845378</v>
+        <v>128845355</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8393,10 +8363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541032</v>
+        <v>541637</v>
       </c>
       <c r="R66" t="n">
-        <v>7174308</v>
+        <v>7174473</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8428,7 +8398,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8438,7 +8408,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8465,10 +8440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845375</v>
+        <v>128845324</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8476,21 +8451,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8500,10 +8475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541136</v>
+        <v>541610</v>
       </c>
       <c r="R67" t="n">
-        <v>7174402</v>
+        <v>7174586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8535,7 +8510,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8545,7 +8520,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8556,6 +8536,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8572,10 +8567,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845355</v>
+        <v>128845282</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8583,24 +8578,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8684,7 +8684,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845282</v>
+        <v>128845284</v>
       </c>
       <c r="B69" t="n">
         <v>57723</v>
@@ -8727,7 +8727,7 @@
         <v>541637</v>
       </c>
       <c r="R69" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>128845384</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>128845364</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128845351</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>128845358</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>128845300</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>128845379</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>128845372</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>128845377</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845329</v>
+        <v>128845380</v>
       </c>
       <c r="B79" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,21 +9805,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541141</v>
+        <v>541027</v>
       </c>
       <c r="R79" t="n">
-        <v>7174388</v>
+        <v>7174356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9890,21 +9890,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9921,10 +9906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845380</v>
+        <v>128845371</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9956,10 +9941,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541027</v>
+        <v>541216</v>
       </c>
       <c r="R80" t="n">
-        <v>7174356</v>
+        <v>7174399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9991,7 +9976,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10001,12 +9986,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10033,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845371</v>
+        <v>128845329</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10044,21 +10024,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10068,10 +10048,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541216</v>
+        <v>541141</v>
       </c>
       <c r="R81" t="n">
-        <v>7174399</v>
+        <v>7174388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10103,7 +10083,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10113,7 +10093,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10124,6 +10109,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>128845352</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>128845347</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>128845302</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10717,10 +10717,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845278</v>
+        <v>128845344</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10728,39 +10728,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541418</v>
+        <v>541312</v>
       </c>
       <c r="R87" t="n">
-        <v>7174396</v>
+        <v>7174300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10792,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10802,12 +10797,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10834,50 +10824,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845281</v>
+        <v>128845272</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541599</v>
+        <v>541629</v>
       </c>
       <c r="R88" t="n">
-        <v>7174544</v>
+        <v>7174402</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10909,7 +10894,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10919,12 +10904,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10935,6 +10920,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10951,45 +10951,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845272</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
-        <v>92223</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541629</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174402</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11021,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11031,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11047,21 +11052,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11078,10 +11068,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845344</v>
+        <v>128845281</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11089,34 +11079,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541312</v>
+        <v>541599</v>
       </c>
       <c r="R90" t="n">
-        <v>7174300</v>
+        <v>7174544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11148,7 +11143,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11158,7 +11153,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11302,48 +11302,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845274</v>
+        <v>128845287</v>
       </c>
       <c r="B92" t="n">
-        <v>92223</v>
+        <v>57723</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541116</v>
+        <v>541428</v>
       </c>
       <c r="R92" t="n">
-        <v>7174272</v>
+        <v>7174314</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11375,7 +11377,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11385,12 +11387,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11399,24 +11401,8 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11433,10 +11419,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845270</v>
+        <v>128845274</v>
       </c>
       <c r="B93" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11462,16 +11448,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541134</v>
+        <v>541116</v>
       </c>
       <c r="R93" t="n">
-        <v>7174353</v>
+        <v>7174272</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11503,7 +11492,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11513,12 +11502,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11527,6 +11516,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11560,32 +11550,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845338</v>
+        <v>128845270</v>
       </c>
       <c r="B94" t="n">
-        <v>91541</v>
+        <v>92226</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11595,10 +11585,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541232</v>
+        <v>541134</v>
       </c>
       <c r="R94" t="n">
-        <v>7174426</v>
+        <v>7174353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11630,7 +11620,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11640,7 +11630,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -11687,10 +11677,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845287</v>
+        <v>128845338</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11698,39 +11688,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541428</v>
+        <v>541232</v>
       </c>
       <c r="R95" t="n">
-        <v>7174314</v>
+        <v>7174426</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11762,7 +11747,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11772,12 +11757,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11788,6 +11773,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11807,7 +11807,7 @@
         <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11931,10 +11931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,12 +12011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12043,10 +12038,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R98" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12113,7 +12108,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12123,7 +12118,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12387,7 +12387,7 @@
         <v>128845343</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>128845269</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>128845376</v>
       </c>
       <c r="B103" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B105" t="n">
-        <v>91519</v>
+        <v>91544</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R105" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B106" t="n">
-        <v>91541</v>
+        <v>91522</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R106" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13079,7 +13079,7 @@
         <v>128845366</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>128845350</v>
       </c>
       <c r="B108" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845349</v>
+        <v>128845345</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541462</v>
+        <v>541348</v>
       </c>
       <c r="R109" t="n">
-        <v>7174528</v>
+        <v>7174394</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,7 +13375,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13402,10 +13407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845345</v>
+        <v>128845349</v>
       </c>
       <c r="B110" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13437,10 +13442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541348</v>
+        <v>541462</v>
       </c>
       <c r="R110" t="n">
-        <v>7174394</v>
+        <v>7174528</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13472,7 +13477,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,12 +13487,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99915</v>
+        <v>99918</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845328</v>
+        <v>128845360</v>
       </c>
       <c r="B20" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541428</v>
+        <v>541640</v>
       </c>
       <c r="R20" t="n">
-        <v>7174314</v>
+        <v>7174274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3088,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3104,21 +3099,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3135,32 +3115,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845296</v>
+        <v>128845365</v>
       </c>
       <c r="B21" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3150,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541359</v>
+        <v>541453</v>
       </c>
       <c r="R21" t="n">
-        <v>7174394</v>
+        <v>7174305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3185,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,12 +3195,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,21 +3206,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3262,10 +3222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845322</v>
+        <v>128845296</v>
       </c>
       <c r="B22" t="n">
-        <v>80176</v>
+        <v>80169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,21 +3233,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3297,10 +3257,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541579</v>
+        <v>541359</v>
       </c>
       <c r="R22" t="n">
-        <v>7174417</v>
+        <v>7174394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,7 +3292,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3342,7 +3302,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3389,32 +3349,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845360</v>
+        <v>128845322</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3424,10 +3384,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541640</v>
+        <v>541579</v>
       </c>
       <c r="R23" t="n">
-        <v>7174274</v>
+        <v>7174417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3459,7 +3419,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3469,7 +3429,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3480,6 +3445,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3496,7 +3476,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845365</v>
+        <v>128845346</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -3531,10 +3511,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541453</v>
+        <v>541373</v>
       </c>
       <c r="R24" t="n">
-        <v>7174305</v>
+        <v>7174407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3566,7 +3546,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3576,7 +3556,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3603,10 +3588,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845346</v>
+        <v>128845328</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3614,21 +3599,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3638,10 +3623,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541373</v>
+        <v>541428</v>
       </c>
       <c r="R25" t="n">
-        <v>7174407</v>
+        <v>7174314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3673,7 +3658,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3683,12 +3668,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3699,6 +3684,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845298</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,34 +3843,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541013</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3917,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3944,10 +3949,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845359</v>
+        <v>128845279</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3955,34 +3960,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541617</v>
+        <v>541504</v>
       </c>
       <c r="R28" t="n">
-        <v>7174319</v>
+        <v>7174451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,7 +4024,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4034,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,10 +4066,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845279</v>
+        <v>128845353</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4062,39 +4077,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541504</v>
+        <v>541612</v>
       </c>
       <c r="R29" t="n">
-        <v>7174451</v>
+        <v>7174586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4126,7 +4136,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4136,12 +4146,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4168,32 +4178,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845323</v>
+        <v>128845359</v>
       </c>
       <c r="B30" t="n">
-        <v>98993</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4203,10 +4213,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541182</v>
+        <v>541617</v>
       </c>
       <c r="R30" t="n">
-        <v>7174332</v>
+        <v>7174319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4238,7 +4248,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4248,7 +4258,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4275,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845298</v>
+        <v>128845340</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>91544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4286,39 +4296,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541013</v>
+        <v>541062</v>
       </c>
       <c r="R31" t="n">
-        <v>7174346</v>
+        <v>7174293</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4350,7 +4355,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4360,12 +4365,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4376,6 +4381,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4392,32 +4412,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845340</v>
+        <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>91544</v>
+        <v>98993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4427,10 +4447,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541062</v>
+        <v>541182</v>
       </c>
       <c r="R32" t="n">
-        <v>7174293</v>
+        <v>7174332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4472,12 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4488,21 +4503,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4519,45 +4519,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845341</v>
+        <v>128845275</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541131</v>
+        <v>541057</v>
       </c>
       <c r="R33" t="n">
-        <v>7174440</v>
+        <v>7174336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,7 +4602,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4608,8 +4616,24 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4746,10 +4770,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B35" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4757,21 +4781,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4781,10 +4805,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R35" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4816,7 +4840,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4826,12 +4850,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4842,21 +4861,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4873,48 +4877,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845275</v>
+        <v>128845332</v>
       </c>
       <c r="B36" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541057</v>
+        <v>541284</v>
       </c>
       <c r="R36" t="n">
-        <v>7174336</v>
+        <v>7174287</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4946,7 +4947,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4956,12 +4957,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4970,7 +4971,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845327</v>
+        <v>128845362</v>
       </c>
       <c r="B38" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541654</v>
+        <v>541644</v>
       </c>
       <c r="R38" t="n">
-        <v>7174247</v>
+        <v>7174158</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5201,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5217,21 +5212,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5248,10 +5228,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845283</v>
+        <v>128845367</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,39 +5239,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541605</v>
+        <v>541394</v>
       </c>
       <c r="R39" t="n">
-        <v>7174433</v>
+        <v>7174344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5323,7 +5298,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5333,12 +5308,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5365,10 +5340,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845295</v>
+        <v>128845361</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,46 +5351,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R40" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5447,7 +5410,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5457,12 +5420,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5489,10 +5447,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845362</v>
+        <v>128845327</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5500,21 +5458,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5524,10 +5482,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541644</v>
+        <v>541654</v>
       </c>
       <c r="R41" t="n">
-        <v>7174158</v>
+        <v>7174247</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5559,7 +5517,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5569,7 +5527,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5580,6 +5543,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5596,10 +5574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845361</v>
+        <v>128845283</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5607,34 +5585,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541658</v>
+        <v>541605</v>
       </c>
       <c r="R42" t="n">
-        <v>7174215</v>
+        <v>7174433</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5666,7 +5649,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5676,7 +5659,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5834,10 +5822,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845367</v>
+        <v>128845295</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5845,24 +5833,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845368</v>
+        <v>128845290</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,34 +5957,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541363</v>
+        <v>541211</v>
       </c>
       <c r="R45" t="n">
-        <v>7174330</v>
+        <v>7174387</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6021,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,7 +6031,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6053,7 +6063,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845342</v>
+        <v>128845357</v>
       </c>
       <c r="B46" t="n">
         <v>79035</v>
@@ -6088,10 +6098,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541011</v>
+        <v>541607</v>
       </c>
       <c r="R46" t="n">
-        <v>7174346</v>
+        <v>7174400</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6123,7 +6133,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6133,7 +6143,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6160,10 +6170,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845326</v>
+        <v>128845368</v>
       </c>
       <c r="B47" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6171,21 +6181,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6195,10 +6205,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541626</v>
+        <v>541363</v>
       </c>
       <c r="R47" t="n">
-        <v>7174307</v>
+        <v>7174330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6230,7 +6240,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6240,12 +6250,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6256,21 +6261,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6287,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845357</v>
+        <v>128845342</v>
       </c>
       <c r="B48" t="n">
         <v>79035</v>
@@ -6322,10 +6312,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541607</v>
+        <v>541011</v>
       </c>
       <c r="R48" t="n">
-        <v>7174400</v>
+        <v>7174346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6347,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6357,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6394,10 +6384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845290</v>
+        <v>128845326</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6405,39 +6395,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541211</v>
+        <v>541626</v>
       </c>
       <c r="R49" t="n">
-        <v>7174387</v>
+        <v>7174307</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6469,7 +6454,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6479,12 +6464,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6495,6 +6480,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845385</v>
+        <v>128845289</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,34 +6522,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541163</v>
+        <v>541254</v>
       </c>
       <c r="R50" t="n">
-        <v>7174329</v>
+        <v>7174391</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6586,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6596,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6623,10 +6628,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845369</v>
+        <v>128845291</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,34 +6639,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541285</v>
+        <v>541147</v>
       </c>
       <c r="R51" t="n">
-        <v>7174269</v>
+        <v>7174441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6703,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,7 +6713,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6730,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845335</v>
+        <v>128845336</v>
       </c>
       <c r="B52" t="n">
         <v>91544</v>
@@ -6765,10 +6780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541610</v>
+        <v>541251</v>
       </c>
       <c r="R52" t="n">
-        <v>7174521</v>
+        <v>7174388</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6800,7 +6815,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6810,12 +6825,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6857,7 +6872,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845336</v>
+        <v>128845335</v>
       </c>
       <c r="B53" t="n">
         <v>91544</v>
@@ -6892,10 +6907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541251</v>
+        <v>541610</v>
       </c>
       <c r="R53" t="n">
-        <v>7174388</v>
+        <v>7174521</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6927,7 +6942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6937,12 +6952,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6984,10 +6999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845289</v>
+        <v>128845383</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6995,39 +7010,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541254</v>
+        <v>541079</v>
       </c>
       <c r="R54" t="n">
-        <v>7174391</v>
+        <v>7174333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7069,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,12 +7079,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7101,10 +7111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845291</v>
+        <v>128845385</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7112,39 +7122,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541147</v>
+        <v>541163</v>
       </c>
       <c r="R55" t="n">
-        <v>7174441</v>
+        <v>7174329</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7176,7 +7181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7186,12 +7191,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7218,7 +7223,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845383</v>
+        <v>128845304</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -7253,10 +7258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541079</v>
+        <v>541120</v>
       </c>
       <c r="R56" t="n">
-        <v>7174333</v>
+        <v>7174297</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7288,7 +7293,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7298,12 +7303,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7330,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845304</v>
+        <v>128845369</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541120</v>
+        <v>541285</v>
       </c>
       <c r="R57" t="n">
-        <v>7174297</v>
+        <v>7174269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845333</v>
+        <v>128845292</v>
       </c>
       <c r="B59" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,34 +7560,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541462</v>
+        <v>541140</v>
       </c>
       <c r="R59" t="n">
-        <v>7174528</v>
+        <v>7174441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7624,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,12 +7634,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7645,21 +7650,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7676,10 +7666,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845292</v>
+        <v>128845333</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,39 +7677,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541140</v>
+        <v>541462</v>
       </c>
       <c r="R60" t="n">
-        <v>7174441</v>
+        <v>7174528</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7751,7 +7736,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7761,12 +7746,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7777,6 +7762,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -10717,10 +10717,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845344</v>
+        <v>128845278</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10728,34 +10728,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541312</v>
+        <v>541418</v>
       </c>
       <c r="R87" t="n">
-        <v>7174300</v>
+        <v>7174396</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10792,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,7 +10802,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10824,45 +10834,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845272</v>
+        <v>128845281</v>
       </c>
       <c r="B88" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541629</v>
+        <v>541599</v>
       </c>
       <c r="R88" t="n">
-        <v>7174402</v>
+        <v>7174544</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10894,7 +10909,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10904,12 +10919,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10920,21 +10935,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10951,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845276</v>
       </c>
       <c r="B89" t="n">
         <v>57723</v>
@@ -10982,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541274</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174268</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11068,50 +11068,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845281</v>
+        <v>128845272</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541599</v>
+        <v>541629</v>
       </c>
       <c r="R90" t="n">
-        <v>7174544</v>
+        <v>7174402</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11143,7 +11138,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11153,12 +11148,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11169,6 +11164,21 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11185,10 +11195,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845276</v>
+        <v>128845344</v>
       </c>
       <c r="B91" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11196,39 +11206,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541274</v>
+        <v>541312</v>
       </c>
       <c r="R91" t="n">
-        <v>7174268</v>
+        <v>7174300</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11265,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,12 +11275,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11302,50 +11302,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845287</v>
+        <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541428</v>
+        <v>541116</v>
       </c>
       <c r="R92" t="n">
-        <v>7174314</v>
+        <v>7174272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11377,7 +11375,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11387,12 +11385,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11401,8 +11399,24 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11419,7 +11433,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845274</v>
+        <v>128845270</v>
       </c>
       <c r="B93" t="n">
         <v>92226</v>
@@ -11448,19 +11462,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541116</v>
+        <v>541134</v>
       </c>
       <c r="R93" t="n">
-        <v>7174272</v>
+        <v>7174353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11492,7 +11503,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11502,12 +11513,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11516,7 +11527,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11550,45 +11560,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845270</v>
+        <v>128845287</v>
       </c>
       <c r="B94" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541134</v>
+        <v>541428</v>
       </c>
       <c r="R94" t="n">
-        <v>7174353</v>
+        <v>7174314</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11620,7 +11635,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11630,12 +11645,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11646,21 +11661,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845331</v>
+        <v>128845370</v>
       </c>
       <c r="B96" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541271</v>
+        <v>541222</v>
       </c>
       <c r="R96" t="n">
-        <v>7174269</v>
+        <v>7174409</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,21 +11900,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12038,10 +12023,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845370</v>
+        <v>128845288</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12049,34 +12034,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541222</v>
+        <v>541261</v>
       </c>
       <c r="R98" t="n">
-        <v>7174409</v>
+        <v>7174398</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12108,7 +12098,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12118,12 +12108,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12150,7 +12140,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
         <v>57723</v>
@@ -12190,10 +12180,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12215,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12225,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,10 +12257,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845285</v>
+        <v>128845331</v>
       </c>
       <c r="B100" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12278,39 +12268,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541640</v>
+        <v>541271</v>
       </c>
       <c r="R100" t="n">
-        <v>7174353</v>
+        <v>7174269</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12327,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,12 +12337,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12368,6 +12353,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845343</v>
+        <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,34 +12395,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541074</v>
+        <v>541322</v>
       </c>
       <c r="R101" t="n">
-        <v>7174298</v>
+        <v>7174361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,7 +12501,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845269</v>
+        <v>128845343</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541134</v>
+        <v>541074</v>
       </c>
       <c r="R102" t="n">
-        <v>7174353</v>
+        <v>7174298</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12571,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12581,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,7 +12608,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845376</v>
+        <v>128845269</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -12633,10 +12643,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541109</v>
+        <v>541134</v>
       </c>
       <c r="R103" t="n">
-        <v>7174267</v>
+        <v>7174353</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12678,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12688,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12705,10 +12715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845277</v>
+        <v>128845376</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12716,39 +12726,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541322</v>
+        <v>541109</v>
       </c>
       <c r="R104" t="n">
-        <v>7174361</v>
+        <v>7174267</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12790,12 +12795,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12822,10 +12822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128845334</v>
+        <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91544</v>
+        <v>91522</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12833,21 +12833,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541599</v>
+        <v>541031</v>
       </c>
       <c r="R105" t="n">
-        <v>7174544</v>
+        <v>7174369</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12949,10 +12949,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128845330</v>
+        <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>541031</v>
+        <v>541599</v>
       </c>
       <c r="R106" t="n">
-        <v>7174369</v>
+        <v>7174544</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845345</v>
+        <v>128845349</v>
       </c>
       <c r="B109" t="n">
         <v>79035</v>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541348</v>
+        <v>541462</v>
       </c>
       <c r="R109" t="n">
-        <v>7174394</v>
+        <v>7174528</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,12 +13375,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13407,7 +13402,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845349</v>
+        <v>128845345</v>
       </c>
       <c r="B110" t="n">
         <v>79035</v>
@@ -13442,10 +13437,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541462</v>
+        <v>541348</v>
       </c>
       <c r="R110" t="n">
-        <v>7174528</v>
+        <v>7174394</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13477,7 +13472,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13487,7 +13482,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -3588,10 +3588,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845328</v>
+        <v>128845280</v>
       </c>
       <c r="B25" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,34 +3599,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541428</v>
+        <v>541574</v>
       </c>
       <c r="R25" t="n">
-        <v>7174314</v>
+        <v>7174569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3658,7 +3663,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3668,12 +3673,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,21 +3689,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,10 +3705,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845280</v>
+        <v>128845328</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,39 +3716,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541574</v>
+        <v>541428</v>
       </c>
       <c r="R26" t="n">
-        <v>7174569</v>
+        <v>7174314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3775,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3785,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3816,6 +3801,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,16 +3843,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3863,7 +3863,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R27" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845279</v>
+        <v>128845340</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3960,39 +3960,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541504</v>
+        <v>541062</v>
       </c>
       <c r="R28" t="n">
-        <v>7174451</v>
+        <v>7174293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4034,12 +4029,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4050,6 +4045,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4285,10 +4295,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B31" t="n">
-        <v>91544</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4296,34 +4306,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R31" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4355,7 +4370,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4365,12 +4380,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4381,21 +4396,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845341</v>
+        <v>128845293</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4781,34 +4781,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541131</v>
+        <v>541157</v>
       </c>
       <c r="R35" t="n">
-        <v>7174440</v>
+        <v>7174382</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4840,7 +4845,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4850,7 +4855,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4877,10 +4887,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B36" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4888,21 +4898,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4912,10 +4922,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R36" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4947,7 +4957,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4957,12 +4967,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4973,21 +4978,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5004,10 +4994,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845293</v>
+        <v>128845332</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5015,39 +5005,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541157</v>
+        <v>541284</v>
       </c>
       <c r="R37" t="n">
-        <v>7174382</v>
+        <v>7174287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5064,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5074,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5105,6 +5090,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5574,10 +5574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845283</v>
+        <v>128845339</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5585,39 +5585,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541605</v>
+        <v>541139</v>
       </c>
       <c r="R42" t="n">
-        <v>7174433</v>
+        <v>7174393</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5649,7 +5647,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5659,12 +5657,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5673,8 +5671,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5691,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845339</v>
+        <v>128845283</v>
       </c>
       <c r="B43" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5702,37 +5716,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541139</v>
+        <v>541605</v>
       </c>
       <c r="R43" t="n">
-        <v>7174393</v>
+        <v>7174433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5764,7 +5780,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5774,12 +5790,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5788,24 +5804,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -10013,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B81" t="n">
-        <v>91522</v>
+        <v>57883</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,34 +10024,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10083,7 +10095,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10093,12 +10105,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10109,21 +10121,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10140,10 +10137,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845294</v>
+        <v>128845329</v>
       </c>
       <c r="B82" t="n">
-        <v>57883</v>
+        <v>91522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10151,46 +10148,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541544</v>
+        <v>541141</v>
       </c>
       <c r="R82" t="n">
-        <v>7174513</v>
+        <v>7174388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10207,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10217,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10248,6 +10233,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845370</v>
+        <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541222</v>
+        <v>541271</v>
       </c>
       <c r="R96" t="n">
-        <v>7174409</v>
+        <v>7174269</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,6 +11900,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11916,7 +11931,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -11951,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11986,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11996,7 +12011,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12023,10 +12043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845288</v>
+        <v>128845382</v>
       </c>
       <c r="B98" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12034,39 +12054,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541261</v>
+        <v>541041</v>
       </c>
       <c r="R98" t="n">
-        <v>7174398</v>
+        <v>7174348</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12098,7 +12113,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12108,12 +12123,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12140,7 +12150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
         <v>57723</v>
@@ -12180,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12215,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12225,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12257,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845331</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12268,34 +12278,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541271</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174269</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12327,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12337,12 +12352,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12353,21 +12368,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845277</v>
+        <v>128845343</v>
       </c>
       <c r="B101" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,39 +12395,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541322</v>
+        <v>541074</v>
       </c>
       <c r="R101" t="n">
-        <v>7174361</v>
+        <v>7174298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12459,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12469,12 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12501,7 +12491,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -12536,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R102" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12571,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12581,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12608,7 +12598,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845269</v>
+        <v>128845376</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -12643,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541134</v>
+        <v>541109</v>
       </c>
       <c r="R103" t="n">
-        <v>7174353</v>
+        <v>7174267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12678,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12688,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12715,10 +12705,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845376</v>
+        <v>128845277</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,34 +12716,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541109</v>
+        <v>541322</v>
       </c>
       <c r="R104" t="n">
-        <v>7174267</v>
+        <v>7174361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12785,7 +12780,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12795,7 +12790,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2764,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B18" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,34 +2775,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R18" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2844,12 +2849,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2860,21 +2865,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2891,10 +2881,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845325</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2892,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541618</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2961,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,6 +2977,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3222,32 +3222,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845296</v>
+        <v>128845346</v>
       </c>
       <c r="B22" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541359</v>
+        <v>541373</v>
       </c>
       <c r="R22" t="n">
-        <v>7174394</v>
+        <v>7174407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3318,21 +3318,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3349,10 +3334,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845322</v>
+        <v>128845296</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3360,21 +3345,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3384,10 +3369,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541579</v>
+        <v>541359</v>
       </c>
       <c r="R23" t="n">
-        <v>7174417</v>
+        <v>7174394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3419,7 +3404,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3429,7 +3414,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3476,32 +3461,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845346</v>
+        <v>128845322</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3511,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541373</v>
+        <v>541579</v>
       </c>
       <c r="R24" t="n">
-        <v>7174407</v>
+        <v>7174417</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3546,7 +3531,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3556,12 +3541,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,6 +3557,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3832,50 +3832,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>98993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R27" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3907,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3917,12 +3912,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4412,45 +4402,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845323</v>
+        <v>128845279</v>
       </c>
       <c r="B32" t="n">
-        <v>98993</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541182</v>
+        <v>541504</v>
       </c>
       <c r="R32" t="n">
-        <v>7174332</v>
+        <v>7174451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4492,7 +4487,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4650,10 +4650,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845297</v>
+        <v>128845332</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>91544</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4661,42 +4661,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541232</v>
+        <v>541284</v>
       </c>
       <c r="R34" t="n">
-        <v>7174426</v>
+        <v>7174287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4728,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4738,12 +4730,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4754,6 +4746,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4770,10 +4777,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845293</v>
+        <v>128845297</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4781,16 +4788,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4799,21 +4806,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541157</v>
+        <v>541232</v>
       </c>
       <c r="R35" t="n">
-        <v>7174382</v>
+        <v>7174426</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4845,7 +4855,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4855,12 +4865,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,10 +4897,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845341</v>
+        <v>128845293</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4898,34 +4908,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541131</v>
+        <v>541157</v>
       </c>
       <c r="R36" t="n">
-        <v>7174440</v>
+        <v>7174382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4957,7 +4972,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4967,7 +4982,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4994,10 +5014,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B37" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5005,21 +5025,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5029,10 +5049,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R37" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5064,7 +5084,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5074,12 +5094,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5090,21 +5105,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845362</v>
+        <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541644</v>
+        <v>541654</v>
       </c>
       <c r="R38" t="n">
-        <v>7174158</v>
+        <v>7174247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,7 +5201,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5212,6 +5217,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5228,7 +5248,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845367</v>
+        <v>128845362</v>
       </c>
       <c r="B39" t="n">
         <v>79035</v>
@@ -5263,10 +5283,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541394</v>
+        <v>541644</v>
       </c>
       <c r="R39" t="n">
-        <v>7174344</v>
+        <v>7174158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5298,7 +5318,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5308,12 +5328,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5340,7 +5355,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845361</v>
+        <v>128845367</v>
       </c>
       <c r="B40" t="n">
         <v>79035</v>
@@ -5375,10 +5390,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R40" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5410,7 +5425,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5420,7 +5435,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5447,10 +5467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845327</v>
+        <v>128845361</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5458,21 +5478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5482,10 +5502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541654</v>
+        <v>541658</v>
       </c>
       <c r="R41" t="n">
-        <v>7174247</v>
+        <v>7174215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5517,7 +5537,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5527,12 +5547,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5543,21 +5558,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5574,10 +5574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845339</v>
+        <v>128845283</v>
       </c>
       <c r="B42" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5585,37 +5585,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541139</v>
+        <v>541605</v>
       </c>
       <c r="R42" t="n">
-        <v>7174393</v>
+        <v>7174433</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5647,7 +5649,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5657,12 +5659,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5671,24 +5673,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5705,10 +5691,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845283</v>
+        <v>128845339</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,39 +5702,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541605</v>
+        <v>541139</v>
       </c>
       <c r="R43" t="n">
-        <v>7174433</v>
+        <v>7174393</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5780,7 +5764,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,12 +5774,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,8 +5788,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845357</v>
+        <v>128845326</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6074,21 +6074,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541607</v>
+        <v>541626</v>
       </c>
       <c r="R46" t="n">
-        <v>7174400</v>
+        <v>7174307</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6143,7 +6143,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6154,6 +6159,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6170,7 +6190,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845368</v>
+        <v>128845357</v>
       </c>
       <c r="B47" t="n">
         <v>79035</v>
@@ -6205,10 +6225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541363</v>
+        <v>541607</v>
       </c>
       <c r="R47" t="n">
-        <v>7174330</v>
+        <v>7174400</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6240,7 +6260,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6250,7 +6270,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6297,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845342</v>
+        <v>128845368</v>
       </c>
       <c r="B48" t="n">
         <v>79035</v>
@@ -6312,10 +6332,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541011</v>
+        <v>541363</v>
       </c>
       <c r="R48" t="n">
-        <v>7174346</v>
+        <v>7174330</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6347,7 +6367,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6357,7 +6377,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,10 +6404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845326</v>
+        <v>128845342</v>
       </c>
       <c r="B49" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,21 +6415,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6419,10 +6439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541626</v>
+        <v>541011</v>
       </c>
       <c r="R49" t="n">
-        <v>7174307</v>
+        <v>7174346</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6454,7 +6474,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6464,12 +6484,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6480,21 +6495,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845289</v>
+        <v>128845336</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,39 +6522,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541254</v>
+        <v>541251</v>
       </c>
       <c r="R50" t="n">
-        <v>7174391</v>
+        <v>7174388</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6586,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6596,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6612,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6628,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845291</v>
+        <v>128845335</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6639,39 +6649,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541147</v>
+        <v>541610</v>
       </c>
       <c r="R51" t="n">
-        <v>7174441</v>
+        <v>7174521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6703,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6713,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6729,6 +6734,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6745,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845336</v>
+        <v>128845383</v>
       </c>
       <c r="B52" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6756,21 +6776,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6780,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541251</v>
+        <v>541079</v>
       </c>
       <c r="R52" t="n">
-        <v>7174388</v>
+        <v>7174333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6815,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6825,12 +6845,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6841,21 +6861,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6872,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845335</v>
+        <v>128845385</v>
       </c>
       <c r="B53" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,21 +6888,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541610</v>
+        <v>541163</v>
       </c>
       <c r="R53" t="n">
-        <v>7174521</v>
+        <v>7174329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6952,12 +6957,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6968,21 +6973,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6999,7 +6989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845383</v>
+        <v>128845304</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -7034,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541079</v>
+        <v>541120</v>
       </c>
       <c r="R54" t="n">
-        <v>7174333</v>
+        <v>7174297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7069,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7079,12 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7111,7 +7096,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845385</v>
+        <v>128845369</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -7146,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541163</v>
+        <v>541285</v>
       </c>
       <c r="R55" t="n">
-        <v>7174329</v>
+        <v>7174269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7191,12 +7176,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7223,7 +7203,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845304</v>
+        <v>128845381</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -7258,10 +7238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541120</v>
+        <v>541025</v>
       </c>
       <c r="R56" t="n">
-        <v>7174297</v>
+        <v>7174364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7293,7 +7273,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7303,7 +7283,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7330,10 +7315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845369</v>
+        <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7341,34 +7326,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541285</v>
+        <v>541254</v>
       </c>
       <c r="R57" t="n">
-        <v>7174269</v>
+        <v>7174391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7400,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7410,7 +7400,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7437,10 +7432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845381</v>
+        <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7448,34 +7443,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541025</v>
+        <v>541147</v>
       </c>
       <c r="R58" t="n">
-        <v>7174364</v>
+        <v>7174441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845292</v>
+        <v>128845373</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,39 +7560,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541140</v>
+        <v>541143</v>
       </c>
       <c r="R59" t="n">
-        <v>7174441</v>
+        <v>7174450</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7624,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7634,12 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7666,10 +7656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845333</v>
+        <v>128845292</v>
       </c>
       <c r="B60" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7677,34 +7667,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541462</v>
+        <v>541140</v>
       </c>
       <c r="R60" t="n">
-        <v>7174528</v>
+        <v>7174441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7736,7 +7731,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7746,12 +7741,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På stubbe och låga</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7762,21 +7757,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7793,10 +7773,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845348</v>
+        <v>128845333</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7804,21 +7784,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7828,10 +7808,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541504</v>
+        <v>541462</v>
       </c>
       <c r="R61" t="n">
-        <v>7174451</v>
+        <v>7174528</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7863,7 +7843,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7873,7 +7853,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7884,6 +7869,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7900,7 +7900,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B62" t="n">
         <v>79035</v>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R62" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8440,10 +8440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845324</v>
+        <v>128845282</v>
       </c>
       <c r="B67" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8451,34 +8451,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R67" t="n">
-        <v>7174586</v>
+        <v>7174473</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8510,7 +8515,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8520,12 +8525,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8536,21 +8541,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8567,7 +8557,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845282</v>
+        <v>128845284</v>
       </c>
       <c r="B68" t="n">
         <v>57723</v>
@@ -8610,7 +8600,7 @@
         <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174473</v>
+        <v>7174351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8642,7 +8632,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,7 +8642,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8684,10 +8674,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845284</v>
+        <v>128845324</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8695,39 +8685,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R69" t="n">
-        <v>7174351</v>
+        <v>7174586</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8744,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,12 +8754,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8785,6 +8770,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845384</v>
+        <v>128845364</v>
       </c>
       <c r="B70" t="n">
         <v>79035</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541112</v>
+        <v>541490</v>
       </c>
       <c r="R70" t="n">
-        <v>7174350</v>
+        <v>7174268</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8908,7 +8908,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128845364</v>
+        <v>128845351</v>
       </c>
       <c r="B71" t="n">
         <v>79035</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541490</v>
+        <v>541563</v>
       </c>
       <c r="R71" t="n">
-        <v>7174268</v>
+        <v>7174549</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8988,7 +8988,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9015,7 +9020,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845351</v>
+        <v>128845384</v>
       </c>
       <c r="B72" t="n">
         <v>79035</v>
@@ -9050,10 +9055,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541563</v>
+        <v>541112</v>
       </c>
       <c r="R72" t="n">
-        <v>7174549</v>
+        <v>7174350</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9085,7 +9090,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9095,12 +9100,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845294</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,34 +9805,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541544</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9886,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9906,10 +9918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845329</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9917,21 +9929,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9941,10 +9953,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541141</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9976,7 +9988,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9986,7 +9998,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9997,6 +10014,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10013,10 +10045,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845294</v>
+        <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,46 +10056,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541544</v>
+        <v>541027</v>
       </c>
       <c r="R81" t="n">
-        <v>7174513</v>
+        <v>7174356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10095,7 +10115,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10105,12 +10125,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10137,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B82" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10148,21 +10168,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10172,10 +10192,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R82" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10207,7 +10227,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10217,12 +10237,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10233,21 +10248,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10717,50 +10717,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845278</v>
+        <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541418</v>
+        <v>541629</v>
       </c>
       <c r="R87" t="n">
-        <v>7174396</v>
+        <v>7174402</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10792,7 +10787,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10802,12 +10797,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10818,6 +10813,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10834,7 +10844,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845281</v>
+        <v>128845278</v>
       </c>
       <c r="B88" t="n">
         <v>57723</v>
@@ -10865,7 +10875,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10874,10 +10884,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541599</v>
+        <v>541418</v>
       </c>
       <c r="R88" t="n">
-        <v>7174544</v>
+        <v>7174396</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10909,7 +10919,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10919,12 +10929,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11068,45 +11078,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845272</v>
+        <v>128845281</v>
       </c>
       <c r="B90" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541629</v>
+        <v>541599</v>
       </c>
       <c r="R90" t="n">
-        <v>7174402</v>
+        <v>7174544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11138,7 +11153,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11148,12 +11163,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11164,21 +11179,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11302,48 +11302,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845274</v>
+        <v>128845338</v>
       </c>
       <c r="B92" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541116</v>
+        <v>541232</v>
       </c>
       <c r="R92" t="n">
-        <v>7174272</v>
+        <v>7174426</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11375,7 +11372,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11385,12 +11382,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11399,7 +11396,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11433,7 +11429,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845270</v>
+        <v>128845274</v>
       </c>
       <c r="B93" t="n">
         <v>92226</v>
@@ -11462,16 +11458,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541134</v>
+        <v>541116</v>
       </c>
       <c r="R93" t="n">
-        <v>7174353</v>
+        <v>7174272</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11503,7 +11502,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11513,12 +11512,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11527,6 +11526,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11560,50 +11560,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845287</v>
+        <v>128845270</v>
       </c>
       <c r="B94" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541428</v>
+        <v>541134</v>
       </c>
       <c r="R94" t="n">
-        <v>7174314</v>
+        <v>7174353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11635,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11645,12 +11640,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11661,6 +11656,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11677,10 +11687,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845338</v>
+        <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11688,34 +11698,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541232</v>
+        <v>541428</v>
       </c>
       <c r="R95" t="n">
-        <v>7174426</v>
+        <v>7174314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,7 +11762,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11757,12 +11772,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11773,21 +11788,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11931,7 +11931,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,12 +12011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12043,7 +12038,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B98" t="n">
         <v>79035</v>
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R98" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12113,7 +12108,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12123,7 +12118,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12150,7 +12150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
         <v>57723</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,7 +12267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B100" t="n">
         <v>57723</v>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R100" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12384,7 +12384,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845343</v>
+        <v>128845269</v>
       </c>
       <c r="B101" t="n">
         <v>79035</v>
@@ -12419,10 +12419,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541074</v>
+        <v>541134</v>
       </c>
       <c r="R101" t="n">
-        <v>7174298</v>
+        <v>7174353</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12491,7 +12491,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845269</v>
+        <v>128845376</v>
       </c>
       <c r="B102" t="n">
         <v>79035</v>
@@ -12526,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541134</v>
+        <v>541109</v>
       </c>
       <c r="R102" t="n">
-        <v>7174353</v>
+        <v>7174267</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,7 +12598,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845376</v>
+        <v>128845343</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -12633,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541109</v>
+        <v>541074</v>
       </c>
       <c r="R103" t="n">
-        <v>7174267</v>
+        <v>7174298</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13730,7 +13730,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128845308</v>
+        <v>128845306</v>
       </c>
       <c r="B113" t="n">
         <v>99918</v>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>541477</v>
+        <v>541120</v>
       </c>
       <c r="R113" t="n">
-        <v>7174417</v>
+        <v>7174297</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13838,7 +13838,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128845306</v>
+        <v>128845308</v>
       </c>
       <c r="B114" t="n">
         <v>99918</v>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>541120</v>
+        <v>541477</v>
       </c>
       <c r="R114" t="n">
-        <v>7174297</v>
+        <v>7174417</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14486,7 +14486,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128845315</v>
+        <v>128845307</v>
       </c>
       <c r="B120" t="n">
         <v>99918</v>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>541125</v>
+        <v>541291</v>
       </c>
       <c r="R120" t="n">
-        <v>7174337</v>
+        <v>7174294</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14594,7 +14594,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128845307</v>
+        <v>128845315</v>
       </c>
       <c r="B121" t="n">
         <v>99918</v>
@@ -14629,10 +14629,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>541291</v>
+        <v>541125</v>
       </c>
       <c r="R121" t="n">
-        <v>7174294</v>
+        <v>7174337</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14702,7 +14702,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128845319</v>
+        <v>128845311</v>
       </c>
       <c r="B122" t="n">
         <v>99918</v>
@@ -14737,10 +14737,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>541045</v>
+        <v>541243</v>
       </c>
       <c r="R122" t="n">
-        <v>7174303</v>
+        <v>7174412</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14810,7 +14810,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128845311</v>
+        <v>128845319</v>
       </c>
       <c r="B123" t="n">
         <v>99918</v>
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>541243</v>
+        <v>541045</v>
       </c>
       <c r="R123" t="n">
-        <v>7174412</v>
+        <v>7174303</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15355,7 +15355,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128845299</v>
+        <v>128845312</v>
       </c>
       <c r="B128" t="n">
         <v>99918</v>
@@ -15390,10 +15390,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>541152</v>
+        <v>541164</v>
       </c>
       <c r="R128" t="n">
-        <v>7174446</v>
+        <v>7174343</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15463,7 +15463,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128845312</v>
+        <v>128845299</v>
       </c>
       <c r="B129" t="n">
         <v>99918</v>
@@ -15498,10 +15498,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>541164</v>
+        <v>541152</v>
       </c>
       <c r="R129" t="n">
-        <v>7174343</v>
+        <v>7174446</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2553,7 +2553,7 @@
         <v>128845356</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>128845363</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>128845286</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128845325</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845360</v>
+        <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>91529</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541640</v>
+        <v>541428</v>
       </c>
       <c r="R20" t="n">
-        <v>7174274</v>
+        <v>7174314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,7 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,6 +3104,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3115,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845365</v>
+        <v>128845296</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>80173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3150,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541453</v>
+        <v>541359</v>
       </c>
       <c r="R21" t="n">
-        <v>7174305</v>
+        <v>7174394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3185,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3195,7 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3206,6 +3231,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3222,32 +3262,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845346</v>
+        <v>128845322</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>80180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3257,10 +3297,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541373</v>
+        <v>541579</v>
       </c>
       <c r="R22" t="n">
-        <v>7174407</v>
+        <v>7174417</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3292,7 +3332,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3302,12 +3342,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3318,6 +3358,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3334,32 +3389,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845296</v>
+        <v>128845346</v>
       </c>
       <c r="B23" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3369,10 +3424,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541359</v>
+        <v>541373</v>
       </c>
       <c r="R23" t="n">
-        <v>7174394</v>
+        <v>7174407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3404,7 +3459,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3414,12 +3469,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,21 +3485,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3461,32 +3501,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845322</v>
+        <v>128845360</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3536,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541579</v>
+        <v>541640</v>
       </c>
       <c r="R24" t="n">
-        <v>7174417</v>
+        <v>7174274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3531,7 +3571,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3541,12 +3581,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3557,21 +3592,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3588,10 +3608,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845280</v>
+        <v>128845365</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,39 +3619,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541574</v>
+        <v>541453</v>
       </c>
       <c r="R25" t="n">
-        <v>7174569</v>
+        <v>7174305</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3663,7 +3678,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3673,12 +3688,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3705,10 +3715,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845328</v>
+        <v>128845280</v>
       </c>
       <c r="B26" t="n">
-        <v>91522</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3716,34 +3726,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541428</v>
+        <v>541574</v>
       </c>
       <c r="R26" t="n">
-        <v>7174314</v>
+        <v>7174569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845323</v>
+        <v>128845340</v>
       </c>
       <c r="B27" t="n">
-        <v>98993</v>
+        <v>91551</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541182</v>
+        <v>541062</v>
       </c>
       <c r="R27" t="n">
-        <v>7174332</v>
+        <v>7174293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3923,6 +3928,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3939,10 +3959,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845340</v>
+        <v>128845359</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3950,21 +3970,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3974,10 +3994,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541062</v>
+        <v>541617</v>
       </c>
       <c r="R28" t="n">
-        <v>7174293</v>
+        <v>7174319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4009,7 +4029,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4019,12 +4039,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4035,21 +4050,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4069,7 +4069,7 @@
         <v>128845353</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845359</v>
+        <v>128845279</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,34 +4189,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541617</v>
+        <v>541504</v>
       </c>
       <c r="R30" t="n">
-        <v>7174319</v>
+        <v>7174451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4248,7 +4253,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4258,7 +4263,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4288,7 +4298,7 @@
         <v>128845298</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4402,50 +4412,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>99003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R32" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4477,7 +4482,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,12 +4492,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4519,48 +4519,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845275</v>
+        <v>128845332</v>
       </c>
       <c r="B33" t="n">
-        <v>92226</v>
+        <v>91551</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541057</v>
+        <v>541284</v>
       </c>
       <c r="R33" t="n">
-        <v>7174336</v>
+        <v>7174287</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,12 +4599,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4616,7 +4613,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4650,45 +4646,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845332</v>
+        <v>128845275</v>
       </c>
       <c r="B34" t="n">
-        <v>91544</v>
+        <v>92233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541284</v>
+        <v>541057</v>
       </c>
       <c r="R34" t="n">
-        <v>7174287</v>
+        <v>7174336</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4720,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4730,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4744,6 +4743,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4788,42 +4788,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R35" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4855,7 +4847,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4865,12 +4857,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4900,7 +4887,7 @@
         <v>128845293</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5014,10 +5001,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845341</v>
+        <v>128845297</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5025,34 +5012,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541131</v>
+        <v>541232</v>
       </c>
       <c r="R37" t="n">
-        <v>7174440</v>
+        <v>7174426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5084,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5094,7 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845327</v>
+        <v>128845367</v>
       </c>
       <c r="B38" t="n">
-        <v>91522</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541654</v>
+        <v>541394</v>
       </c>
       <c r="R38" t="n">
-        <v>7174247</v>
+        <v>7174344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5217,21 +5217,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5251,7 +5236,7 @@
         <v>128845362</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5355,10 +5340,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845367</v>
+        <v>128845361</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5390,10 +5375,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R40" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5425,7 +5410,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5435,12 +5420,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5467,10 +5447,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845361</v>
+        <v>128845295</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5478,34 +5458,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R41" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5537,7 +5529,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5547,7 +5539,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5574,10 +5571,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845283</v>
+        <v>128845327</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>91529</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5585,39 +5582,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541605</v>
+        <v>541654</v>
       </c>
       <c r="R42" t="n">
-        <v>7174433</v>
+        <v>7174247</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5649,7 +5641,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5659,12 +5651,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5675,6 +5667,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5694,7 +5701,7 @@
         <v>128845339</v>
       </c>
       <c r="B43" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5822,10 +5829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845295</v>
+        <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5833,46 +5840,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541394</v>
+        <v>541605</v>
       </c>
       <c r="R44" t="n">
-        <v>7174344</v>
+        <v>7174433</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845290</v>
+        <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>91529</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,39 +5957,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541211</v>
+        <v>541626</v>
       </c>
       <c r="R45" t="n">
-        <v>7174387</v>
+        <v>7174307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6021,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6031,12 +6026,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6047,6 +6042,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6063,10 +6073,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845326</v>
+        <v>128845368</v>
       </c>
       <c r="B46" t="n">
-        <v>91522</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6074,21 +6084,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6098,10 +6108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541626</v>
+        <v>541363</v>
       </c>
       <c r="R46" t="n">
-        <v>7174307</v>
+        <v>7174330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6133,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6143,12 +6153,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6159,21 +6164,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6190,10 +6180,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845357</v>
+        <v>128845342</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6225,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541607</v>
+        <v>541011</v>
       </c>
       <c r="R47" t="n">
-        <v>7174400</v>
+        <v>7174346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6260,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6270,7 +6260,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6297,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845368</v>
+        <v>128845357</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6332,10 +6322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541363</v>
+        <v>541607</v>
       </c>
       <c r="R48" t="n">
-        <v>7174330</v>
+        <v>7174400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6367,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6377,7 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6404,10 +6394,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845342</v>
+        <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6415,34 +6405,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541011</v>
+        <v>541211</v>
       </c>
       <c r="R49" t="n">
-        <v>7174346</v>
+        <v>7174387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6474,7 +6469,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6484,7 +6479,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845336</v>
+        <v>128845335</v>
       </c>
       <c r="B50" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541251</v>
+        <v>541610</v>
       </c>
       <c r="R50" t="n">
-        <v>7174388</v>
+        <v>7174521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6638,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845335</v>
+        <v>128845336</v>
       </c>
       <c r="B51" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541610</v>
+        <v>541251</v>
       </c>
       <c r="R51" t="n">
-        <v>7174521</v>
+        <v>7174388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6765,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845383</v>
+        <v>128845381</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541079</v>
+        <v>541025</v>
       </c>
       <c r="R52" t="n">
-        <v>7174333</v>
+        <v>7174364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6880,7 +6880,7 @@
         <v>128845385</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845304</v>
+        <v>128845383</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541120</v>
+        <v>541079</v>
       </c>
       <c r="R54" t="n">
-        <v>7174297</v>
+        <v>7174333</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7069,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7096,10 +7101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845369</v>
+        <v>128845304</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7131,10 +7136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541285</v>
+        <v>541120</v>
       </c>
       <c r="R55" t="n">
-        <v>7174269</v>
+        <v>7174297</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7166,7 +7171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7176,7 +7181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7203,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845381</v>
+        <v>128845369</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7238,10 +7243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541025</v>
+        <v>541285</v>
       </c>
       <c r="R56" t="n">
-        <v>7174364</v>
+        <v>7174269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7273,7 +7278,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7283,12 +7288,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7318,7 +7318,7 @@
         <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845373</v>
+        <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541143</v>
+        <v>541462</v>
       </c>
       <c r="R59" t="n">
-        <v>7174450</v>
+        <v>7174528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7640,6 +7645,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7656,10 +7676,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845292</v>
+        <v>128845373</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7667,39 +7687,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541140</v>
+        <v>541143</v>
       </c>
       <c r="R60" t="n">
-        <v>7174441</v>
+        <v>7174450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7731,7 +7746,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7741,12 +7756,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7773,10 +7783,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845333</v>
+        <v>128845348</v>
       </c>
       <c r="B61" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7784,21 +7794,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7808,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541462</v>
+        <v>541504</v>
       </c>
       <c r="R61" t="n">
-        <v>7174528</v>
+        <v>7174451</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7853,12 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7869,21 +7874,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7900,10 +7890,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845348</v>
+        <v>128845354</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7935,10 +7925,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541504</v>
+        <v>541618</v>
       </c>
       <c r="R62" t="n">
-        <v>7174451</v>
+        <v>7174522</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7970,7 +7960,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7980,7 +7970,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8007,10 +7997,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128845354</v>
+        <v>128845292</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8018,34 +8008,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541618</v>
+        <v>541140</v>
       </c>
       <c r="R63" t="n">
-        <v>7174522</v>
+        <v>7174441</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8077,7 +8072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8087,7 +8082,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845378</v>
+        <v>128845375</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541032</v>
+        <v>541136</v>
       </c>
       <c r="R64" t="n">
-        <v>7174308</v>
+        <v>7174402</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8221,10 +8221,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845375</v>
+        <v>128845378</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541136</v>
+        <v>541032</v>
       </c>
       <c r="R65" t="n">
-        <v>7174402</v>
+        <v>7174308</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8331,7 +8331,7 @@
         <v>128845355</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>128845282</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>128845284</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>128845324</v>
       </c>
       <c r="B69" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>128845364</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>128845351</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128845384</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9127,10 +9127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845358</v>
+        <v>128845379</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541633</v>
+        <v>540962</v>
       </c>
       <c r="R73" t="n">
-        <v>7174358</v>
+        <v>7174330</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,7 +9207,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9234,10 +9239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845300</v>
+        <v>128845358</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541095</v>
+        <v>541633</v>
       </c>
       <c r="R74" t="n">
-        <v>7174393</v>
+        <v>7174358</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9304,7 +9309,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9314,7 +9319,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9341,10 +9346,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845379</v>
+        <v>128845300</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9376,10 +9381,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540962</v>
+        <v>541095</v>
       </c>
       <c r="R75" t="n">
-        <v>7174330</v>
+        <v>7174393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9411,7 +9416,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9421,12 +9426,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9580,10 +9580,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845372</v>
+        <v>128845377</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541206</v>
+        <v>541055</v>
       </c>
       <c r="R77" t="n">
-        <v>7174374</v>
+        <v>7174298</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9687,10 +9687,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845377</v>
+        <v>128845372</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541055</v>
+        <v>541206</v>
       </c>
       <c r="R78" t="n">
-        <v>7174298</v>
+        <v>7174374</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845294</v>
+        <v>128845380</v>
       </c>
       <c r="B79" t="n">
-        <v>57883</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,46 +9805,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541544</v>
+        <v>541027</v>
       </c>
       <c r="R79" t="n">
-        <v>7174513</v>
+        <v>7174356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9876,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9886,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9918,10 +9906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9929,21 +9917,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9953,10 +9941,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R80" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9988,7 +9976,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9998,12 +9986,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10014,21 +9997,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10045,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845380</v>
+        <v>128845329</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>91529</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10056,21 +10024,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10080,10 +10048,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541027</v>
+        <v>541141</v>
       </c>
       <c r="R81" t="n">
-        <v>7174356</v>
+        <v>7174388</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10115,7 +10083,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10125,12 +10093,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10141,6 +10109,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10157,10 +10140,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845371</v>
+        <v>128845294</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,34 +10151,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541216</v>
+        <v>541544</v>
       </c>
       <c r="R82" t="n">
-        <v>7174399</v>
+        <v>7174513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10227,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10237,7 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>128845352</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10498,10 +10498,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845347</v>
+        <v>128845302</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541411</v>
+        <v>541089</v>
       </c>
       <c r="R85" t="n">
-        <v>7174397</v>
+        <v>7174431</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10578,12 +10578,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10610,10 +10605,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845302</v>
+        <v>128845347</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10645,10 +10640,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541089</v>
+        <v>541411</v>
       </c>
       <c r="R86" t="n">
-        <v>7174431</v>
+        <v>7174397</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10680,7 +10675,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10690,7 +10685,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10720,7 +10720,7 @@
         <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845344</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10855,39 +10855,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541312</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10919,7 +10914,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10929,12 +10924,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10961,10 +10951,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845276</v>
+        <v>128845278</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10992,7 +10982,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11001,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541274</v>
+        <v>541418</v>
       </c>
       <c r="R89" t="n">
-        <v>7174268</v>
+        <v>7174396</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11036,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11046,12 +11036,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11081,7 +11071,7 @@
         <v>128845281</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11195,10 +11185,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845344</v>
+        <v>128845276</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11206,34 +11196,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541312</v>
+        <v>541274</v>
       </c>
       <c r="R91" t="n">
-        <v>7174300</v>
+        <v>7174268</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11265,7 +11260,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11275,7 +11270,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11302,10 +11302,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845338</v>
+        <v>128845287</v>
       </c>
       <c r="B92" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11313,34 +11313,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541232</v>
+        <v>541428</v>
       </c>
       <c r="R92" t="n">
-        <v>7174426</v>
+        <v>7174314</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11372,7 +11377,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11382,12 +11387,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11398,21 +11403,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11432,7 +11422,7 @@
         <v>128845274</v>
       </c>
       <c r="B93" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11563,7 +11553,7 @@
         <v>128845270</v>
       </c>
       <c r="B94" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11687,10 +11677,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845287</v>
+        <v>128845338</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11698,39 +11688,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541428</v>
+        <v>541232</v>
       </c>
       <c r="R95" t="n">
-        <v>7174314</v>
+        <v>7174426</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11762,7 +11747,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11772,12 +11757,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11788,6 +11773,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11807,7 +11807,7 @@
         <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>128845382</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>128845370</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12150,10 +12150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12387,7 +12387,7 @@
         <v>128845269</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12491,10 +12491,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128845376</v>
+        <v>128845343</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12526,10 +12526,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>541109</v>
+        <v>541074</v>
       </c>
       <c r="R102" t="n">
-        <v>7174267</v>
+        <v>7174298</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12598,10 +12598,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845343</v>
+        <v>128845376</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12633,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541074</v>
+        <v>541109</v>
       </c>
       <c r="R103" t="n">
-        <v>7174298</v>
+        <v>7174267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12708,7 +12708,7 @@
         <v>128845277</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13076,10 +13076,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845366</v>
+        <v>128845345</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541398</v>
+        <v>541348</v>
       </c>
       <c r="R107" t="n">
-        <v>7174337</v>
+        <v>7174394</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,7 +13156,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13183,10 +13188,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845350</v>
+        <v>128845349</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13218,10 +13223,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541554</v>
+        <v>541462</v>
       </c>
       <c r="R108" t="n">
-        <v>7174535</v>
+        <v>7174528</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13253,7 +13258,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13263,12 +13268,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,10 +13295,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845349</v>
+        <v>128845350</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541462</v>
+        <v>541554</v>
       </c>
       <c r="R109" t="n">
-        <v>7174528</v>
+        <v>7174535</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,7 +13375,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13402,10 +13407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845345</v>
+        <v>128845366</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13437,10 +13442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541348</v>
+        <v>541398</v>
       </c>
       <c r="R110" t="n">
-        <v>7174394</v>
+        <v>7174337</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13472,7 +13477,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,12 +13487,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13730,10 +13730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128845306</v>
+        <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>541120</v>
+        <v>541477</v>
       </c>
       <c r="R113" t="n">
-        <v>7174297</v>
+        <v>7174417</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13838,10 +13838,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128845308</v>
+        <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>541477</v>
+        <v>541120</v>
       </c>
       <c r="R114" t="n">
-        <v>7174417</v>
+        <v>7174297</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14486,10 +14486,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128845307</v>
+        <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>541291</v>
+        <v>541125</v>
       </c>
       <c r="R120" t="n">
-        <v>7174294</v>
+        <v>7174337</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14594,10 +14594,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128845315</v>
+        <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14629,10 +14629,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>541125</v>
+        <v>541291</v>
       </c>
       <c r="R121" t="n">
-        <v>7174337</v>
+        <v>7174294</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14702,10 +14702,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128845311</v>
+        <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14737,10 +14737,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>541243</v>
+        <v>541045</v>
       </c>
       <c r="R122" t="n">
-        <v>7174412</v>
+        <v>7174303</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14810,10 +14810,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128845319</v>
+        <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>541045</v>
+        <v>541243</v>
       </c>
       <c r="R123" t="n">
-        <v>7174303</v>
+        <v>7174412</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15355,10 +15355,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128845312</v>
+        <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15390,10 +15390,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>541164</v>
+        <v>541152</v>
       </c>
       <c r="R128" t="n">
-        <v>7174343</v>
+        <v>7174446</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15463,10 +15463,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128845299</v>
+        <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99918</v>
+        <v>99928</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15498,10 +15498,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>541152</v>
+        <v>541164</v>
       </c>
       <c r="R129" t="n">
-        <v>7174446</v>
+        <v>7174343</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -4519,45 +4519,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128845332</v>
+        <v>128845275</v>
       </c>
       <c r="B33" t="n">
-        <v>91551</v>
+        <v>92233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541284</v>
+        <v>541057</v>
       </c>
       <c r="R33" t="n">
-        <v>7174287</v>
+        <v>7174336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4599,12 +4602,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Gamla fruktkroppar på granstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4613,6 +4616,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4646,48 +4650,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845275</v>
+        <v>128845293</v>
       </c>
       <c r="B34" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541057</v>
+        <v>541157</v>
       </c>
       <c r="R34" t="n">
-        <v>7174336</v>
+        <v>7174382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4725,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4735,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på granstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4743,24 +4749,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4777,10 +4767,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845341</v>
+        <v>128845297</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4788,34 +4778,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541131</v>
+        <v>541232</v>
       </c>
       <c r="R35" t="n">
-        <v>7174440</v>
+        <v>7174426</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4847,7 +4845,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4857,7 +4855,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4884,10 +4887,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845293</v>
+        <v>128845332</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,39 +4898,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541157</v>
+        <v>541284</v>
       </c>
       <c r="R36" t="n">
-        <v>7174382</v>
+        <v>7174287</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4959,7 +4957,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4969,12 +4967,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4985,6 +4983,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5001,10 +5014,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845297</v>
+        <v>128845341</v>
       </c>
       <c r="B37" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5012,42 +5025,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541232</v>
+        <v>541131</v>
       </c>
       <c r="R37" t="n">
-        <v>7174426</v>
+        <v>7174440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5084,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5094,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ljudobs.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845367</v>
+        <v>128845339</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,34 +5132,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541394</v>
+        <v>541139</v>
       </c>
       <c r="R38" t="n">
-        <v>7174344</v>
+        <v>7174393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5194,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5204,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5215,8 +5218,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5233,7 +5252,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845362</v>
+        <v>128845367</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -5268,10 +5287,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R39" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5303,7 +5322,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5313,7 +5332,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5340,7 +5364,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845361</v>
+        <v>128845362</v>
       </c>
       <c r="B40" t="n">
         <v>79039</v>
@@ -5375,10 +5399,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541658</v>
+        <v>541644</v>
       </c>
       <c r="R40" t="n">
-        <v>7174215</v>
+        <v>7174158</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5410,7 +5434,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5420,7 +5444,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5447,10 +5471,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845295</v>
+        <v>128845361</v>
       </c>
       <c r="B41" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5458,46 +5482,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R41" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5529,7 +5541,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5539,12 +5551,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5698,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845339</v>
+        <v>128845283</v>
       </c>
       <c r="B43" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5709,37 +5716,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541139</v>
+        <v>541605</v>
       </c>
       <c r="R43" t="n">
-        <v>7174393</v>
+        <v>7174433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5771,7 +5780,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5781,12 +5790,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,24 +5804,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5829,10 +5822,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845283</v>
+        <v>128845295</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5840,39 +5833,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541605</v>
+        <v>541394</v>
       </c>
       <c r="R44" t="n">
-        <v>7174433</v>
+        <v>7174344</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6511,7 +6511,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845335</v>
+        <v>128845336</v>
       </c>
       <c r="B50" t="n">
         <v>91551</v>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541610</v>
+        <v>541251</v>
       </c>
       <c r="R50" t="n">
-        <v>7174521</v>
+        <v>7174388</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6638,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845336</v>
+        <v>128845289</v>
       </c>
       <c r="B51" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6649,34 +6649,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541251</v>
+        <v>541254</v>
       </c>
       <c r="R51" t="n">
-        <v>7174388</v>
+        <v>7174391</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6708,7 +6713,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,12 +6723,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6734,21 +6739,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6765,10 +6755,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845381</v>
+        <v>128845291</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6776,34 +6766,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541025</v>
+        <v>541147</v>
       </c>
       <c r="R52" t="n">
-        <v>7174364</v>
+        <v>7174441</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6835,7 +6830,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,12 +6840,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6877,10 +6872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845385</v>
+        <v>128845335</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6888,21 +6883,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541163</v>
+        <v>541610</v>
       </c>
       <c r="R53" t="n">
-        <v>7174329</v>
+        <v>7174521</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6957,12 +6952,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6973,6 +6968,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6989,7 +6999,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845383</v>
+        <v>128845381</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -7024,10 +7034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541079</v>
+        <v>541025</v>
       </c>
       <c r="R54" t="n">
-        <v>7174333</v>
+        <v>7174364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7069,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7079,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7101,7 +7111,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845304</v>
+        <v>128845385</v>
       </c>
       <c r="B55" t="n">
         <v>79039</v>
@@ -7136,10 +7146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541120</v>
+        <v>541163</v>
       </c>
       <c r="R55" t="n">
-        <v>7174297</v>
+        <v>7174329</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7171,7 +7181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7181,7 +7191,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7208,7 +7223,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845369</v>
+        <v>128845383</v>
       </c>
       <c r="B56" t="n">
         <v>79039</v>
@@ -7243,10 +7258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541285</v>
+        <v>541079</v>
       </c>
       <c r="R56" t="n">
-        <v>7174269</v>
+        <v>7174333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7278,7 +7293,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7288,7 +7303,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7315,10 +7335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845289</v>
+        <v>128845304</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7326,39 +7346,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541254</v>
+        <v>541120</v>
       </c>
       <c r="R57" t="n">
-        <v>7174391</v>
+        <v>7174297</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7390,7 +7405,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7400,12 +7415,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7432,10 +7442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845291</v>
+        <v>128845369</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7443,39 +7453,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541147</v>
+        <v>541285</v>
       </c>
       <c r="R58" t="n">
-        <v>7174441</v>
+        <v>7174269</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7507,7 +7512,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7517,12 +7522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845333</v>
+        <v>128845373</v>
       </c>
       <c r="B59" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541462</v>
+        <v>541143</v>
       </c>
       <c r="R59" t="n">
-        <v>7174528</v>
+        <v>7174450</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,12 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7645,21 +7640,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7676,7 +7656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B60" t="n">
         <v>79039</v>
@@ -7711,10 +7691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7746,7 +7726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7756,7 +7736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7783,7 +7763,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845348</v>
+        <v>128845354</v>
       </c>
       <c r="B61" t="n">
         <v>79039</v>
@@ -7818,10 +7798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541504</v>
+        <v>541618</v>
       </c>
       <c r="R61" t="n">
-        <v>7174451</v>
+        <v>7174522</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7853,7 +7833,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7863,7 +7843,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7890,10 +7870,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845354</v>
+        <v>128845333</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7901,21 +7881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7925,10 +7905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541618</v>
+        <v>541462</v>
       </c>
       <c r="R62" t="n">
-        <v>7174522</v>
+        <v>7174528</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7960,7 +7940,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7970,7 +7950,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7981,6 +7966,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845375</v>
+        <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>91529</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541136</v>
+        <v>541610</v>
       </c>
       <c r="R64" t="n">
-        <v>7174402</v>
+        <v>7174586</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,7 +8194,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8205,6 +8210,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8221,7 +8241,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845378</v>
+        <v>128845375</v>
       </c>
       <c r="B65" t="n">
         <v>79039</v>
@@ -8256,10 +8276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541032</v>
+        <v>541136</v>
       </c>
       <c r="R65" t="n">
-        <v>7174308</v>
+        <v>7174402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8291,7 +8311,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8301,7 +8321,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8328,7 +8348,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845355</v>
+        <v>128845378</v>
       </c>
       <c r="B66" t="n">
         <v>79039</v>
@@ -8363,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541637</v>
+        <v>541032</v>
       </c>
       <c r="R66" t="n">
-        <v>7174473</v>
+        <v>7174308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8398,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8408,12 +8428,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8440,10 +8455,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845282</v>
+        <v>128845355</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8451,29 +8466,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8515,7 +8525,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8525,12 +8535,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,7 +8567,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845284</v>
+        <v>128845282</v>
       </c>
       <c r="B68" t="n">
         <v>57725</v>
@@ -8600,7 +8610,7 @@
         <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8632,7 +8642,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8642,7 +8652,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8674,10 +8684,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845324</v>
+        <v>128845284</v>
       </c>
       <c r="B69" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8685,34 +8695,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R69" t="n">
-        <v>7174586</v>
+        <v>7174351</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8744,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8754,12 +8769,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8770,21 +8785,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -11302,10 +11302,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845287</v>
+        <v>128845338</v>
       </c>
       <c r="B92" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11313,39 +11313,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541428</v>
+        <v>541232</v>
       </c>
       <c r="R92" t="n">
-        <v>7174314</v>
+        <v>7174426</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11377,7 +11372,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11387,12 +11382,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11403,6 +11398,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11419,48 +11429,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845274</v>
+        <v>128845287</v>
       </c>
       <c r="B93" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541116</v>
+        <v>541428</v>
       </c>
       <c r="R93" t="n">
-        <v>7174272</v>
+        <v>7174314</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11492,7 +11504,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11502,12 +11514,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11516,24 +11528,8 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11550,7 +11546,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845270</v>
+        <v>128845274</v>
       </c>
       <c r="B94" t="n">
         <v>92233</v>
@@ -11579,16 +11575,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541134</v>
+        <v>541116</v>
       </c>
       <c r="R94" t="n">
-        <v>7174353</v>
+        <v>7174272</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11620,7 +11619,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11630,12 +11629,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11644,6 +11643,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11677,32 +11677,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845338</v>
+        <v>128845270</v>
       </c>
       <c r="B95" t="n">
-        <v>91551</v>
+        <v>92233</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541232</v>
+        <v>541134</v>
       </c>
       <c r="R95" t="n">
-        <v>7174426</v>
+        <v>7174353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845331</v>
+        <v>128845382</v>
       </c>
       <c r="B96" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541271</v>
+        <v>541041</v>
       </c>
       <c r="R96" t="n">
-        <v>7174269</v>
+        <v>7174348</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,21 +11895,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11931,7 +11911,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
         <v>79039</v>
@@ -11966,10 +11946,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +11981,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,7 +11991,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12038,10 +12023,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845370</v>
+        <v>128845288</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12049,34 +12034,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541222</v>
+        <v>541261</v>
       </c>
       <c r="R98" t="n">
-        <v>7174409</v>
+        <v>7174398</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12108,7 +12098,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12118,12 +12108,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12150,7 +12140,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
         <v>57725</v>
@@ -12190,10 +12180,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12215,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12225,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,10 +12257,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845285</v>
+        <v>128845331</v>
       </c>
       <c r="B100" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12278,39 +12268,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541640</v>
+        <v>541271</v>
       </c>
       <c r="R100" t="n">
-        <v>7174353</v>
+        <v>7174269</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12327,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,12 +12337,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12368,6 +12353,21 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2884,7 +2884,7 @@
         <v>128845325</v>
       </c>
       <c r="B19" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845346</v>
+        <v>128845360</v>
       </c>
       <c r="B23" t="n">
         <v>79039</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541373</v>
+        <v>541640</v>
       </c>
       <c r="R23" t="n">
-        <v>7174407</v>
+        <v>7174274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3469,12 +3469,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3501,7 +3496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845360</v>
+        <v>128845365</v>
       </c>
       <c r="B24" t="n">
         <v>79039</v>
@@ -3536,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541640</v>
+        <v>541453</v>
       </c>
       <c r="R24" t="n">
-        <v>7174274</v>
+        <v>7174305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3571,7 +3566,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3581,7 +3576,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3608,7 +3603,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845365</v>
+        <v>128845346</v>
       </c>
       <c r="B25" t="n">
         <v>79039</v>
@@ -3643,10 +3638,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541453</v>
+        <v>541373</v>
       </c>
       <c r="R25" t="n">
-        <v>7174305</v>
+        <v>7174407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3678,7 +3673,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3688,7 +3683,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B27" t="n">
-        <v>91551</v>
+        <v>57722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,34 +3843,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R27" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3917,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3928,21 +3933,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3959,7 +3949,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845359</v>
+        <v>128845353</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3994,10 +3984,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541617</v>
+        <v>541612</v>
       </c>
       <c r="R28" t="n">
-        <v>7174319</v>
+        <v>7174586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4029,7 +4019,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4039,7 +4029,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4066,7 +4061,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845353</v>
+        <v>128845359</v>
       </c>
       <c r="B29" t="n">
         <v>79039</v>
@@ -4101,10 +4096,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541612</v>
+        <v>541617</v>
       </c>
       <c r="R29" t="n">
-        <v>7174586</v>
+        <v>7174319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4136,7 +4131,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4146,12 +4141,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,10 +4168,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845279</v>
+        <v>128845340</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>91558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,39 +4179,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541504</v>
+        <v>541062</v>
       </c>
       <c r="R30" t="n">
-        <v>7174451</v>
+        <v>7174293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,7 +4238,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4263,12 +4248,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4279,6 +4264,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4295,10 +4295,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B31" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4306,16 +4306,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4326,7 +4326,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R31" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4415,7 +4415,7 @@
         <v>128845323</v>
       </c>
       <c r="B32" t="n">
-        <v>99003</v>
+        <v>99010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>128845275</v>
       </c>
       <c r="B33" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845293</v>
+        <v>128845341</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4661,39 +4661,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541157</v>
+        <v>541131</v>
       </c>
       <c r="R34" t="n">
-        <v>7174382</v>
+        <v>7174440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4725,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4735,12 +4730,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4767,10 +4757,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845297</v>
+        <v>128845332</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4778,42 +4768,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541232</v>
+        <v>541284</v>
       </c>
       <c r="R35" t="n">
-        <v>7174426</v>
+        <v>7174287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4845,7 +4827,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4855,12 +4837,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4871,6 +4853,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4887,10 +4884,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845332</v>
+        <v>128845297</v>
       </c>
       <c r="B36" t="n">
-        <v>91551</v>
+        <v>57722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4898,34 +4895,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541284</v>
+        <v>541232</v>
       </c>
       <c r="R36" t="n">
-        <v>7174287</v>
+        <v>7174426</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4957,7 +4962,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4967,12 +4972,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På stubbe</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4983,21 +4988,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5014,10 +5004,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845341</v>
+        <v>128845293</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5025,34 +5015,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541131</v>
+        <v>541157</v>
       </c>
       <c r="R37" t="n">
-        <v>7174440</v>
+        <v>7174382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5084,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5094,7 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845339</v>
+        <v>128845295</v>
       </c>
       <c r="B38" t="n">
-        <v>91551</v>
+        <v>57885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,26 +5132,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5159,10 +5168,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541139</v>
+        <v>541394</v>
       </c>
       <c r="R38" t="n">
-        <v>7174393</v>
+        <v>7174344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5194,7 +5203,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5204,12 +5213,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5218,24 +5227,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5252,10 +5245,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845367</v>
+        <v>128845339</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,34 +5256,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541394</v>
+        <v>541139</v>
       </c>
       <c r="R39" t="n">
-        <v>7174344</v>
+        <v>7174393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5322,7 +5318,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5332,12 +5328,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5346,8 +5342,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5364,10 +5376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845362</v>
+        <v>128845327</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>91536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5375,21 +5387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5399,10 +5411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541644</v>
+        <v>541654</v>
       </c>
       <c r="R40" t="n">
-        <v>7174158</v>
+        <v>7174247</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5434,7 +5446,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5444,7 +5456,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5455,6 +5472,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5471,7 +5503,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845361</v>
+        <v>128845362</v>
       </c>
       <c r="B41" t="n">
         <v>79039</v>
@@ -5506,10 +5538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541658</v>
+        <v>541644</v>
       </c>
       <c r="R41" t="n">
-        <v>7174215</v>
+        <v>7174158</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5541,7 +5573,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5551,7 +5583,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5578,10 +5610,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845327</v>
+        <v>128845367</v>
       </c>
       <c r="B42" t="n">
-        <v>91529</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5589,21 +5621,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5613,10 +5645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541654</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174247</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5680,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5690,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,21 +5706,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5705,10 +5722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845283</v>
+        <v>128845361</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,39 +5733,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541605</v>
+        <v>541658</v>
       </c>
       <c r="R43" t="n">
-        <v>7174433</v>
+        <v>7174215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5780,7 +5792,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5790,12 +5802,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5822,10 +5829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845295</v>
+        <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5833,46 +5840,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541394</v>
+        <v>541605</v>
       </c>
       <c r="R44" t="n">
-        <v>7174344</v>
+        <v>7174433</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5949,7 +5949,7 @@
         <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845368</v>
+        <v>128845357</v>
       </c>
       <c r="B46" t="n">
         <v>79039</v>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541363</v>
+        <v>541607</v>
       </c>
       <c r="R46" t="n">
-        <v>7174330</v>
+        <v>7174400</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6180,7 +6180,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845342</v>
+        <v>128845368</v>
       </c>
       <c r="B47" t="n">
         <v>79039</v>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541011</v>
+        <v>541363</v>
       </c>
       <c r="R47" t="n">
-        <v>7174346</v>
+        <v>7174330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6287,7 +6287,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845357</v>
+        <v>128845342</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541607</v>
+        <v>541011</v>
       </c>
       <c r="R48" t="n">
-        <v>7174400</v>
+        <v>7174346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845336</v>
+        <v>128845383</v>
       </c>
       <c r="B50" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541251</v>
+        <v>541079</v>
       </c>
       <c r="R50" t="n">
-        <v>7174388</v>
+        <v>7174333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,21 +6607,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6638,10 +6623,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845289</v>
+        <v>128845385</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6649,39 +6634,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541254</v>
+        <v>541163</v>
       </c>
       <c r="R51" t="n">
-        <v>7174391</v>
+        <v>7174329</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6713,7 +6693,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6723,12 +6703,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6755,10 +6735,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845291</v>
+        <v>128845304</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6766,39 +6746,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541147</v>
+        <v>541120</v>
       </c>
       <c r="R52" t="n">
-        <v>7174441</v>
+        <v>7174297</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6830,7 +6805,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6840,12 +6815,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6872,10 +6842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845335</v>
+        <v>128845369</v>
       </c>
       <c r="B53" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6883,21 +6853,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6907,10 +6877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541610</v>
+        <v>541285</v>
       </c>
       <c r="R53" t="n">
-        <v>7174521</v>
+        <v>7174269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6942,7 +6912,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6952,12 +6922,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6968,21 +6933,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7111,10 +7061,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845385</v>
+        <v>128845335</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7122,21 +7072,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7146,10 +7096,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541163</v>
+        <v>541610</v>
       </c>
       <c r="R55" t="n">
-        <v>7174329</v>
+        <v>7174521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,7 +7131,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7191,12 +7141,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7207,6 +7157,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7223,10 +7188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845383</v>
+        <v>128845336</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7234,21 +7199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7258,10 +7223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541079</v>
+        <v>541251</v>
       </c>
       <c r="R56" t="n">
-        <v>7174333</v>
+        <v>7174388</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7293,7 +7258,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7303,12 +7268,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7319,6 +7284,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7335,10 +7315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128845304</v>
+        <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7346,34 +7326,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541120</v>
+        <v>541254</v>
       </c>
       <c r="R57" t="n">
-        <v>7174297</v>
+        <v>7174391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7405,7 +7390,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7415,7 +7400,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7442,10 +7432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128845369</v>
+        <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7453,34 +7443,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541285</v>
+        <v>541147</v>
       </c>
       <c r="R58" t="n">
-        <v>7174269</v>
+        <v>7174441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7512,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7522,7 +7517,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7549,7 +7549,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B59" t="n">
         <v>79039</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R59" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7656,7 +7656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845348</v>
+        <v>128845373</v>
       </c>
       <c r="B60" t="n">
         <v>79039</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541504</v>
+        <v>541143</v>
       </c>
       <c r="R60" t="n">
-        <v>7174451</v>
+        <v>7174450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7873,7 +7873,7 @@
         <v>128845333</v>
       </c>
       <c r="B62" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845324</v>
+        <v>128845284</v>
       </c>
       <c r="B64" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,34 +8125,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R64" t="n">
-        <v>7174586</v>
+        <v>7174351</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8189,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,12 +8199,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8210,21 +8215,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8241,10 +8231,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845375</v>
+        <v>128845282</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,34 +8242,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R65" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8311,7 +8306,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8321,7 +8316,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8348,10 +8348,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845378</v>
+        <v>128845324</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>91536</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8359,21 +8359,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541032</v>
+        <v>541610</v>
       </c>
       <c r="R66" t="n">
-        <v>7174308</v>
+        <v>7174586</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,7 +8428,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8439,6 +8444,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8455,7 +8475,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845355</v>
+        <v>128845378</v>
       </c>
       <c r="B67" t="n">
         <v>79039</v>
@@ -8490,10 +8510,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541637</v>
+        <v>541032</v>
       </c>
       <c r="R67" t="n">
-        <v>7174473</v>
+        <v>7174308</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8525,7 +8545,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8535,12 +8555,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8567,10 +8582,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845282</v>
+        <v>128845375</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8578,39 +8593,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R68" t="n">
-        <v>7174473</v>
+        <v>7174402</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8642,7 +8652,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8652,12 +8662,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8684,10 +8689,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845284</v>
+        <v>128845355</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8695,29 +8700,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8727,7 +8727,7 @@
         <v>541637</v>
       </c>
       <c r="R69" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128845364</v>
+        <v>128845384</v>
       </c>
       <c r="B70" t="n">
         <v>79039</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541490</v>
+        <v>541112</v>
       </c>
       <c r="R70" t="n">
-        <v>7174268</v>
+        <v>7174350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8908,7 +8908,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128845351</v>
+        <v>128845364</v>
       </c>
       <c r="B71" t="n">
         <v>79039</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541563</v>
+        <v>541490</v>
       </c>
       <c r="R71" t="n">
-        <v>7174549</v>
+        <v>7174268</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8988,12 +8988,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9020,7 +9015,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128845384</v>
+        <v>128845351</v>
       </c>
       <c r="B72" t="n">
         <v>79039</v>
@@ -9055,10 +9050,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541112</v>
+        <v>541563</v>
       </c>
       <c r="R72" t="n">
-        <v>7174350</v>
+        <v>7174549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9090,7 +9085,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9100,7 +9095,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9127,7 +9127,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128845379</v>
+        <v>128845358</v>
       </c>
       <c r="B73" t="n">
         <v>79039</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540962</v>
+        <v>541633</v>
       </c>
       <c r="R73" t="n">
-        <v>7174330</v>
+        <v>7174358</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9207,12 +9207,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9239,7 +9234,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128845358</v>
+        <v>128845300</v>
       </c>
       <c r="B74" t="n">
         <v>79039</v>
@@ -9274,10 +9269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541633</v>
+        <v>541095</v>
       </c>
       <c r="R74" t="n">
-        <v>7174358</v>
+        <v>7174393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9309,7 +9304,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9319,7 +9314,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9346,7 +9341,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128845300</v>
+        <v>128845379</v>
       </c>
       <c r="B75" t="n">
         <v>79039</v>
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541095</v>
+        <v>540962</v>
       </c>
       <c r="R75" t="n">
-        <v>7174393</v>
+        <v>7174330</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9416,7 +9411,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9426,7 +9421,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845377</v>
+        <v>128845372</v>
       </c>
       <c r="B77" t="n">
         <v>79039</v>
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541055</v>
+        <v>541206</v>
       </c>
       <c r="R77" t="n">
-        <v>7174298</v>
+        <v>7174374</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9687,7 +9687,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128845372</v>
+        <v>128845377</v>
       </c>
       <c r="B78" t="n">
         <v>79039</v>
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541206</v>
+        <v>541055</v>
       </c>
       <c r="R78" t="n">
-        <v>7174374</v>
+        <v>7174298</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10013,10 +10013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845329</v>
+        <v>128845294</v>
       </c>
       <c r="B81" t="n">
-        <v>91529</v>
+        <v>57885</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,34 +10024,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541141</v>
+        <v>541544</v>
       </c>
       <c r="R81" t="n">
-        <v>7174388</v>
+        <v>7174513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10083,7 +10095,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10093,12 +10105,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10109,21 +10121,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10140,10 +10137,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845294</v>
+        <v>128845329</v>
       </c>
       <c r="B82" t="n">
-        <v>57885</v>
+        <v>91536</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10151,46 +10148,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541544</v>
+        <v>541141</v>
       </c>
       <c r="R82" t="n">
-        <v>7174513</v>
+        <v>7174388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10222,7 +10207,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10232,12 +10217,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10248,6 +10233,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>128845273</v>
       </c>
       <c r="B83" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845302</v>
+        <v>128845347</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -10533,10 +10533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541089</v>
+        <v>541411</v>
       </c>
       <c r="R85" t="n">
-        <v>7174431</v>
+        <v>7174397</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10578,7 +10578,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10605,7 +10610,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845347</v>
+        <v>128845302</v>
       </c>
       <c r="B86" t="n">
         <v>79039</v>
@@ -10640,10 +10645,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541411</v>
+        <v>541089</v>
       </c>
       <c r="R86" t="n">
-        <v>7174397</v>
+        <v>7174431</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10675,7 +10680,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10685,12 +10690,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10720,7 +10720,7 @@
         <v>128845272</v>
       </c>
       <c r="B87" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845344</v>
+        <v>128845278</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10855,34 +10855,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541312</v>
+        <v>541418</v>
       </c>
       <c r="R88" t="n">
-        <v>7174300</v>
+        <v>7174396</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10914,7 +10919,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10924,7 +10929,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10951,7 +10961,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845278</v>
+        <v>128845276</v>
       </c>
       <c r="B89" t="n">
         <v>57725</v>
@@ -10982,7 +10992,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10991,10 +11001,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541418</v>
+        <v>541274</v>
       </c>
       <c r="R89" t="n">
-        <v>7174396</v>
+        <v>7174268</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11036,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,12 +11046,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11185,10 +11195,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845276</v>
+        <v>128845344</v>
       </c>
       <c r="B91" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11196,39 +11206,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541274</v>
+        <v>541312</v>
       </c>
       <c r="R91" t="n">
-        <v>7174268</v>
+        <v>7174300</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11260,7 +11265,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11270,12 +11275,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11305,7 +11305,7 @@
         <v>128845338</v>
       </c>
       <c r="B92" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11429,50 +11429,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845287</v>
+        <v>128845274</v>
       </c>
       <c r="B93" t="n">
-        <v>57725</v>
+        <v>92240</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541428</v>
+        <v>541116</v>
       </c>
       <c r="R93" t="n">
-        <v>7174314</v>
+        <v>7174272</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11504,7 +11502,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11514,12 +11512,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11528,8 +11526,24 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11546,10 +11560,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845274</v>
+        <v>128845270</v>
       </c>
       <c r="B94" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11575,19 +11589,16 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541116</v>
+        <v>541134</v>
       </c>
       <c r="R94" t="n">
-        <v>7174272</v>
+        <v>7174353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11619,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11629,12 +11640,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11643,7 +11654,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11677,45 +11687,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128845270</v>
+        <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541134</v>
+        <v>541428</v>
       </c>
       <c r="R95" t="n">
-        <v>7174353</v>
+        <v>7174314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,7 +11762,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11757,12 +11772,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11773,21 +11788,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11804,7 +11804,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B96" t="n">
         <v>79039</v>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R96" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,7 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11911,7 +11916,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
         <v>79039</v>
@@ -11946,10 +11951,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11981,7 +11986,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11991,12 +11996,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12023,10 +12023,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845288</v>
+        <v>128845331</v>
       </c>
       <c r="B98" t="n">
-        <v>57725</v>
+        <v>91558</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12034,39 +12034,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541261</v>
+        <v>541271</v>
       </c>
       <c r="R98" t="n">
-        <v>7174398</v>
+        <v>7174269</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12098,7 +12093,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12108,12 +12103,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12124,6 +12119,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12257,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845331</v>
+        <v>128845288</v>
       </c>
       <c r="B100" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12268,34 +12278,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541271</v>
+        <v>541261</v>
       </c>
       <c r="R100" t="n">
-        <v>7174269</v>
+        <v>7174398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12327,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12337,12 +12352,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12353,21 +12368,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845269</v>
+        <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,34 +12395,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541134</v>
+        <v>541322</v>
       </c>
       <c r="R101" t="n">
-        <v>7174353</v>
+        <v>7174361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12454,7 +12459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12464,7 +12469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12598,7 +12608,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845376</v>
+        <v>128845269</v>
       </c>
       <c r="B103" t="n">
         <v>79039</v>
@@ -12633,10 +12643,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541109</v>
+        <v>541134</v>
       </c>
       <c r="R103" t="n">
-        <v>7174267</v>
+        <v>7174353</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12668,7 +12678,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12678,7 +12688,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12705,10 +12715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845277</v>
+        <v>128845376</v>
       </c>
       <c r="B104" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12716,39 +12726,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541322</v>
+        <v>541109</v>
       </c>
       <c r="R104" t="n">
-        <v>7174361</v>
+        <v>7174267</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12790,12 +12795,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12825,7 +12825,7 @@
         <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128845345</v>
+        <v>128845366</v>
       </c>
       <c r="B107" t="n">
         <v>79039</v>
@@ -13111,10 +13111,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>541348</v>
+        <v>541398</v>
       </c>
       <c r="R107" t="n">
-        <v>7174394</v>
+        <v>7174337</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13156,12 +13156,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13188,7 +13183,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128845349</v>
+        <v>128845350</v>
       </c>
       <c r="B108" t="n">
         <v>79039</v>
@@ -13223,10 +13218,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>541462</v>
+        <v>541554</v>
       </c>
       <c r="R108" t="n">
-        <v>7174528</v>
+        <v>7174535</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13258,7 +13253,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13268,7 +13263,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845350</v>
+        <v>128845349</v>
       </c>
       <c r="B109" t="n">
         <v>79039</v>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541554</v>
+        <v>541462</v>
       </c>
       <c r="R109" t="n">
-        <v>7174535</v>
+        <v>7174528</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,12 +13375,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13407,7 +13402,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845366</v>
+        <v>128845345</v>
       </c>
       <c r="B110" t="n">
         <v>79039</v>
@@ -13442,10 +13437,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541398</v>
+        <v>541348</v>
       </c>
       <c r="R110" t="n">
-        <v>7174337</v>
+        <v>7174394</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13477,7 +13472,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13487,7 +13482,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128845314</v>
+        <v>128845308</v>
       </c>
       <c r="B112" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>541139</v>
+        <v>541477</v>
       </c>
       <c r="R112" t="n">
-        <v>7174373</v>
+        <v>7174417</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13730,10 +13730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128845308</v>
+        <v>128845314</v>
       </c>
       <c r="B113" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>541477</v>
+        <v>541139</v>
       </c>
       <c r="R113" t="n">
-        <v>7174417</v>
+        <v>7174373</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99928</v>
+        <v>99935</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845356</v>
+        <v>128845325</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541606</v>
+        <v>541618</v>
       </c>
       <c r="R16" t="n">
-        <v>7174439</v>
+        <v>7174399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2630,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2646,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2657,10 +2677,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845363</v>
+        <v>128845356</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541623</v>
+        <v>541606</v>
       </c>
       <c r="R17" t="n">
-        <v>7174167</v>
+        <v>7174439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2737,7 +2757,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845286</v>
+        <v>128845363</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2775,39 +2795,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541617</v>
+        <v>541623</v>
       </c>
       <c r="R18" t="n">
-        <v>7174320</v>
+        <v>7174167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,12 +2864,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845325</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2892,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541618</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174399</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2951,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,12 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På högstubbe av gran</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,21 +2992,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3011,7 +3011,7 @@
         <v>128845328</v>
       </c>
       <c r="B20" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3135,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845296</v>
+        <v>128845360</v>
       </c>
       <c r="B21" t="n">
-        <v>80173</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541359</v>
+        <v>541640</v>
       </c>
       <c r="R21" t="n">
-        <v>7174394</v>
+        <v>7174274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,12 +3215,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,21 +3226,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3262,32 +3242,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845322</v>
+        <v>128845365</v>
       </c>
       <c r="B22" t="n">
-        <v>80180</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3297,10 +3277,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541579</v>
+        <v>541453</v>
       </c>
       <c r="R22" t="n">
-        <v>7174417</v>
+        <v>7174305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,7 +3312,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3342,12 +3322,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3358,21 +3333,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3389,10 +3349,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845360</v>
+        <v>128845346</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3424,10 +3384,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541640</v>
+        <v>541373</v>
       </c>
       <c r="R23" t="n">
-        <v>7174274</v>
+        <v>7174407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3459,7 +3419,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3469,7 +3429,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3496,10 +3461,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845365</v>
+        <v>128845280</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3507,34 +3472,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541453</v>
+        <v>541574</v>
       </c>
       <c r="R24" t="n">
-        <v>7174305</v>
+        <v>7174569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3566,7 +3536,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3576,7 +3546,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3603,32 +3578,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845346</v>
+        <v>128845296</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3638,10 +3613,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541373</v>
+        <v>541359</v>
       </c>
       <c r="R25" t="n">
-        <v>7174407</v>
+        <v>7174394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3673,7 +3648,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3683,12 +3658,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3699,6 +3674,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3715,50 +3705,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845280</v>
+        <v>128845322</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>80182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541574</v>
+        <v>541579</v>
       </c>
       <c r="R26" t="n">
-        <v>7174569</v>
+        <v>7174417</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3790,7 +3775,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3800,12 +3785,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3816,6 +3801,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845298</v>
+        <v>128845353</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,39 +3843,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541013</v>
+        <v>541612</v>
       </c>
       <c r="R27" t="n">
-        <v>7174346</v>
+        <v>7174586</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3907,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3917,12 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3949,10 +3944,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845353</v>
+        <v>128845359</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3984,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541612</v>
+        <v>541617</v>
       </c>
       <c r="R28" t="n">
-        <v>7174586</v>
+        <v>7174319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4029,12 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4061,10 +4051,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845359</v>
+        <v>128845279</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4072,34 +4062,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541617</v>
+        <v>541504</v>
       </c>
       <c r="R29" t="n">
-        <v>7174319</v>
+        <v>7174451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4131,7 +4126,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4141,7 +4136,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4168,10 +4168,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B30" t="n">
-        <v>91558</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4179,34 +4179,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R30" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4238,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4248,12 +4253,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4264,21 +4269,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4295,50 +4285,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845279</v>
+        <v>128845323</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>99012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541504</v>
+        <v>541182</v>
       </c>
       <c r="R31" t="n">
-        <v>7174451</v>
+        <v>7174332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4370,7 +4355,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4380,12 +4365,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4412,32 +4392,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845323</v>
+        <v>128845340</v>
       </c>
       <c r="B32" t="n">
-        <v>99010</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4447,10 +4427,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541182</v>
+        <v>541062</v>
       </c>
       <c r="R32" t="n">
-        <v>7174332</v>
+        <v>7174293</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,7 +4462,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4492,7 +4472,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4503,6 +4488,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v>128845275</v>
       </c>
       <c r="B33" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128845341</v>
+        <v>128845332</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541131</v>
+        <v>541284</v>
       </c>
       <c r="R34" t="n">
-        <v>7174440</v>
+        <v>7174287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4730,7 +4730,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På stubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4741,6 +4746,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4757,10 +4777,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128845332</v>
+        <v>128845341</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4768,21 +4788,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4792,10 +4812,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541284</v>
+        <v>541131</v>
       </c>
       <c r="R35" t="n">
-        <v>7174287</v>
+        <v>7174440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4827,7 +4847,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4837,12 +4857,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På stubbe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,21 +4868,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128845297</v>
+        <v>128845293</v>
       </c>
       <c r="B36" t="n">
-        <v>57722</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4895,16 +4895,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4913,24 +4913,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541232</v>
+        <v>541157</v>
       </c>
       <c r="R36" t="n">
-        <v>7174426</v>
+        <v>7174382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4962,7 +4959,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4972,12 +4969,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ljudobs.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5004,10 +5001,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128845293</v>
+        <v>128845297</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5015,16 +5012,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5033,21 +5030,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541157</v>
+        <v>541232</v>
       </c>
       <c r="R37" t="n">
-        <v>7174382</v>
+        <v>7174426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Ljudobs.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845295</v>
+        <v>128845327</v>
       </c>
       <c r="B38" t="n">
-        <v>57885</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,46 +5132,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541394</v>
+        <v>541654</v>
       </c>
       <c r="R38" t="n">
-        <v>7174344</v>
+        <v>7174247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5203,7 +5191,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5213,12 +5201,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5229,6 +5217,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5248,7 +5251,7 @@
         <v>128845339</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5376,10 +5379,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845327</v>
+        <v>128845362</v>
       </c>
       <c r="B40" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5387,21 +5390,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5411,10 +5414,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541654</v>
+        <v>541644</v>
       </c>
       <c r="R40" t="n">
-        <v>7174247</v>
+        <v>7174158</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5446,7 +5449,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5456,12 +5459,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5472,21 +5470,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5503,10 +5486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845362</v>
+        <v>128845367</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5538,10 +5521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541644</v>
+        <v>541394</v>
       </c>
       <c r="R41" t="n">
-        <v>7174158</v>
+        <v>7174344</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5573,7 +5556,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5583,7 +5566,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5610,10 +5598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845367</v>
+        <v>128845361</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5645,10 +5633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541394</v>
+        <v>541658</v>
       </c>
       <c r="R42" t="n">
-        <v>7174344</v>
+        <v>7174215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5680,7 +5668,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5690,12 +5678,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5722,10 +5705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845361</v>
+        <v>128845295</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5733,34 +5716,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R43" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5802,7 +5797,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5832,7 +5832,7 @@
         <v>128845283</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>128845357</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>128845368</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>128845342</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>128845290</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128845383</v>
+        <v>128845335</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541079</v>
+        <v>541610</v>
       </c>
       <c r="R50" t="n">
-        <v>7174333</v>
+        <v>7174521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,6 +6607,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6623,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128845385</v>
+        <v>128845336</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6634,21 +6649,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6658,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541163</v>
+        <v>541251</v>
       </c>
       <c r="R51" t="n">
-        <v>7174329</v>
+        <v>7174388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6693,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6703,12 +6718,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6719,6 +6734,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6735,10 +6765,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128845304</v>
+        <v>128845383</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6770,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541120</v>
+        <v>541079</v>
       </c>
       <c r="R52" t="n">
-        <v>7174297</v>
+        <v>7174333</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6815,7 +6845,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6842,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128845369</v>
+        <v>128845385</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6877,10 +6912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541285</v>
+        <v>541163</v>
       </c>
       <c r="R53" t="n">
-        <v>7174269</v>
+        <v>7174329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6912,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6922,7 +6957,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6949,10 +6989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845381</v>
+        <v>128845304</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6984,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541025</v>
+        <v>541120</v>
       </c>
       <c r="R54" t="n">
-        <v>7174364</v>
+        <v>7174297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7019,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7029,12 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7061,10 +7096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845335</v>
+        <v>128845369</v>
       </c>
       <c r="B55" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7072,21 +7107,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7096,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541610</v>
+        <v>541285</v>
       </c>
       <c r="R55" t="n">
-        <v>7174521</v>
+        <v>7174269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7131,7 +7166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7141,12 +7176,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7157,21 +7187,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7188,10 +7203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845336</v>
+        <v>128845381</v>
       </c>
       <c r="B56" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7199,21 +7214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7223,10 +7238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541251</v>
+        <v>541025</v>
       </c>
       <c r="R56" t="n">
-        <v>7174388</v>
+        <v>7174364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7258,7 +7273,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7268,12 +7283,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7284,21 +7299,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7318,7 +7318,7 @@
         <v>128845289</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128845291</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128845348</v>
+        <v>128845333</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541504</v>
+        <v>541462</v>
       </c>
       <c r="R59" t="n">
-        <v>7174451</v>
+        <v>7174528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7629,7 +7629,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På stubbe och låga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7640,6 +7645,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7656,10 +7676,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128845373</v>
+        <v>128845348</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7691,10 +7711,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541143</v>
+        <v>541504</v>
       </c>
       <c r="R60" t="n">
-        <v>7174450</v>
+        <v>7174451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7746,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7736,7 +7756,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7763,10 +7783,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128845354</v>
+        <v>128845373</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7798,10 +7818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541618</v>
+        <v>541143</v>
       </c>
       <c r="R61" t="n">
-        <v>7174522</v>
+        <v>7174450</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7833,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7843,7 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7870,10 +7890,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128845333</v>
+        <v>128845354</v>
       </c>
       <c r="B62" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7881,21 +7901,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7905,10 +7925,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541462</v>
+        <v>541618</v>
       </c>
       <c r="R62" t="n">
-        <v>7174528</v>
+        <v>7174522</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7940,7 +7960,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7950,12 +7970,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På stubbe och låga</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7966,21 +7981,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8000,7 +8000,7 @@
         <v>128845292</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845284</v>
+        <v>128845324</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,39 +8125,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R64" t="n">
-        <v>7174351</v>
+        <v>7174586</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8189,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8199,12 +8194,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8215,6 +8210,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8234,7 +8244,7 @@
         <v>128845282</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8348,10 +8358,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845324</v>
+        <v>128845284</v>
       </c>
       <c r="B66" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8359,34 +8369,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541610</v>
+        <v>541637</v>
       </c>
       <c r="R66" t="n">
-        <v>7174586</v>
+        <v>7174351</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8418,7 +8433,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8428,12 +8443,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8444,21 +8459,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8478,7 +8478,7 @@
         <v>128845378</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>128845375</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>128845355</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>128845384</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>128845364</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>128845351</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>128845358</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>128845300</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>128845379</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>128845271</v>
       </c>
       <c r="B76" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>128845372</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>128845377</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845380</v>
+        <v>128845294</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,34 +9805,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541027</v>
+        <v>541544</v>
       </c>
       <c r="R79" t="n">
-        <v>7174356</v>
+        <v>7174513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9874,12 +9886,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9906,10 +9918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845371</v>
+        <v>128845329</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9917,21 +9929,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9941,10 +9953,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541216</v>
+        <v>541141</v>
       </c>
       <c r="R80" t="n">
-        <v>7174399</v>
+        <v>7174388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9976,7 +9988,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9986,7 +9998,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9997,6 +10014,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10013,10 +10045,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845294</v>
+        <v>128845380</v>
       </c>
       <c r="B81" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10024,46 +10056,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541544</v>
+        <v>541027</v>
       </c>
       <c r="R81" t="n">
-        <v>7174513</v>
+        <v>7174356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10095,7 +10115,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10105,12 +10125,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10137,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845329</v>
+        <v>128845371</v>
       </c>
       <c r="B82" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10148,21 +10168,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10172,10 +10192,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541141</v>
+        <v>541216</v>
       </c>
       <c r="R82" t="n">
-        <v>7174388</v>
+        <v>7174399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10207,7 +10227,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10217,12 +10237,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10233,21 +10248,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10264,32 +10264,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128845273</v>
+        <v>128845352</v>
       </c>
       <c r="B83" t="n">
-        <v>92240</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541329</v>
+        <v>541591</v>
       </c>
       <c r="R83" t="n">
-        <v>7174232</v>
+        <v>7174563</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10344,12 +10344,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10360,21 +10355,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10391,10 +10371,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128845352</v>
+        <v>128845347</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10426,10 +10406,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>541591</v>
+        <v>541411</v>
       </c>
       <c r="R84" t="n">
-        <v>7174563</v>
+        <v>7174397</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10461,7 +10441,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10471,7 +10451,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10498,10 +10483,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128845347</v>
+        <v>128845302</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10533,10 +10518,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541411</v>
+        <v>541089</v>
       </c>
       <c r="R85" t="n">
-        <v>7174397</v>
+        <v>7174431</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10568,7 +10553,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10578,12 +10563,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10610,32 +10590,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128845302</v>
+        <v>128845273</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10645,10 +10625,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541089</v>
+        <v>541329</v>
       </c>
       <c r="R86" t="n">
-        <v>7174431</v>
+        <v>7174232</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10680,7 +10660,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10690,7 +10670,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10701,6 +10686,21 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10717,45 +10717,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128845272</v>
+        <v>128845278</v>
       </c>
       <c r="B87" t="n">
-        <v>92240</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541629</v>
+        <v>541418</v>
       </c>
       <c r="R87" t="n">
-        <v>7174402</v>
+        <v>7174396</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10787,7 +10792,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10797,12 +10802,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10813,21 +10818,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10844,10 +10834,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845278</v>
+        <v>128845281</v>
       </c>
       <c r="B88" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10875,7 +10865,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10884,10 +10874,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541418</v>
+        <v>541599</v>
       </c>
       <c r="R88" t="n">
-        <v>7174396</v>
+        <v>7174544</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10919,7 +10909,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10929,12 +10919,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10964,7 +10954,7 @@
         <v>128845276</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11078,50 +11068,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845281</v>
+        <v>128845272</v>
       </c>
       <c r="B90" t="n">
-        <v>57725</v>
+        <v>92242</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541599</v>
+        <v>541629</v>
       </c>
       <c r="R90" t="n">
-        <v>7174544</v>
+        <v>7174402</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11153,7 +11138,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11163,12 +11148,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11179,6 +11164,21 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11198,7 +11198,7 @@
         <v>128845344</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11302,45 +11302,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845338</v>
+        <v>128845274</v>
       </c>
       <c r="B92" t="n">
-        <v>91558</v>
+        <v>92242</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541232</v>
+        <v>541116</v>
       </c>
       <c r="R92" t="n">
-        <v>7174426</v>
+        <v>7174272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11372,7 +11375,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11382,12 +11385,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11396,6 +11399,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11429,10 +11433,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845274</v>
+        <v>128845270</v>
       </c>
       <c r="B93" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11458,19 +11462,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541116</v>
+        <v>541134</v>
       </c>
       <c r="R93" t="n">
-        <v>7174272</v>
+        <v>7174353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11502,7 +11503,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11512,12 +11513,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11526,7 +11527,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11560,32 +11560,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128845270</v>
+        <v>128845338</v>
       </c>
       <c r="B94" t="n">
-        <v>92240</v>
+        <v>91560</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541134</v>
+        <v>541232</v>
       </c>
       <c r="R94" t="n">
-        <v>7174353</v>
+        <v>7174426</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -11690,7 +11690,7 @@
         <v>128845287</v>
       </c>
       <c r="B95" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128845370</v>
+        <v>128845331</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>541222</v>
+        <v>541271</v>
       </c>
       <c r="R96" t="n">
-        <v>7174409</v>
+        <v>7174269</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11900,6 +11900,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11916,10 +11931,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11951,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R97" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11986,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11996,7 +12011,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12023,10 +12043,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845331</v>
+        <v>128845382</v>
       </c>
       <c r="B98" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12034,21 +12054,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12058,10 +12078,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541271</v>
+        <v>541041</v>
       </c>
       <c r="R98" t="n">
-        <v>7174269</v>
+        <v>7174348</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12093,7 +12113,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12103,12 +12123,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12119,21 +12134,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12150,10 +12150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B99" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R99" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,10 +12267,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B100" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R100" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12387,7 +12387,7 @@
         <v>128845277</v>
       </c>
       <c r="B101" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>128845343</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>128845269</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>128845376</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>128845330</v>
       </c>
       <c r="B105" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>128845334</v>
       </c>
       <c r="B106" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>128845366</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>128845350</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>128845349</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>128845345</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128845318</v>
       </c>
       <c r="B111" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128845308</v>
+        <v>128845314</v>
       </c>
       <c r="B112" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>541477</v>
+        <v>541139</v>
       </c>
       <c r="R112" t="n">
-        <v>7174417</v>
+        <v>7174373</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13730,10 +13730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128845314</v>
+        <v>128845308</v>
       </c>
       <c r="B113" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>541139</v>
+        <v>541477</v>
       </c>
       <c r="R113" t="n">
-        <v>7174373</v>
+        <v>7174417</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13841,7 +13841,7 @@
         <v>128845306</v>
       </c>
       <c r="B114" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128845317</v>
       </c>
       <c r="B115" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>128845301</v>
       </c>
       <c r="B116" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>128845316</v>
       </c>
       <c r="B117" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>128845310</v>
       </c>
       <c r="B118" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>128845303</v>
       </c>
       <c r="B119" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>128845315</v>
       </c>
       <c r="B120" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128845307</v>
       </c>
       <c r="B121" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>128845319</v>
       </c>
       <c r="B122" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>128845311</v>
       </c>
       <c r="B123" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>128845313</v>
       </c>
       <c r="B124" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>128845320</v>
       </c>
       <c r="B125" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>128845309</v>
       </c>
       <c r="B126" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>128845321</v>
       </c>
       <c r="B127" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>128845299</v>
       </c>
       <c r="B128" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>128845312</v>
       </c>
       <c r="B129" t="n">
-        <v>99935</v>
+        <v>99937</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845325</v>
+        <v>128845363</v>
       </c>
       <c r="B16" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541618</v>
+        <v>541623</v>
       </c>
       <c r="R16" t="n">
-        <v>7174399</v>
+        <v>7174167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,12 +2630,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,21 +2641,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2677,10 +2657,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845356</v>
+        <v>128845286</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,34 +2668,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541606</v>
+        <v>541617</v>
       </c>
       <c r="R17" t="n">
-        <v>7174439</v>
+        <v>7174320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2732,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,7 +2742,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2784,10 +2774,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845363</v>
+        <v>128845325</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2785,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541623</v>
+        <v>541618</v>
       </c>
       <c r="R18" t="n">
-        <v>7174167</v>
+        <v>7174399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2854,7 +2844,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,7 +2854,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,6 +2870,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2891,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845286</v>
+        <v>128845356</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2902,39 +2912,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541617</v>
+        <v>541606</v>
       </c>
       <c r="R19" t="n">
-        <v>7174320</v>
+        <v>7174439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2966,7 +2971,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2976,12 +2981,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,32 +3008,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845328</v>
+        <v>128845296</v>
       </c>
       <c r="B20" t="n">
-        <v>91538</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541428</v>
+        <v>541359</v>
       </c>
       <c r="R20" t="n">
-        <v>7174314</v>
+        <v>7174394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3135,32 +3135,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845360</v>
+        <v>128845322</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541640</v>
+        <v>541579</v>
       </c>
       <c r="R21" t="n">
-        <v>7174274</v>
+        <v>7174417</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3215,7 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3226,6 +3231,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3461,10 +3481,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845280</v>
+        <v>128845328</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3472,39 +3492,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541574</v>
+        <v>541428</v>
       </c>
       <c r="R24" t="n">
-        <v>7174569</v>
+        <v>7174314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3536,7 +3551,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3546,12 +3561,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3562,6 +3577,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3578,32 +3608,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845296</v>
+        <v>128845360</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3613,10 +3643,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541359</v>
+        <v>541640</v>
       </c>
       <c r="R25" t="n">
-        <v>7174394</v>
+        <v>7174274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3648,7 +3678,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3658,12 +3688,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3674,21 +3699,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3705,45 +3715,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845322</v>
+        <v>128845280</v>
       </c>
       <c r="B26" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541579</v>
+        <v>541574</v>
       </c>
       <c r="R26" t="n">
-        <v>7174417</v>
+        <v>7174569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3785,12 +3800,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,21 +3816,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845353</v>
+        <v>128845323</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>99012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541612</v>
+        <v>541182</v>
       </c>
       <c r="R27" t="n">
-        <v>7174586</v>
+        <v>7174332</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,12 +3912,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3944,7 +3939,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845359</v>
+        <v>128845353</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541617</v>
+        <v>541612</v>
       </c>
       <c r="R28" t="n">
-        <v>7174319</v>
+        <v>7174586</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4019,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,10 +4051,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845279</v>
+        <v>128845359</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4062,39 +4062,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541504</v>
+        <v>541617</v>
       </c>
       <c r="R29" t="n">
-        <v>7174451</v>
+        <v>7174319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4126,7 +4121,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4136,12 +4131,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4168,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4179,16 +4169,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4199,7 +4189,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R30" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4243,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,12 +4243,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4285,45 +4275,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845323</v>
+        <v>128845298</v>
       </c>
       <c r="B31" t="n">
-        <v>99012</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219880</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541182</v>
+        <v>541013</v>
       </c>
       <c r="R31" t="n">
-        <v>7174332</v>
+        <v>7174346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4355,7 +4350,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4365,7 +4360,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128845327</v>
+        <v>128845283</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5132,34 +5132,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541654</v>
+        <v>541605</v>
       </c>
       <c r="R38" t="n">
-        <v>7174247</v>
+        <v>7174433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5191,7 +5196,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5201,12 +5206,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5217,21 +5222,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5248,10 +5238,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128845339</v>
+        <v>128845295</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5259,26 +5249,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5286,10 +5285,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541139</v>
+        <v>541394</v>
       </c>
       <c r="R39" t="n">
-        <v>7174393</v>
+        <v>7174344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5321,7 +5320,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5331,12 +5330,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar på stubbe</t>
+          <t>Ljudobs 2 varnande individer</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5345,24 +5344,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,10 +5362,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128845362</v>
+        <v>128845339</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5390,34 +5373,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541644</v>
+        <v>541139</v>
       </c>
       <c r="R40" t="n">
-        <v>7174158</v>
+        <v>7174393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5449,7 +5435,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5459,7 +5445,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på stubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5468,8 +5459,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5486,10 +5493,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128845367</v>
+        <v>128845327</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5497,21 +5504,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5521,10 +5528,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541394</v>
+        <v>541654</v>
       </c>
       <c r="R41" t="n">
-        <v>7174344</v>
+        <v>7174247</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5556,7 +5563,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5566,12 +5573,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5582,6 +5589,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5598,7 +5620,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128845361</v>
+        <v>128845367</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -5633,10 +5655,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541658</v>
+        <v>541394</v>
       </c>
       <c r="R42" t="n">
-        <v>7174215</v>
+        <v>7174344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5668,7 +5690,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5678,7 +5700,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5705,10 +5732,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128845295</v>
+        <v>128845362</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5716,46 +5743,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541394</v>
+        <v>541644</v>
       </c>
       <c r="R43" t="n">
-        <v>7174344</v>
+        <v>7174158</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5787,7 +5802,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5797,12 +5812,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ljudobs 2 varnande individer</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5829,10 +5839,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128845283</v>
+        <v>128845361</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5840,39 +5850,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541605</v>
+        <v>541658</v>
       </c>
       <c r="R44" t="n">
-        <v>7174433</v>
+        <v>7174215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5904,7 +5909,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5914,12 +5919,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845326</v>
+        <v>128845290</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,34 +5957,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541626</v>
+        <v>541211</v>
       </c>
       <c r="R45" t="n">
-        <v>7174307</v>
+        <v>7174387</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6016,7 +6021,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6026,12 +6031,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,21 +6047,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6073,10 +6063,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845357</v>
+        <v>128845326</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6084,21 +6074,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6108,10 +6098,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541607</v>
+        <v>541626</v>
       </c>
       <c r="R46" t="n">
-        <v>7174400</v>
+        <v>7174307</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6143,7 +6133,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6153,7 +6143,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6164,6 +6159,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6180,7 +6190,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845368</v>
+        <v>128845357</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -6215,10 +6225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541363</v>
+        <v>541607</v>
       </c>
       <c r="R47" t="n">
-        <v>7174330</v>
+        <v>7174400</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6260,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,7 +6270,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6287,7 +6297,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128845342</v>
+        <v>128845368</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -6322,10 +6332,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541011</v>
+        <v>541363</v>
       </c>
       <c r="R48" t="n">
-        <v>7174346</v>
+        <v>7174330</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6367,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6367,7 +6377,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6394,10 +6404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128845290</v>
+        <v>128845342</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6405,39 +6415,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541211</v>
+        <v>541011</v>
       </c>
       <c r="R49" t="n">
-        <v>7174387</v>
+        <v>7174346</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6469,7 +6474,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6479,12 +6484,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6989,7 +6989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128845304</v>
+        <v>128845381</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541120</v>
+        <v>541025</v>
       </c>
       <c r="R54" t="n">
-        <v>7174297</v>
+        <v>7174364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7069,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7096,7 +7101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128845369</v>
+        <v>128845304</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -7131,10 +7136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541285</v>
+        <v>541120</v>
       </c>
       <c r="R55" t="n">
-        <v>7174269</v>
+        <v>7174297</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7166,7 +7171,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7176,7 +7181,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7203,7 +7208,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128845381</v>
+        <v>128845369</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -7238,10 +7243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541025</v>
+        <v>541285</v>
       </c>
       <c r="R56" t="n">
-        <v>7174364</v>
+        <v>7174269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7273,7 +7278,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7283,12 +7288,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128845324</v>
+        <v>128845378</v>
       </c>
       <c r="B64" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541610</v>
+        <v>541032</v>
       </c>
       <c r="R64" t="n">
-        <v>7174586</v>
+        <v>7174308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8194,12 +8194,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På levande gran</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8210,21 +8205,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8241,10 +8221,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128845282</v>
+        <v>128845375</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,39 +8232,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541637</v>
+        <v>541136</v>
       </c>
       <c r="R65" t="n">
-        <v>7174473</v>
+        <v>7174402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8316,7 +8291,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8326,12 +8301,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8358,10 +8328,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128845284</v>
+        <v>128845355</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8369,29 +8339,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
@@ -8401,7 +8366,7 @@
         <v>541637</v>
       </c>
       <c r="R66" t="n">
-        <v>7174351</v>
+        <v>7174473</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8433,7 +8398,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8443,12 +8408,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8475,10 +8440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128845378</v>
+        <v>128845284</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8486,34 +8451,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541032</v>
+        <v>541637</v>
       </c>
       <c r="R67" t="n">
-        <v>7174308</v>
+        <v>7174351</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8545,7 +8515,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8555,7 +8525,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8582,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128845375</v>
+        <v>128845282</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8593,34 +8568,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541136</v>
+        <v>541637</v>
       </c>
       <c r="R68" t="n">
-        <v>7174402</v>
+        <v>7174473</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8652,7 +8632,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8662,7 +8642,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8689,10 +8674,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128845355</v>
+        <v>128845324</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8700,21 +8685,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8724,10 +8709,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541637</v>
+        <v>541610</v>
       </c>
       <c r="R69" t="n">
-        <v>7174473</v>
+        <v>7174586</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8759,7 +8744,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8769,12 +8754,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8785,6 +8770,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9453,32 +9453,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128845271</v>
+        <v>128845372</v>
       </c>
       <c r="B76" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541616</v>
+        <v>541206</v>
       </c>
       <c r="R76" t="n">
-        <v>7174449</v>
+        <v>7174374</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9533,12 +9533,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På stående levande gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9549,21 +9544,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9580,32 +9560,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128845372</v>
+        <v>128845271</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9615,10 +9595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541206</v>
+        <v>541616</v>
       </c>
       <c r="R77" t="n">
-        <v>7174374</v>
+        <v>7174449</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9650,7 +9630,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9660,7 +9640,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På stående levande gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9671,6 +9656,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9794,10 +9794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128845294</v>
+        <v>128845329</v>
       </c>
       <c r="B79" t="n">
-        <v>57887</v>
+        <v>91538</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9805,46 +9805,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541544</v>
+        <v>541141</v>
       </c>
       <c r="R79" t="n">
-        <v>7174513</v>
+        <v>7174388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9876,7 +9864,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9886,12 +9874,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobs</t>
+          <t>På stubbe, låga och levande gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9902,6 +9890,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9918,10 +9921,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128845329</v>
+        <v>128845380</v>
       </c>
       <c r="B80" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9929,21 +9932,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9953,10 +9956,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541141</v>
+        <v>541027</v>
       </c>
       <c r="R80" t="n">
-        <v>7174388</v>
+        <v>7174356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9988,7 +9991,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9998,12 +10001,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På stubbe, låga och levande gran</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10014,21 +10017,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10045,7 +10033,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128845380</v>
+        <v>128845371</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -10080,10 +10068,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541027</v>
+        <v>541216</v>
       </c>
       <c r="R81" t="n">
-        <v>7174356</v>
+        <v>7174399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10115,7 +10103,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10125,12 +10113,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10157,10 +10140,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128845371</v>
+        <v>128845294</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,34 +10151,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541216</v>
+        <v>541544</v>
       </c>
       <c r="R82" t="n">
-        <v>7174399</v>
+        <v>7174513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10227,7 +10222,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10237,7 +10232,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Synobs</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10834,7 +10834,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128845281</v>
+        <v>128845276</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -10874,10 +10874,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>541599</v>
+        <v>541274</v>
       </c>
       <c r="R88" t="n">
-        <v>7174544</v>
+        <v>7174268</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10951,7 +10951,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128845276</v>
+        <v>128845281</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>541274</v>
+        <v>541599</v>
       </c>
       <c r="R89" t="n">
-        <v>7174268</v>
+        <v>7174544</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -11068,32 +11068,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128845272</v>
+        <v>128845344</v>
       </c>
       <c r="B90" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541629</v>
+        <v>541312</v>
       </c>
       <c r="R90" t="n">
-        <v>7174402</v>
+        <v>7174300</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11148,12 +11148,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>I en stubbe av nyfallen gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11164,21 +11159,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11195,32 +11175,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128845344</v>
+        <v>128845272</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11230,10 +11210,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541312</v>
+        <v>541629</v>
       </c>
       <c r="R91" t="n">
-        <v>7174300</v>
+        <v>7174402</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11265,7 +11245,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11275,7 +11255,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I en stubbe av nyfallen gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11286,6 +11271,21 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11302,7 +11302,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128845274</v>
+        <v>128845270</v>
       </c>
       <c r="B92" t="n">
         <v>92242</v>
@@ -11331,19 +11331,16 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541116</v>
+        <v>541134</v>
       </c>
       <c r="R92" t="n">
-        <v>7174272</v>
+        <v>7174353</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11375,7 +11372,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11385,12 +11382,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På stubbe, gamla fruktkroppar</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11399,7 +11396,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11433,7 +11429,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128845270</v>
+        <v>128845274</v>
       </c>
       <c r="B93" t="n">
         <v>92242</v>
@@ -11462,16 +11458,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>541134</v>
+        <v>541116</v>
       </c>
       <c r="R93" t="n">
-        <v>7174353</v>
+        <v>7174272</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11503,7 +11502,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11513,12 +11512,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På stubbe, gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11527,6 +11526,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128845370</v>
+        <v>128845382</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>541222</v>
+        <v>541041</v>
       </c>
       <c r="R97" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12011,12 +12011,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12043,7 +12038,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128845382</v>
+        <v>128845370</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541041</v>
+        <v>541222</v>
       </c>
       <c r="R98" t="n">
-        <v>7174348</v>
+        <v>7174409</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12113,7 +12108,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12123,7 +12118,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12150,7 +12150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128845288</v>
+        <v>128845285</v>
       </c>
       <c r="B99" t="n">
         <v>57727</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>541261</v>
+        <v>541640</v>
       </c>
       <c r="R99" t="n">
-        <v>7174398</v>
+        <v>7174353</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12267,7 +12267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128845285</v>
+        <v>128845288</v>
       </c>
       <c r="B100" t="n">
         <v>57727</v>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541640</v>
+        <v>541261</v>
       </c>
       <c r="R100" t="n">
-        <v>7174353</v>
+        <v>7174398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12384,10 +12384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128845277</v>
+        <v>128845269</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12395,39 +12395,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>541322</v>
+        <v>541134</v>
       </c>
       <c r="R101" t="n">
-        <v>7174361</v>
+        <v>7174353</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12459,7 +12454,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12469,12 +12464,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12608,7 +12598,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128845269</v>
+        <v>128845376</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -12643,10 +12633,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>541134</v>
+        <v>541109</v>
       </c>
       <c r="R103" t="n">
-        <v>7174353</v>
+        <v>7174267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12678,7 +12668,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12688,7 +12678,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12715,10 +12705,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128845376</v>
+        <v>128845277</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,34 +12716,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541109</v>
+        <v>541322</v>
       </c>
       <c r="R104" t="n">
-        <v>7174267</v>
+        <v>7174361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12785,7 +12780,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12795,7 +12790,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128845349</v>
+        <v>128845345</v>
       </c>
       <c r="B109" t="n">
         <v>79041</v>
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541462</v>
+        <v>541348</v>
       </c>
       <c r="R109" t="n">
-        <v>7174528</v>
+        <v>7174394</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13375,7 +13375,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13402,7 +13407,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128845345</v>
+        <v>128845349</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -13437,10 +13442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541348</v>
+        <v>541462</v>
       </c>
       <c r="R110" t="n">
-        <v>7174394</v>
+        <v>7174528</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13472,7 +13477,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,12 +13487,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845363</v>
+        <v>128845325</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541623</v>
+        <v>541618</v>
       </c>
       <c r="R16" t="n">
-        <v>7174167</v>
+        <v>7174399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2630,7 +2630,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2646,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2657,10 +2677,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845286</v>
+        <v>128845356</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,39 +2688,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541617</v>
+        <v>541606</v>
       </c>
       <c r="R17" t="n">
-        <v>7174320</v>
+        <v>7174439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2732,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2742,12 +2757,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2774,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845325</v>
+        <v>128845363</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2785,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2809,10 +2819,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541618</v>
+        <v>541623</v>
       </c>
       <c r="R18" t="n">
-        <v>7174399</v>
+        <v>7174167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2844,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2854,12 +2864,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2870,21 +2875,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2901,10 +2891,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845356</v>
+        <v>128845286</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,34 +2902,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541606</v>
+        <v>541617</v>
       </c>
       <c r="R19" t="n">
-        <v>7174439</v>
+        <v>7174320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2971,7 +2966,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,7 +2976,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845323</v>
+        <v>128845340</v>
       </c>
       <c r="B27" t="n">
-        <v>99012</v>
+        <v>91560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541182</v>
+        <v>541062</v>
       </c>
       <c r="R27" t="n">
-        <v>7174332</v>
+        <v>7174293</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3923,6 +3928,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3939,32 +3959,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845353</v>
+        <v>128845323</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>99012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3974,10 +3994,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541612</v>
+        <v>541182</v>
       </c>
       <c r="R28" t="n">
-        <v>7174586</v>
+        <v>7174332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4009,7 +4029,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4019,12 +4039,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,7 +4066,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845359</v>
+        <v>128845353</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -4086,10 +4101,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541617</v>
+        <v>541612</v>
       </c>
       <c r="R29" t="n">
-        <v>7174319</v>
+        <v>7174586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4121,7 +4136,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4131,7 +4146,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4158,10 +4178,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845279</v>
+        <v>128845359</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4169,39 +4189,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541504</v>
+        <v>541617</v>
       </c>
       <c r="R30" t="n">
-        <v>7174451</v>
+        <v>7174319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4233,7 +4248,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4243,12 +4258,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4275,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845298</v>
+        <v>128845279</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4286,16 +4296,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4306,7 +4316,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4315,10 +4325,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541013</v>
+        <v>541504</v>
       </c>
       <c r="R31" t="n">
-        <v>7174346</v>
+        <v>7174451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4350,7 +4360,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4360,12 +4370,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,10 +4402,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128845340</v>
+        <v>128845298</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4403,34 +4413,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541062</v>
+        <v>541013</v>
       </c>
       <c r="R32" t="n">
-        <v>7174293</v>
+        <v>7174346</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4462,7 +4477,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4472,12 +4487,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På manshög stubbe</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4488,21 +4503,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128845290</v>
+        <v>128845326</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5957,39 +5957,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541211</v>
+        <v>541626</v>
       </c>
       <c r="R45" t="n">
-        <v>7174387</v>
+        <v>7174307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6021,7 +6016,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6031,12 +6026,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På manshög stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6047,6 +6042,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6063,10 +6073,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128845326</v>
+        <v>128845357</v>
       </c>
       <c r="B46" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6074,21 +6084,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6098,10 +6108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541626</v>
+        <v>541607</v>
       </c>
       <c r="R46" t="n">
-        <v>7174307</v>
+        <v>7174400</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6133,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6143,12 +6153,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På manshög stubbe</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6159,21 +6164,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6190,7 +6180,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128845357</v>
+        <v>128845368</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -6225,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541607</v>
+        <v>541363</v>
       </c>
       <c r="R47" t="n">
-        <v>7174400</v>
+        <v>7174330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6260,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6270,7 +6260,7 @@
       </c>
       <c r="A